--- a/tiers_gen9nationaldexdoubles.xlsx
+++ b/tiers_gen9nationaldexdoubles.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\power bi\webhook\codigo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\power bi\webhook\Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB694749-3AC9-469E-8671-4780C71A57E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A986137A-4586-4B31-A040-075B7F8441A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2128,7 +2128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -2143,6 +2143,12 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -33884,16 +33890,16 @@
       <c r="A2" s="4" t="s">
         <v>616</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>478</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="7" t="s">
         <v>470</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>478</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="7" t="s">
         <v>470</v>
       </c>
     </row>
@@ -33901,13 +33907,13 @@
       <c r="A3" s="4" t="s">
         <v>617</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>566</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>511</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>566</v>
       </c>
       <c r="E3" s="5" t="s">
@@ -33918,13 +33924,13 @@
       <c r="A4" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>412</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>486</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="4" t="s">
         <v>412</v>
       </c>
       <c r="E4" s="5" t="s">
@@ -33935,47 +33941,47 @@
       <c r="A5" s="4" t="s">
         <v>619</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
+        <v>563</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>563</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="E5" s="5" t="s">
         <v>221</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>563</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>620</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
+        <v>546</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>336</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="D6" s="4" t="s">
         <v>546</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="E6" s="5" t="s">
         <v>336</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>621</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>188</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="4" t="s">
         <v>188</v>
       </c>
       <c r="E7" s="5" t="s">
@@ -33986,30 +33992,30 @@
       <c r="A8" s="4" t="s">
         <v>622</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="D8" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="E8" s="5" t="s">
         <v>236</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>623</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>347</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>507</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="4" t="s">
         <v>347</v>
       </c>
       <c r="E9" s="5" t="s">
@@ -34020,13 +34026,13 @@
       <c r="A10" s="4" t="s">
         <v>624</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="4" t="s">
         <v>182</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="4" t="s">
         <v>182</v>
       </c>
       <c r="E10" s="5" t="s">
@@ -34037,13 +34043,13 @@
       <c r="A11" s="4" t="s">
         <v>625</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>325</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>555</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="4" t="s">
         <v>325</v>
       </c>
       <c r="E11" s="5" t="s">
@@ -34054,47 +34060,47 @@
       <c r="A12" s="4" t="s">
         <v>626</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>551</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="D12" s="4" t="s">
         <v>504</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="E12" s="5" t="s">
         <v>551</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>504</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>627</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="4" t="s">
+        <v>540</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>367</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="D13" s="4" t="s">
         <v>540</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="E13" s="5" t="s">
         <v>367</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>540</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>628</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="4" t="s">
         <v>490</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="4" t="s">
         <v>490</v>
       </c>
       <c r="E14" s="5" t="s">
@@ -34105,13 +34111,13 @@
       <c r="A15" s="4" t="s">
         <v>629</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="4" t="s">
         <v>377</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="4" t="s">
         <v>377</v>
       </c>
       <c r="E15" s="5" t="s">
@@ -34122,30 +34128,30 @@
       <c r="A16" s="4" t="s">
         <v>630</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="4" t="s">
+        <v>519</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="D16" s="4" t="s">
         <v>519</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="E16" s="5" t="s">
         <v>241</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>631</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="4" t="s">
         <v>258</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="4" t="s">
         <v>258</v>
       </c>
       <c r="E17" s="5" t="s">
@@ -34156,47 +34162,47 @@
       <c r="A18" s="4" t="s">
         <v>632</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>553</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="D18" s="4" t="s">
         <v>529</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="E18" s="5" t="s">
         <v>553</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>529</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>633</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="4" t="s">
+        <v>548</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>472</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="D19" s="4" t="s">
         <v>548</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="E19" s="5" t="s">
         <v>472</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>634</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="4" t="s">
         <v>473</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>441</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="4" t="s">
         <v>473</v>
       </c>
       <c r="E20" s="5" t="s">
@@ -34207,30 +34213,30 @@
       <c r="A21" s="4" t="s">
         <v>635</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="4" t="s">
+        <v>468</v>
+      </c>
+      <c r="C21" s="5" t="s">
         <v>502</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="D21" s="4" t="s">
         <v>468</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="E21" s="5" t="s">
         <v>502</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>636</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="4" t="s">
         <v>637</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>268</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D22" s="4" t="s">
         <v>637</v>
       </c>
       <c r="E22" s="5" t="s">
@@ -34241,30 +34247,30 @@
       <c r="A23" s="4" t="s">
         <v>638</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="C23" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="D23" s="4" t="s">
         <v>494</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="E23" s="5" t="s">
         <v>170</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>639</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="4" t="s">
         <v>541</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>266</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="D24" s="4" t="s">
         <v>541</v>
       </c>
       <c r="E24" s="5" t="s">
@@ -34275,30 +34281,30 @@
       <c r="A25" s="4" t="s">
         <v>640</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="C25" s="5" t="s">
         <v>398</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="D25" s="4" t="s">
         <v>499</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="E25" s="5" t="s">
         <v>398</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>641</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="4" t="s">
         <v>577</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>570</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="D26" s="4" t="s">
         <v>577</v>
       </c>
       <c r="E26" s="5" t="s">
@@ -34309,13 +34315,13 @@
       <c r="A27" s="4" t="s">
         <v>642</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="4" t="s">
         <v>343</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>444</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="D27" s="4" t="s">
         <v>343</v>
       </c>
       <c r="E27" s="5" t="s">
@@ -34326,13 +34332,13 @@
       <c r="A28" s="4" t="s">
         <v>643</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="4" t="s">
         <v>359</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="D28" s="4" t="s">
         <v>359</v>
       </c>
       <c r="E28" s="5" t="s">
@@ -34343,81 +34349,81 @@
       <c r="A29" s="4" t="s">
         <v>644</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="C29" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="D29" s="4" t="s">
         <v>516</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="E29" s="5" t="s">
         <v>165</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>516</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>645</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C30" s="5" t="s">
         <v>501</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="D30" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D30" s="5" t="s">
+      <c r="E30" s="5" t="s">
         <v>501</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>646</v>
       </c>
-      <c r="B31" s="5" t="s">
+      <c r="B31" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="C31" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="D31" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="D31" s="5" t="s">
+      <c r="E31" s="5" t="s">
         <v>19</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
         <v>647</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B32" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="C32" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="D32" s="4" t="s">
         <v>476</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="E32" s="5" t="s">
         <v>175</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>476</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>648</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="4" t="s">
         <v>387</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>432</v>
       </c>
-      <c r="D33" s="5" t="s">
+      <c r="D33" s="4" t="s">
         <v>387</v>
       </c>
       <c r="E33" s="5" t="s">
@@ -34428,30 +34434,30 @@
       <c r="A34" s="4" t="s">
         <v>649</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B34" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="C34" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="D34" s="4" t="s">
         <v>424</v>
       </c>
-      <c r="D34" s="5" t="s">
+      <c r="E34" s="5" t="s">
         <v>8</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>650</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="4" t="s">
         <v>482</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="D35" s="5" t="s">
+      <c r="D35" s="4" t="s">
         <v>482</v>
       </c>
       <c r="E35" s="5" t="s">
@@ -34462,47 +34468,47 @@
       <c r="A36" s="4" t="s">
         <v>651</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B36" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="C36" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="D36" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="D36" s="5" t="s">
+      <c r="E36" s="5" t="s">
         <v>189</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>652</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B37" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="C37" s="5" t="s">
         <v>538</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="D37" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="D37" s="5" t="s">
+      <c r="E37" s="5" t="s">
         <v>538</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>653</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="B38" s="4" t="s">
         <v>137</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>379</v>
       </c>
-      <c r="D38" s="5" t="s">
+      <c r="D38" s="4" t="s">
         <v>137</v>
       </c>
       <c r="E38" s="5" t="s">
@@ -34513,13 +34519,13 @@
       <c r="A39" s="4" t="s">
         <v>654</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="B39" s="4" t="s">
         <v>422</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>510</v>
       </c>
-      <c r="D39" s="5" t="s">
+      <c r="D39" s="4" t="s">
         <v>422</v>
       </c>
       <c r="E39" s="5" t="s">
@@ -34530,30 +34536,30 @@
       <c r="A40" s="4" t="s">
         <v>655</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B40" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="C40" s="5" t="s">
         <v>543</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="D40" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="D40" s="5" t="s">
+      <c r="E40" s="5" t="s">
         <v>543</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>542</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
         <v>656</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="B41" s="4" t="s">
         <v>150</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="D41" s="5" t="s">
+      <c r="D41" s="4" t="s">
         <v>150</v>
       </c>
       <c r="E41" s="5" t="s">

--- a/tiers_gen9nationaldexdoubles.xlsx
+++ b/tiers_gen9nationaldexdoubles.xlsx
@@ -8,15 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\power bi\webhook\Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A986137A-4586-4B31-A040-075B7F8441A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62C9E5B5-35E4-48C2-B7DD-AF56FF9AB1F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pokemon" sheetId="1" r:id="rId1"/>
     <sheet name="Equipos" sheetId="2" r:id="rId2"/>
     <sheet name="Teams" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Pokemon!$A$1:$H$1051</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -2453,6 +2456,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:H1051"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2492,7 +2496,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -2518,7 +2522,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -2544,7 +2548,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -2570,7 +2574,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -2596,7 +2600,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -2622,7 +2626,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -2648,7 +2652,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -2674,7 +2678,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -2700,7 +2704,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -2726,7 +2730,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -2752,7 +2756,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -2778,7 +2782,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -2804,7 +2808,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -2830,7 +2834,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>26</v>
       </c>
@@ -2856,7 +2860,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>26</v>
       </c>
@@ -2882,7 +2886,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -2908,7 +2912,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>26</v>
       </c>
@@ -2934,7 +2938,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>26</v>
       </c>
@@ -2960,7 +2964,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -2986,7 +2990,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>33</v>
       </c>
@@ -3012,7 +3016,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>33</v>
       </c>
@@ -3038,7 +3042,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>33</v>
       </c>
@@ -3064,7 +3068,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>33</v>
       </c>
@@ -3090,7 +3094,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>33</v>
       </c>
@@ -3116,7 +3120,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>39</v>
       </c>
@@ -3142,7 +3146,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>39</v>
       </c>
@@ -3168,7 +3172,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>39</v>
       </c>
@@ -3194,7 +3198,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>39</v>
       </c>
@@ -3220,7 +3224,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>39</v>
       </c>
@@ -3246,7 +3250,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>39</v>
       </c>
@@ -3272,7 +3276,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>46</v>
       </c>
@@ -3298,7 +3302,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>46</v>
       </c>
@@ -3324,7 +3328,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>46</v>
       </c>
@@ -3350,7 +3354,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>46</v>
       </c>
@@ -3376,7 +3380,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>46</v>
       </c>
@@ -3402,7 +3406,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>46</v>
       </c>
@@ -3428,7 +3432,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>51</v>
       </c>
@@ -3454,7 +3458,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>51</v>
       </c>
@@ -3480,7 +3484,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>51</v>
       </c>
@@ -3506,7 +3510,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>51</v>
       </c>
@@ -3532,7 +3536,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>51</v>
       </c>
@@ -3558,7 +3562,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>51</v>
       </c>
@@ -3584,7 +3588,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>56</v>
       </c>
@@ -3610,7 +3614,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>56</v>
       </c>
@@ -3636,7 +3640,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>56</v>
       </c>
@@ -3662,7 +3666,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>56</v>
       </c>
@@ -3688,7 +3692,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>56</v>
       </c>
@@ -3714,7 +3718,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>56</v>
       </c>
@@ -3740,7 +3744,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>63</v>
       </c>
@@ -3766,7 +3770,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>63</v>
       </c>
@@ -3792,7 +3796,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>63</v>
       </c>
@@ -3818,7 +3822,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>63</v>
       </c>
@@ -3844,7 +3848,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>63</v>
       </c>
@@ -3870,7 +3874,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>63</v>
       </c>
@@ -3896,7 +3900,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>69</v>
       </c>
@@ -3922,7 +3926,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>69</v>
       </c>
@@ -3948,7 +3952,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>69</v>
       </c>
@@ -3974,7 +3978,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>69</v>
       </c>
@@ -4000,7 +4004,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>69</v>
       </c>
@@ -4026,7 +4030,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>69</v>
       </c>
@@ -4052,7 +4056,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>74</v>
       </c>
@@ -4078,7 +4082,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>74</v>
       </c>
@@ -4104,7 +4108,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>74</v>
       </c>
@@ -4130,7 +4134,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>74</v>
       </c>
@@ -4156,7 +4160,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>74</v>
       </c>
@@ -4182,7 +4186,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>74</v>
       </c>
@@ -4208,7 +4212,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>81</v>
       </c>
@@ -4234,7 +4238,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>81</v>
       </c>
@@ -4260,7 +4264,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>81</v>
       </c>
@@ -4286,7 +4290,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>81</v>
       </c>
@@ -4312,7 +4316,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>81</v>
       </c>
@@ -4338,7 +4342,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>81</v>
       </c>
@@ -4364,7 +4368,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>87</v>
       </c>
@@ -4390,7 +4394,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>87</v>
       </c>
@@ -4416,7 +4420,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>87</v>
       </c>
@@ -4442,7 +4446,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>87</v>
       </c>
@@ -4468,7 +4472,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>87</v>
       </c>
@@ -4494,7 +4498,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>87</v>
       </c>
@@ -4520,7 +4524,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>92</v>
       </c>
@@ -4546,7 +4550,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>92</v>
       </c>
@@ -4572,7 +4576,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>92</v>
       </c>
@@ -4598,7 +4602,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>92</v>
       </c>
@@ -4624,7 +4628,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>92</v>
       </c>
@@ -4650,7 +4654,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>92</v>
       </c>
@@ -4676,7 +4680,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>99</v>
       </c>
@@ -4702,7 +4706,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>99</v>
       </c>
@@ -4728,7 +4732,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>99</v>
       </c>
@@ -4754,7 +4758,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>99</v>
       </c>
@@ -4780,7 +4784,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>99</v>
       </c>
@@ -4806,7 +4810,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>99</v>
       </c>
@@ -4832,7 +4836,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>104</v>
       </c>
@@ -4858,7 +4862,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>104</v>
       </c>
@@ -4884,7 +4888,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>104</v>
       </c>
@@ -4910,7 +4914,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>104</v>
       </c>
@@ -4936,7 +4940,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>104</v>
       </c>
@@ -4962,7 +4966,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>104</v>
       </c>
@@ -4988,7 +4992,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>107</v>
       </c>
@@ -5014,7 +5018,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>107</v>
       </c>
@@ -5040,7 +5044,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>107</v>
       </c>
@@ -5066,7 +5070,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>107</v>
       </c>
@@ -5092,7 +5096,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>107</v>
       </c>
@@ -5118,7 +5122,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>107</v>
       </c>
@@ -5144,7 +5148,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>114</v>
       </c>
@@ -5170,7 +5174,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>114</v>
       </c>
@@ -5196,7 +5200,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>114</v>
       </c>
@@ -5222,7 +5226,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>114</v>
       </c>
@@ -5248,7 +5252,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>114</v>
       </c>
@@ -5274,7 +5278,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>114</v>
       </c>
@@ -5300,7 +5304,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>120</v>
       </c>
@@ -5326,7 +5330,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>120</v>
       </c>
@@ -5352,7 +5356,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>120</v>
       </c>
@@ -5378,7 +5382,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>120</v>
       </c>
@@ -5404,7 +5408,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>120</v>
       </c>
@@ -5430,7 +5434,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>120</v>
       </c>
@@ -5456,7 +5460,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>126</v>
       </c>
@@ -5482,7 +5486,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>126</v>
       </c>
@@ -5508,7 +5512,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>126</v>
       </c>
@@ -5534,7 +5538,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>126</v>
       </c>
@@ -5560,7 +5564,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>126</v>
       </c>
@@ -5586,7 +5590,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>126</v>
       </c>
@@ -5612,7 +5616,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>132</v>
       </c>
@@ -5638,7 +5642,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>132</v>
       </c>
@@ -5664,7 +5668,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>132</v>
       </c>
@@ -5690,7 +5694,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>132</v>
       </c>
@@ -5716,7 +5720,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>132</v>
       </c>
@@ -5742,7 +5746,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>132</v>
       </c>
@@ -5768,7 +5772,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>137</v>
       </c>
@@ -5794,7 +5798,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>137</v>
       </c>
@@ -5820,7 +5824,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>137</v>
       </c>
@@ -5846,7 +5850,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>137</v>
       </c>
@@ -5872,7 +5876,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>137</v>
       </c>
@@ -5898,7 +5902,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>137</v>
       </c>
@@ -5924,7 +5928,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>140</v>
       </c>
@@ -5950,7 +5954,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>140</v>
       </c>
@@ -5976,7 +5980,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>140</v>
       </c>
@@ -6002,7 +6006,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>140</v>
       </c>
@@ -6028,7 +6032,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>140</v>
       </c>
@@ -6080,7 +6084,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>146</v>
       </c>
@@ -6106,7 +6110,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>146</v>
       </c>
@@ -6132,7 +6136,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>146</v>
       </c>
@@ -6158,7 +6162,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>146</v>
       </c>
@@ -6184,7 +6188,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>146</v>
       </c>
@@ -6236,7 +6240,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>150</v>
       </c>
@@ -6262,7 +6266,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>150</v>
       </c>
@@ -6288,7 +6292,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>150</v>
       </c>
@@ -6314,7 +6318,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>150</v>
       </c>
@@ -6340,7 +6344,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>150</v>
       </c>
@@ -6366,7 +6370,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>150</v>
       </c>
@@ -6392,7 +6396,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>152</v>
       </c>
@@ -6418,7 +6422,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>152</v>
       </c>
@@ -6444,7 +6448,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>152</v>
       </c>
@@ -6470,7 +6474,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>152</v>
       </c>
@@ -6496,7 +6500,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>152</v>
       </c>
@@ -6522,7 +6526,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>152</v>
       </c>
@@ -6548,7 +6552,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>156</v>
       </c>
@@ -6574,7 +6578,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>156</v>
       </c>
@@ -6600,7 +6604,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>156</v>
       </c>
@@ -6626,7 +6630,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>156</v>
       </c>
@@ -6652,7 +6656,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>156</v>
       </c>
@@ -6678,7 +6682,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>156</v>
       </c>
@@ -6704,7 +6708,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>158</v>
       </c>
@@ -6730,7 +6734,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>158</v>
       </c>
@@ -6756,7 +6760,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>158</v>
       </c>
@@ -6782,7 +6786,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>158</v>
       </c>
@@ -6808,7 +6812,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>158</v>
       </c>
@@ -6834,7 +6838,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>158</v>
       </c>
@@ -6860,7 +6864,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>160</v>
       </c>
@@ -6886,7 +6890,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>160</v>
       </c>
@@ -6912,7 +6916,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>160</v>
       </c>
@@ -6938,7 +6942,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>160</v>
       </c>
@@ -6964,7 +6968,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>160</v>
       </c>
@@ -6990,7 +6994,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>160</v>
       </c>
@@ -7016,7 +7020,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>165</v>
       </c>
@@ -7042,7 +7046,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>165</v>
       </c>
@@ -7068,7 +7072,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>165</v>
       </c>
@@ -7094,7 +7098,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>165</v>
       </c>
@@ -7120,7 +7124,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>165</v>
       </c>
@@ -7146,7 +7150,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>165</v>
       </c>
@@ -7172,7 +7176,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>170</v>
       </c>
@@ -7198,7 +7202,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>170</v>
       </c>
@@ -7224,7 +7228,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>170</v>
       </c>
@@ -7250,7 +7254,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>170</v>
       </c>
@@ -7276,7 +7280,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>170</v>
       </c>
@@ -7302,7 +7306,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>170</v>
       </c>
@@ -7328,7 +7332,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>175</v>
       </c>
@@ -7354,7 +7358,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>175</v>
       </c>
@@ -7380,7 +7384,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>175</v>
       </c>
@@ -7406,7 +7410,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>175</v>
       </c>
@@ -7432,7 +7436,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>175</v>
       </c>
@@ -7458,7 +7462,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>175</v>
       </c>
@@ -7484,7 +7488,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>182</v>
       </c>
@@ -7510,7 +7514,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>182</v>
       </c>
@@ -7536,7 +7540,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>182</v>
       </c>
@@ -7562,7 +7566,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>182</v>
       </c>
@@ -7588,7 +7592,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>182</v>
       </c>
@@ -7614,7 +7618,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>182</v>
       </c>
@@ -7640,7 +7644,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>186</v>
       </c>
@@ -7666,7 +7670,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>186</v>
       </c>
@@ -7692,7 +7696,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>186</v>
       </c>
@@ -7718,7 +7722,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>186</v>
       </c>
@@ -7744,7 +7748,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>186</v>
       </c>
@@ -7770,7 +7774,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>186</v>
       </c>
@@ -7796,7 +7800,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>187</v>
       </c>
@@ -7822,7 +7826,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>187</v>
       </c>
@@ -7848,7 +7852,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>187</v>
       </c>
@@ -7874,7 +7878,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>187</v>
       </c>
@@ -7900,7 +7904,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>187</v>
       </c>
@@ -7926,7 +7930,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>187</v>
       </c>
@@ -7952,7 +7956,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>188</v>
       </c>
@@ -7978,7 +7982,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>188</v>
       </c>
@@ -8004,7 +8008,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>188</v>
       </c>
@@ -8030,7 +8034,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>188</v>
       </c>
@@ -8056,7 +8060,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>188</v>
       </c>
@@ -8082,7 +8086,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>188</v>
       </c>
@@ -8108,7 +8112,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>189</v>
       </c>
@@ -8134,7 +8138,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>189</v>
       </c>
@@ -8160,7 +8164,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>189</v>
       </c>
@@ -8186,7 +8190,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>189</v>
       </c>
@@ -8212,7 +8216,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>189</v>
       </c>
@@ -8238,7 +8242,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>189</v>
       </c>
@@ -8264,7 +8268,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>191</v>
       </c>
@@ -8290,7 +8294,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>191</v>
       </c>
@@ -8316,7 +8320,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>191</v>
       </c>
@@ -8342,7 +8346,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>191</v>
       </c>
@@ -8368,7 +8372,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>191</v>
       </c>
@@ -8394,7 +8398,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>191</v>
       </c>
@@ -8420,7 +8424,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>192</v>
       </c>
@@ -8446,7 +8450,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>192</v>
       </c>
@@ -8472,7 +8476,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>192</v>
       </c>
@@ -8498,7 +8502,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>192</v>
       </c>
@@ -8524,7 +8528,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>192</v>
       </c>
@@ -8550,7 +8554,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>192</v>
       </c>
@@ -8576,7 +8580,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>196</v>
       </c>
@@ -8602,7 +8606,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>196</v>
       </c>
@@ -8628,7 +8632,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>196</v>
       </c>
@@ -8654,7 +8658,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>196</v>
       </c>
@@ -8680,7 +8684,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>196</v>
       </c>
@@ -8706,7 +8710,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>196</v>
       </c>
@@ -8732,7 +8736,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>198</v>
       </c>
@@ -8758,7 +8762,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>198</v>
       </c>
@@ -8784,7 +8788,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>198</v>
       </c>
@@ -8810,7 +8814,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>198</v>
       </c>
@@ -8836,7 +8840,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>198</v>
       </c>
@@ -8862,7 +8866,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>198</v>
       </c>
@@ -8888,7 +8892,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>199</v>
       </c>
@@ -8914,7 +8918,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>199</v>
       </c>
@@ -8940,7 +8944,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>199</v>
       </c>
@@ -8966,7 +8970,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>199</v>
       </c>
@@ -8992,7 +8996,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>199</v>
       </c>
@@ -9018,7 +9022,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>199</v>
       </c>
@@ -9044,7 +9048,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>200</v>
       </c>
@@ -9070,7 +9074,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>200</v>
       </c>
@@ -9096,7 +9100,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>200</v>
       </c>
@@ -9122,7 +9126,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>200</v>
       </c>
@@ -9148,7 +9152,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>200</v>
       </c>
@@ -9174,7 +9178,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>200</v>
       </c>
@@ -9200,7 +9204,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>204</v>
       </c>
@@ -9226,7 +9230,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>204</v>
       </c>
@@ -9252,7 +9256,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>204</v>
       </c>
@@ -9278,7 +9282,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>204</v>
       </c>
@@ -9304,7 +9308,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>204</v>
       </c>
@@ -9330,7 +9334,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>204</v>
       </c>
@@ -9356,7 +9360,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>209</v>
       </c>
@@ -9382,7 +9386,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>209</v>
       </c>
@@ -9408,7 +9412,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>209</v>
       </c>
@@ -9434,7 +9438,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>209</v>
       </c>
@@ -9460,7 +9464,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>209</v>
       </c>
@@ -9486,7 +9490,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>209</v>
       </c>
@@ -9512,7 +9516,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>212</v>
       </c>
@@ -9538,7 +9542,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="273" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>212</v>
       </c>
@@ -9564,7 +9568,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="274" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>212</v>
       </c>
@@ -9590,7 +9594,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="275" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>212</v>
       </c>
@@ -9616,7 +9620,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="276" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>212</v>
       </c>
@@ -9642,7 +9646,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="277" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>212</v>
       </c>
@@ -9668,7 +9672,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="278" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>216</v>
       </c>
@@ -9694,7 +9698,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="279" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>216</v>
       </c>
@@ -9720,7 +9724,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="280" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>216</v>
       </c>
@@ -9746,7 +9750,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="281" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>216</v>
       </c>
@@ -9772,7 +9776,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="282" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>216</v>
       </c>
@@ -9798,7 +9802,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="283" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>216</v>
       </c>
@@ -9824,7 +9828,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="284" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>221</v>
       </c>
@@ -9850,7 +9854,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="285" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>221</v>
       </c>
@@ -9876,7 +9880,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="286" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>221</v>
       </c>
@@ -9902,7 +9906,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="287" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>221</v>
       </c>
@@ -9928,7 +9932,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="288" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>221</v>
       </c>
@@ -9954,7 +9958,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="289" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>221</v>
       </c>
@@ -9980,7 +9984,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="290" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>224</v>
       </c>
@@ -10006,7 +10010,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="291" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>224</v>
       </c>
@@ -10032,7 +10036,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="292" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>224</v>
       </c>
@@ -10058,7 +10062,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="293" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>224</v>
       </c>
@@ -10084,7 +10088,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="294" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>224</v>
       </c>
@@ -10110,7 +10114,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="295" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>224</v>
       </c>
@@ -10136,7 +10140,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="296" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>228</v>
       </c>
@@ -10162,7 +10166,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="297" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>228</v>
       </c>
@@ -10188,7 +10192,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="298" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>228</v>
       </c>
@@ -10214,7 +10218,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="299" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>228</v>
       </c>
@@ -10240,7 +10244,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="300" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>228</v>
       </c>
@@ -10266,7 +10270,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="301" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>228</v>
       </c>
@@ -10292,7 +10296,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="302" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>232</v>
       </c>
@@ -10318,7 +10322,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="303" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>232</v>
       </c>
@@ -10344,7 +10348,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="304" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>232</v>
       </c>
@@ -10370,7 +10374,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="305" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>232</v>
       </c>
@@ -10396,7 +10400,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="306" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>232</v>
       </c>
@@ -10422,7 +10426,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="307" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>232</v>
       </c>
@@ -10448,7 +10452,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="308" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>236</v>
       </c>
@@ -10474,7 +10478,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="309" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>236</v>
       </c>
@@ -10500,7 +10504,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="310" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>236</v>
       </c>
@@ -10526,7 +10530,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="311" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>236</v>
       </c>
@@ -10552,7 +10556,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="312" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>236</v>
       </c>
@@ -10578,7 +10582,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="313" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>236</v>
       </c>
@@ -10604,7 +10608,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="314" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>241</v>
       </c>
@@ -10630,7 +10634,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="315" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>241</v>
       </c>
@@ -10656,7 +10660,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="316" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>241</v>
       </c>
@@ -10682,7 +10686,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="317" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>241</v>
       </c>
@@ -10708,7 +10712,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="318" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>241</v>
       </c>
@@ -10734,7 +10738,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="319" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>241</v>
       </c>
@@ -10760,7 +10764,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="320" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>246</v>
       </c>
@@ -10786,7 +10790,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="321" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>246</v>
       </c>
@@ -10812,7 +10816,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="322" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>246</v>
       </c>
@@ -10838,7 +10842,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="323" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>246</v>
       </c>
@@ -10864,7 +10868,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="324" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>246</v>
       </c>
@@ -10890,7 +10894,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="325" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>246</v>
       </c>
@@ -10916,7 +10920,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="326" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>250</v>
       </c>
@@ -10942,7 +10946,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="327" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>250</v>
       </c>
@@ -10968,7 +10972,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="328" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>250</v>
       </c>
@@ -10994,7 +10998,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="329" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>250</v>
       </c>
@@ -11020,7 +11024,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="330" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>250</v>
       </c>
@@ -11046,7 +11050,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="331" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>250</v>
       </c>
@@ -11072,7 +11076,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="332" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>255</v>
       </c>
@@ -11098,7 +11102,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="333" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>255</v>
       </c>
@@ -11124,7 +11128,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="334" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>255</v>
       </c>
@@ -11150,7 +11154,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="335" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>255</v>
       </c>
@@ -11176,7 +11180,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="336" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>255</v>
       </c>
@@ -11202,7 +11206,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="337" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>255</v>
       </c>
@@ -11228,7 +11232,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="338" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>258</v>
       </c>
@@ -11254,7 +11258,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="339" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>258</v>
       </c>
@@ -11280,7 +11284,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="340" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>258</v>
       </c>
@@ -11306,7 +11310,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="341" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>258</v>
       </c>
@@ -11332,7 +11336,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="342" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>258</v>
       </c>
@@ -11358,7 +11362,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="343" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>258</v>
       </c>
@@ -11384,7 +11388,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="344" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>262</v>
       </c>
@@ -11410,7 +11414,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="345" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>262</v>
       </c>
@@ -11436,7 +11440,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="346" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>262</v>
       </c>
@@ -11462,7 +11466,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="347" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>262</v>
       </c>
@@ -11488,7 +11492,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="348" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>262</v>
       </c>
@@ -11514,7 +11518,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="349" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>262</v>
       </c>
@@ -11540,7 +11544,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="350" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>266</v>
       </c>
@@ -11566,7 +11570,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="351" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>266</v>
       </c>
@@ -11592,7 +11596,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="352" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>266</v>
       </c>
@@ -11618,7 +11622,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="353" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>266</v>
       </c>
@@ -11644,7 +11648,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="354" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>266</v>
       </c>
@@ -11670,7 +11674,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="355" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>266</v>
       </c>
@@ -11696,7 +11700,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="356" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>268</v>
       </c>
@@ -11722,7 +11726,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="357" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>268</v>
       </c>
@@ -11748,7 +11752,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="358" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>268</v>
       </c>
@@ -11774,7 +11778,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="359" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>268</v>
       </c>
@@ -11800,7 +11804,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="360" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>268</v>
       </c>
@@ -11826,7 +11830,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="361" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>268</v>
       </c>
@@ -11852,7 +11856,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="362" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>271</v>
       </c>
@@ -11878,7 +11882,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="363" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>271</v>
       </c>
@@ -11904,7 +11908,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="364" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>271</v>
       </c>
@@ -11930,7 +11934,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="365" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>271</v>
       </c>
@@ -11956,7 +11960,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="366" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>271</v>
       </c>
@@ -11982,7 +11986,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="367" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>271</v>
       </c>
@@ -12008,7 +12012,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="368" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>276</v>
       </c>
@@ -12034,7 +12038,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="369" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>276</v>
       </c>
@@ -12060,7 +12064,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="370" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>276</v>
       </c>
@@ -12086,7 +12090,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="371" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>276</v>
       </c>
@@ -12112,7 +12116,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="372" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>276</v>
       </c>
@@ -12138,7 +12142,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="373" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>276</v>
       </c>
@@ -12164,7 +12168,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="374" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>280</v>
       </c>
@@ -12190,7 +12194,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="375" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>280</v>
       </c>
@@ -12216,7 +12220,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="376" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>280</v>
       </c>
@@ -12242,7 +12246,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="377" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>280</v>
       </c>
@@ -12268,7 +12272,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="378" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>280</v>
       </c>
@@ -12294,7 +12298,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="379" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>280</v>
       </c>
@@ -12320,7 +12324,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="380" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>283</v>
       </c>
@@ -12346,7 +12350,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="381" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>283</v>
       </c>
@@ -12372,7 +12376,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="382" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>283</v>
       </c>
@@ -12398,7 +12402,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="383" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>283</v>
       </c>
@@ -12424,7 +12428,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="384" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>283</v>
       </c>
@@ -12450,7 +12454,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="385" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>283</v>
       </c>
@@ -12476,7 +12480,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="386" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>286</v>
       </c>
@@ -12502,7 +12506,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="387" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>286</v>
       </c>
@@ -12528,7 +12532,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="388" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>286</v>
       </c>
@@ -12554,7 +12558,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="389" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>286</v>
       </c>
@@ -12580,7 +12584,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="390" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>286</v>
       </c>
@@ -12606,7 +12610,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="391" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>286</v>
       </c>
@@ -12632,7 +12636,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="392" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>292</v>
       </c>
@@ -12658,7 +12662,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="393" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>292</v>
       </c>
@@ -12684,7 +12688,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="394" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>292</v>
       </c>
@@ -12710,7 +12714,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="395" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>292</v>
       </c>
@@ -12736,7 +12740,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="396" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>292</v>
       </c>
@@ -12762,7 +12766,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="397" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>292</v>
       </c>
@@ -12788,7 +12792,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="398" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>296</v>
       </c>
@@ -12814,7 +12818,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="399" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>296</v>
       </c>
@@ -12840,7 +12844,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="400" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>296</v>
       </c>
@@ -12866,7 +12870,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="401" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>296</v>
       </c>
@@ -12892,7 +12896,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="402" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>296</v>
       </c>
@@ -12918,7 +12922,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="403" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>296</v>
       </c>
@@ -12944,7 +12948,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="404" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>298</v>
       </c>
@@ -12970,7 +12974,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="405" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>298</v>
       </c>
@@ -12996,7 +13000,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="406" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>298</v>
       </c>
@@ -13022,7 +13026,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="407" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>298</v>
       </c>
@@ -13048,7 +13052,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="408" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>298</v>
       </c>
@@ -13074,7 +13078,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="409" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>298</v>
       </c>
@@ -13100,7 +13104,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="410" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>304</v>
       </c>
@@ -13126,7 +13130,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="411" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>304</v>
       </c>
@@ -13152,7 +13156,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="412" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>304</v>
       </c>
@@ -13178,7 +13182,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="413" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>304</v>
       </c>
@@ -13204,7 +13208,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="414" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>304</v>
       </c>
@@ -13230,7 +13234,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="415" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>304</v>
       </c>
@@ -13256,7 +13260,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="416" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>309</v>
       </c>
@@ -13282,7 +13286,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="417" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>309</v>
       </c>
@@ -13308,7 +13312,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="418" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>309</v>
       </c>
@@ -13334,7 +13338,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="419" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>309</v>
       </c>
@@ -13360,7 +13364,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="420" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>309</v>
       </c>
@@ -13386,7 +13390,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="421" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>309</v>
       </c>
@@ -13412,7 +13416,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="422" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>313</v>
       </c>
@@ -13438,7 +13442,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="423" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>313</v>
       </c>
@@ -13464,7 +13468,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="424" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>313</v>
       </c>
@@ -13490,7 +13494,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="425" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>313</v>
       </c>
@@ -13516,7 +13520,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="426" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>313</v>
       </c>
@@ -13542,7 +13546,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="427" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>313</v>
       </c>
@@ -13568,7 +13572,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="428" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>317</v>
       </c>
@@ -13594,7 +13598,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="429" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>317</v>
       </c>
@@ -13620,7 +13624,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="430" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>317</v>
       </c>
@@ -13646,7 +13650,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="431" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>317</v>
       </c>
@@ -13672,7 +13676,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="432" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>317</v>
       </c>
@@ -13698,7 +13702,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="433" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>317</v>
       </c>
@@ -13724,7 +13728,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="434" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>320</v>
       </c>
@@ -13750,7 +13754,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="435" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>320</v>
       </c>
@@ -13776,7 +13780,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="436" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>320</v>
       </c>
@@ -13802,7 +13806,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="437" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>320</v>
       </c>
@@ -13828,7 +13832,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="438" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>320</v>
       </c>
@@ -13854,7 +13858,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="439" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>320</v>
       </c>
@@ -13880,7 +13884,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="440" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>323</v>
       </c>
@@ -13906,7 +13910,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="441" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>323</v>
       </c>
@@ -13932,7 +13936,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="442" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>323</v>
       </c>
@@ -13958,7 +13962,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="443" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>323</v>
       </c>
@@ -13984,7 +13988,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="444" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>323</v>
       </c>
@@ -14010,7 +14014,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="445" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>323</v>
       </c>
@@ -14036,7 +14040,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="446" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>325</v>
       </c>
@@ -14062,7 +14066,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="447" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>325</v>
       </c>
@@ -14088,7 +14092,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="448" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>325</v>
       </c>
@@ -14114,7 +14118,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="449" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>325</v>
       </c>
@@ -14140,7 +14144,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="450" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>325</v>
       </c>
@@ -14166,7 +14170,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="451" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>325</v>
       </c>
@@ -14192,7 +14196,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="452" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>327</v>
       </c>
@@ -14218,7 +14222,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="453" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>327</v>
       </c>
@@ -14244,7 +14248,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="454" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>327</v>
       </c>
@@ -14270,7 +14274,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="455" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>327</v>
       </c>
@@ -14296,7 +14300,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="456" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>327</v>
       </c>
@@ -14322,7 +14326,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="457" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>327</v>
       </c>
@@ -14348,7 +14352,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="458" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>328</v>
       </c>
@@ -14374,7 +14378,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="459" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>328</v>
       </c>
@@ -14400,7 +14404,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="460" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>328</v>
       </c>
@@ -14426,7 +14430,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="461" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>328</v>
       </c>
@@ -14452,7 +14456,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="462" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>328</v>
       </c>
@@ -14478,7 +14482,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="463" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>328</v>
       </c>
@@ -14504,7 +14508,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="464" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>333</v>
       </c>
@@ -14530,7 +14534,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="465" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>333</v>
       </c>
@@ -14556,7 +14560,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="466" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>333</v>
       </c>
@@ -14582,7 +14586,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="467" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>333</v>
       </c>
@@ -14608,7 +14612,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="468" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>333</v>
       </c>
@@ -14634,7 +14638,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="469" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>333</v>
       </c>
@@ -14660,7 +14664,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="470" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>336</v>
       </c>
@@ -14686,7 +14690,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="471" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>336</v>
       </c>
@@ -14712,7 +14716,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="472" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>336</v>
       </c>
@@ -14738,7 +14742,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="473" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>336</v>
       </c>
@@ -14764,7 +14768,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="474" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>336</v>
       </c>
@@ -14790,7 +14794,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="475" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>336</v>
       </c>
@@ -14816,7 +14820,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="476" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>339</v>
       </c>
@@ -14842,7 +14846,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="477" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>339</v>
       </c>
@@ -14868,7 +14872,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="478" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>339</v>
       </c>
@@ -14894,7 +14898,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="479" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>339</v>
       </c>
@@ -14920,7 +14924,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="480" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>339</v>
       </c>
@@ -14946,7 +14950,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="481" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>339</v>
       </c>
@@ -14972,7 +14976,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="482" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>343</v>
       </c>
@@ -14998,7 +15002,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="483" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
         <v>343</v>
       </c>
@@ -15024,7 +15028,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="484" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
         <v>343</v>
       </c>
@@ -15050,7 +15054,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="485" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
         <v>343</v>
       </c>
@@ -15076,7 +15080,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="486" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
         <v>343</v>
       </c>
@@ -15102,7 +15106,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="487" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
         <v>343</v>
       </c>
@@ -15128,7 +15132,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="488" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
         <v>347</v>
       </c>
@@ -15154,7 +15158,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="489" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
         <v>347</v>
       </c>
@@ -15180,7 +15184,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="490" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
         <v>347</v>
       </c>
@@ -15206,7 +15210,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="491" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
         <v>347</v>
       </c>
@@ -15232,7 +15236,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="492" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
         <v>347</v>
       </c>
@@ -15258,7 +15262,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="493" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
         <v>347</v>
       </c>
@@ -15284,7 +15288,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="494" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
         <v>351</v>
       </c>
@@ -15310,7 +15314,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="495" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
         <v>351</v>
       </c>
@@ -15336,7 +15340,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="496" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
         <v>351</v>
       </c>
@@ -15362,7 +15366,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="497" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
         <v>351</v>
       </c>
@@ -15388,7 +15392,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="498" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
         <v>351</v>
       </c>
@@ -15414,7 +15418,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="499" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
         <v>351</v>
       </c>
@@ -15440,7 +15444,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="500" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>352</v>
       </c>
@@ -15466,7 +15470,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="501" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
         <v>352</v>
       </c>
@@ -15492,7 +15496,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="502" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
         <v>352</v>
       </c>
@@ -15518,7 +15522,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="503" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
         <v>352</v>
       </c>
@@ -15544,7 +15548,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="504" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
         <v>352</v>
       </c>
@@ -15570,7 +15574,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="505" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
         <v>352</v>
       </c>
@@ -15596,7 +15600,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="506" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
         <v>355</v>
       </c>
@@ -15622,7 +15626,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="507" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
         <v>355</v>
       </c>
@@ -15648,7 +15652,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="508" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
         <v>355</v>
       </c>
@@ -15674,7 +15678,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="509" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
         <v>355</v>
       </c>
@@ -15700,7 +15704,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="510" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
         <v>355</v>
       </c>
@@ -15726,7 +15730,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="511" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
         <v>355</v>
       </c>
@@ -15752,7 +15756,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="512" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
         <v>357</v>
       </c>
@@ -15778,7 +15782,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="513" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
         <v>357</v>
       </c>
@@ -15804,7 +15808,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="514" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
         <v>357</v>
       </c>
@@ -15830,7 +15834,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="515" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
         <v>357</v>
       </c>
@@ -15856,7 +15860,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="516" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
         <v>357</v>
       </c>
@@ -15882,7 +15886,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="517" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
         <v>357</v>
       </c>
@@ -15908,7 +15912,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="518" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
         <v>359</v>
       </c>
@@ -15934,7 +15938,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="519" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
         <v>359</v>
       </c>
@@ -15960,7 +15964,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="520" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
         <v>359</v>
       </c>
@@ -15986,7 +15990,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="521" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
         <v>359</v>
       </c>
@@ -16012,7 +16016,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="522" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
         <v>359</v>
       </c>
@@ -16038,7 +16042,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="523" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
         <v>359</v>
       </c>
@@ -16064,7 +16068,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="524" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
         <v>361</v>
       </c>
@@ -16090,7 +16094,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="525" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
         <v>361</v>
       </c>
@@ -16116,7 +16120,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="526" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
         <v>361</v>
       </c>
@@ -16142,7 +16146,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="527" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
         <v>361</v>
       </c>
@@ -16194,7 +16198,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="529" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
         <v>361</v>
       </c>
@@ -16220,7 +16224,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="530" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
         <v>365</v>
       </c>
@@ -16246,7 +16250,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="531" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
         <v>365</v>
       </c>
@@ -16272,7 +16276,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="532" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
         <v>365</v>
       </c>
@@ -16298,7 +16302,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="533" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
         <v>365</v>
       </c>
@@ -16324,7 +16328,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="534" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
         <v>365</v>
       </c>
@@ -16350,7 +16354,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="535" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
         <v>365</v>
       </c>
@@ -16376,7 +16380,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="536" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
         <v>367</v>
       </c>
@@ -16402,7 +16406,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="537" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
         <v>367</v>
       </c>
@@ -16428,7 +16432,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="538" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
         <v>367</v>
       </c>
@@ -16454,7 +16458,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="539" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
         <v>367</v>
       </c>
@@ -16480,7 +16484,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="540" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
         <v>367</v>
       </c>
@@ -16506,7 +16510,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="541" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
         <v>367</v>
       </c>
@@ -16532,7 +16536,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="542" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
         <v>370</v>
       </c>
@@ -16558,7 +16562,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="543" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
         <v>370</v>
       </c>
@@ -16584,7 +16588,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="544" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
         <v>370</v>
       </c>
@@ -16610,7 +16614,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="545" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
         <v>370</v>
       </c>
@@ -16636,7 +16640,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="546" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
         <v>370</v>
       </c>
@@ -16662,7 +16666,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="547" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
         <v>370</v>
       </c>
@@ -16688,7 +16692,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="548" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
         <v>373</v>
       </c>
@@ -16714,7 +16718,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="549" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
         <v>373</v>
       </c>
@@ -16740,7 +16744,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="550" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
         <v>373</v>
       </c>
@@ -16766,7 +16770,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="551" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
         <v>373</v>
       </c>
@@ -16792,7 +16796,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="552" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
         <v>373</v>
       </c>
@@ -16818,7 +16822,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="553" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
         <v>373</v>
       </c>
@@ -16844,7 +16848,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="554" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
         <v>377</v>
       </c>
@@ -16870,7 +16874,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="555" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
         <v>377</v>
       </c>
@@ -16896,7 +16900,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="556" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
         <v>377</v>
       </c>
@@ -16922,7 +16926,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="557" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
         <v>377</v>
       </c>
@@ -16948,7 +16952,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="558" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
         <v>377</v>
       </c>
@@ -16974,7 +16978,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="559" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
         <v>377</v>
       </c>
@@ -17000,7 +17004,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="560" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
         <v>378</v>
       </c>
@@ -17026,7 +17030,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="561" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
         <v>378</v>
       </c>
@@ -17052,7 +17056,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="562" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
         <v>378</v>
       </c>
@@ -17078,7 +17082,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="563" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
         <v>378</v>
       </c>
@@ -17104,7 +17108,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="564" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
         <v>378</v>
       </c>
@@ -17130,7 +17134,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="565" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
         <v>378</v>
       </c>
@@ -17156,7 +17160,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="566" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
         <v>379</v>
       </c>
@@ -17182,7 +17186,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="567" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
         <v>379</v>
       </c>
@@ -17208,7 +17212,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="568" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
         <v>379</v>
       </c>
@@ -17234,7 +17238,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="569" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
         <v>379</v>
       </c>
@@ -17260,7 +17264,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="570" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
         <v>379</v>
       </c>
@@ -17286,7 +17290,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="571" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
         <v>379</v>
       </c>
@@ -17312,7 +17316,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="572" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
         <v>383</v>
       </c>
@@ -17338,7 +17342,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="573" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
         <v>383</v>
       </c>
@@ -17364,7 +17368,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="574" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
         <v>383</v>
       </c>
@@ -17390,7 +17394,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="575" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
         <v>383</v>
       </c>
@@ -17416,7 +17420,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="576" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
         <v>383</v>
       </c>
@@ -17442,7 +17446,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="577" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
         <v>383</v>
       </c>
@@ -17468,7 +17472,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="578" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
         <v>387</v>
       </c>
@@ -17494,7 +17498,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="579" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
         <v>387</v>
       </c>
@@ -17520,7 +17524,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="580" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
         <v>387</v>
       </c>
@@ -17546,7 +17550,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="581" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
         <v>387</v>
       </c>
@@ -17572,7 +17576,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="582" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
         <v>387</v>
       </c>
@@ -17598,7 +17602,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="583" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
         <v>387</v>
       </c>
@@ -17624,7 +17628,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="584" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
         <v>391</v>
       </c>
@@ -17650,7 +17654,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="585" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
         <v>391</v>
       </c>
@@ -17676,7 +17680,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="586" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
         <v>391</v>
       </c>
@@ -17702,7 +17706,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="587" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
         <v>391</v>
       </c>
@@ -17728,7 +17732,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="588" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
         <v>391</v>
       </c>
@@ -17754,7 +17758,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="589" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
         <v>391</v>
       </c>
@@ -17780,7 +17784,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="590" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
         <v>393</v>
       </c>
@@ -17806,7 +17810,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="591" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
         <v>393</v>
       </c>
@@ -17832,7 +17836,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="592" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
         <v>393</v>
       </c>
@@ -17858,7 +17862,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="593" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
         <v>393</v>
       </c>
@@ -17884,7 +17888,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="594" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
         <v>393</v>
       </c>
@@ -17910,7 +17914,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="595" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
         <v>393</v>
       </c>
@@ -17936,7 +17940,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="596" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
         <v>398</v>
       </c>
@@ -17962,7 +17966,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="597" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
         <v>398</v>
       </c>
@@ -17988,7 +17992,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="598" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
         <v>398</v>
       </c>
@@ -18014,7 +18018,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="599" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
         <v>398</v>
       </c>
@@ -18040,7 +18044,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="600" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
         <v>398</v>
       </c>
@@ -18066,7 +18070,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="601" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
         <v>398</v>
       </c>
@@ -18092,7 +18096,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="602" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
         <v>400</v>
       </c>
@@ -18118,7 +18122,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="603" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
         <v>400</v>
       </c>
@@ -18144,7 +18148,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="604" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
         <v>400</v>
       </c>
@@ -18170,7 +18174,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="605" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
         <v>400</v>
       </c>
@@ -18196,7 +18200,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="606" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
         <v>400</v>
       </c>
@@ -18222,7 +18226,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="607" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
         <v>400</v>
       </c>
@@ -18248,7 +18252,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="608" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
         <v>404</v>
       </c>
@@ -18274,7 +18278,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="609" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
         <v>404</v>
       </c>
@@ -18300,7 +18304,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="610" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
         <v>404</v>
       </c>
@@ -18326,7 +18330,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="611" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
         <v>404</v>
       </c>
@@ -18352,7 +18356,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="612" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
         <v>404</v>
       </c>
@@ -18378,7 +18382,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="613" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
         <v>404</v>
       </c>
@@ -18404,7 +18408,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="614" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
         <v>409</v>
       </c>
@@ -18430,7 +18434,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="615" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
         <v>409</v>
       </c>
@@ -18456,7 +18460,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="616" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
         <v>409</v>
       </c>
@@ -18482,7 +18486,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="617" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
         <v>409</v>
       </c>
@@ -18508,7 +18512,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="618" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
         <v>409</v>
       </c>
@@ -18534,7 +18538,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="619" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
         <v>409</v>
       </c>
@@ -18560,7 +18564,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="620" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
         <v>412</v>
       </c>
@@ -18586,7 +18590,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="621" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
         <v>412</v>
       </c>
@@ -18612,7 +18616,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="622" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
         <v>412</v>
       </c>
@@ -18638,7 +18642,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="623" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
         <v>412</v>
       </c>
@@ -18664,7 +18668,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="624" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
         <v>412</v>
       </c>
@@ -18690,7 +18694,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="625" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
         <v>412</v>
       </c>
@@ -18716,7 +18720,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="626" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
         <v>413</v>
       </c>
@@ -18742,7 +18746,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="627" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
         <v>413</v>
       </c>
@@ -18768,7 +18772,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="628" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
         <v>413</v>
       </c>
@@ -18794,7 +18798,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="629" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
         <v>413</v>
       </c>
@@ -18820,7 +18824,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="630" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
         <v>413</v>
       </c>
@@ -18846,7 +18850,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="631" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
         <v>413</v>
       </c>
@@ -18872,7 +18876,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="632" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
         <v>415</v>
       </c>
@@ -18898,7 +18902,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="633" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
         <v>415</v>
       </c>
@@ -18924,7 +18928,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="634" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
         <v>415</v>
       </c>
@@ -18950,7 +18954,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="635" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
         <v>415</v>
       </c>
@@ -18976,7 +18980,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="636" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
         <v>415</v>
       </c>
@@ -19002,7 +19006,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="637" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
         <v>415</v>
       </c>
@@ -19028,7 +19032,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="638" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
         <v>417</v>
       </c>
@@ -19054,7 +19058,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="639" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
         <v>417</v>
       </c>
@@ -19080,7 +19084,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="640" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
         <v>417</v>
       </c>
@@ -19106,7 +19110,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="641" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
         <v>417</v>
       </c>
@@ -19132,7 +19136,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="642" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
         <v>417</v>
       </c>
@@ -19184,7 +19188,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="644" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
         <v>422</v>
       </c>
@@ -19210,7 +19214,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="645" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
         <v>422</v>
       </c>
@@ -19236,7 +19240,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="646" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
         <v>422</v>
       </c>
@@ -19262,7 +19266,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="647" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
         <v>422</v>
       </c>
@@ -19288,7 +19292,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="648" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
         <v>422</v>
       </c>
@@ -19314,7 +19318,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="649" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
         <v>422</v>
       </c>
@@ -19340,7 +19344,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="650" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
         <v>424</v>
       </c>
@@ -19366,7 +19370,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="651" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
         <v>424</v>
       </c>
@@ -19392,7 +19396,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="652" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
         <v>424</v>
       </c>
@@ -19418,7 +19422,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="653" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
         <v>424</v>
       </c>
@@ -19444,7 +19448,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="654" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
         <v>424</v>
       </c>
@@ -19470,7 +19474,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="655" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
         <v>424</v>
       </c>
@@ -19496,7 +19500,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="656" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
         <v>426</v>
       </c>
@@ -19522,7 +19526,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="657" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
         <v>426</v>
       </c>
@@ -19548,7 +19552,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="658" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
         <v>426</v>
       </c>
@@ -19574,7 +19578,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="659" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
         <v>426</v>
       </c>
@@ -19600,7 +19604,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="660" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
         <v>426</v>
       </c>
@@ -19626,7 +19630,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="661" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
         <v>426</v>
       </c>
@@ -19652,7 +19656,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="662" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
         <v>432</v>
       </c>
@@ -19678,7 +19682,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="663" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
         <v>432</v>
       </c>
@@ -19704,7 +19708,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="664" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
         <v>432</v>
       </c>
@@ -19730,7 +19734,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="665" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
         <v>432</v>
       </c>
@@ -19756,7 +19760,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="666" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
         <v>432</v>
       </c>
@@ -19782,7 +19786,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="667" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
         <v>432</v>
       </c>
@@ -19808,7 +19812,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="668" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
         <v>435</v>
       </c>
@@ -19834,7 +19838,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="669" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
         <v>435</v>
       </c>
@@ -19860,7 +19864,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="670" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
         <v>435</v>
       </c>
@@ -19886,7 +19890,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="671" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
         <v>435</v>
       </c>
@@ -19912,7 +19916,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="672" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
         <v>435</v>
       </c>
@@ -19938,7 +19942,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="673" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
         <v>435</v>
       </c>
@@ -19964,7 +19968,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="674" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
         <v>436</v>
       </c>
@@ -19990,7 +19994,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="675" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
         <v>436</v>
       </c>
@@ -20016,7 +20020,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="676" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
         <v>436</v>
       </c>
@@ -20042,7 +20046,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="677" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
         <v>436</v>
       </c>
@@ -20068,7 +20072,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="678" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
         <v>436</v>
       </c>
@@ -20094,7 +20098,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="679" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
         <v>436</v>
       </c>
@@ -20120,7 +20124,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="680" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
         <v>438</v>
       </c>
@@ -20146,7 +20150,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="681" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
         <v>438</v>
       </c>
@@ -20172,7 +20176,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="682" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
         <v>438</v>
       </c>
@@ -20198,7 +20202,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="683" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
         <v>438</v>
       </c>
@@ -20224,7 +20228,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="684" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
         <v>438</v>
       </c>
@@ -20250,7 +20254,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="685" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
         <v>438</v>
       </c>
@@ -20276,7 +20280,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="686" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
         <v>439</v>
       </c>
@@ -20302,7 +20306,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="687" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
         <v>439</v>
       </c>
@@ -20328,7 +20332,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="688" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
         <v>439</v>
       </c>
@@ -20354,7 +20358,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="689" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
         <v>439</v>
       </c>
@@ -20380,7 +20384,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="690" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
         <v>439</v>
       </c>
@@ -20406,7 +20410,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="691" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
         <v>439</v>
       </c>
@@ -20432,7 +20436,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="692" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
         <v>441</v>
       </c>
@@ -20458,7 +20462,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="693" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
         <v>441</v>
       </c>
@@ -20484,7 +20488,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="694" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
         <v>441</v>
       </c>
@@ -20510,7 +20514,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="695" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
         <v>441</v>
       </c>
@@ -20536,7 +20540,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="696" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
         <v>441</v>
       </c>
@@ -20562,7 +20566,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="697" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
         <v>441</v>
       </c>
@@ -20588,7 +20592,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="698" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
         <v>442</v>
       </c>
@@ -20614,7 +20618,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="699" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
         <v>442</v>
       </c>
@@ -20640,7 +20644,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="700" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
         <v>442</v>
       </c>
@@ -20666,7 +20670,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="701" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
         <v>442</v>
       </c>
@@ -20692,7 +20696,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="702" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A702" t="s">
         <v>442</v>
       </c>
@@ -20718,7 +20722,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="703" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
         <v>442</v>
       </c>
@@ -20744,7 +20748,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="704" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A704" t="s">
         <v>444</v>
       </c>
@@ -20770,7 +20774,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="705" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
         <v>444</v>
       </c>
@@ -20796,7 +20800,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="706" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
         <v>444</v>
       </c>
@@ -20822,7 +20826,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="707" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
         <v>444</v>
       </c>
@@ -20848,7 +20852,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="708" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A708" t="s">
         <v>444</v>
       </c>
@@ -20874,7 +20878,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="709" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A709" t="s">
         <v>444</v>
       </c>
@@ -20900,7 +20904,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="710" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
         <v>447</v>
       </c>
@@ -20926,7 +20930,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="711" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A711" t="s">
         <v>447</v>
       </c>
@@ -20952,7 +20956,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="712" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A712" t="s">
         <v>447</v>
       </c>
@@ -20978,7 +20982,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="713" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A713" t="s">
         <v>447</v>
       </c>
@@ -21004,7 +21008,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="714" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A714" t="s">
         <v>447</v>
       </c>
@@ -21030,7 +21034,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="715" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A715" t="s">
         <v>447</v>
       </c>
@@ -21056,7 +21060,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="716" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A716" t="s">
         <v>449</v>
       </c>
@@ -21082,7 +21086,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="717" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A717" t="s">
         <v>449</v>
       </c>
@@ -21108,7 +21112,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="718" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A718" t="s">
         <v>449</v>
       </c>
@@ -21134,7 +21138,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="719" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A719" t="s">
         <v>449</v>
       </c>
@@ -21160,7 +21164,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="720" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A720" t="s">
         <v>449</v>
       </c>
@@ -21186,7 +21190,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="721" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A721" t="s">
         <v>449</v>
       </c>
@@ -21212,7 +21216,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="722" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A722" t="s">
         <v>453</v>
       </c>
@@ -21238,7 +21242,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="723" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A723" t="s">
         <v>453</v>
       </c>
@@ -21264,7 +21268,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="724" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A724" t="s">
         <v>453</v>
       </c>
@@ -21290,7 +21294,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="725" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A725" t="s">
         <v>453</v>
       </c>
@@ -21316,7 +21320,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="726" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A726" t="s">
         <v>453</v>
       </c>
@@ -21342,7 +21346,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="727" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A727" t="s">
         <v>453</v>
       </c>
@@ -21368,7 +21372,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="728" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A728" t="s">
         <v>456</v>
       </c>
@@ -21394,7 +21398,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="729" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A729" t="s">
         <v>456</v>
       </c>
@@ -21420,7 +21424,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="730" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A730" t="s">
         <v>456</v>
       </c>
@@ -21446,7 +21450,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="731" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A731" t="s">
         <v>456</v>
       </c>
@@ -21472,7 +21476,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="732" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A732" t="s">
         <v>456</v>
       </c>
@@ -21498,7 +21502,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="733" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A733" t="s">
         <v>456</v>
       </c>
@@ -21524,7 +21528,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="734" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A734" t="s">
         <v>458</v>
       </c>
@@ -21550,7 +21554,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="735" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A735" t="s">
         <v>458</v>
       </c>
@@ -21576,7 +21580,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="736" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A736" t="s">
         <v>458</v>
       </c>
@@ -21602,7 +21606,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="737" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A737" t="s">
         <v>458</v>
       </c>
@@ -21628,7 +21632,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="738" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A738" t="s">
         <v>458</v>
       </c>
@@ -21654,7 +21658,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="739" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A739" t="s">
         <v>458</v>
       </c>
@@ -21680,7 +21684,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="740" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A740" t="s">
         <v>460</v>
       </c>
@@ -21706,7 +21710,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="741" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A741" t="s">
         <v>460</v>
       </c>
@@ -21732,7 +21736,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="742" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A742" t="s">
         <v>460</v>
       </c>
@@ -21758,7 +21762,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="743" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A743" t="s">
         <v>460</v>
       </c>
@@ -21784,7 +21788,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="744" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A744" t="s">
         <v>460</v>
       </c>
@@ -21810,7 +21814,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="745" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A745" t="s">
         <v>460</v>
       </c>
@@ -21836,7 +21840,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="746" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A746" t="s">
         <v>465</v>
       </c>
@@ -21862,7 +21866,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="747" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A747" t="s">
         <v>465</v>
       </c>
@@ -21888,7 +21892,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="748" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A748" t="s">
         <v>465</v>
       </c>
@@ -21914,7 +21918,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="749" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A749" t="s">
         <v>465</v>
       </c>
@@ -21940,7 +21944,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="750" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A750" t="s">
         <v>465</v>
       </c>
@@ -21966,7 +21970,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="751" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A751" t="s">
         <v>465</v>
       </c>
@@ -21992,7 +21996,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="752" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A752" t="s">
         <v>468</v>
       </c>
@@ -22018,7 +22022,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="753" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A753" t="s">
         <v>468</v>
       </c>
@@ -22044,7 +22048,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="754" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A754" t="s">
         <v>468</v>
       </c>
@@ -22070,7 +22074,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="755" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A755" t="s">
         <v>468</v>
       </c>
@@ -22096,7 +22100,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="756" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A756" t="s">
         <v>468</v>
       </c>
@@ -22122,7 +22126,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="757" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A757" t="s">
         <v>468</v>
       </c>
@@ -22148,7 +22152,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="758" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A758" t="s">
         <v>470</v>
       </c>
@@ -22174,7 +22178,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="759" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A759" t="s">
         <v>470</v>
       </c>
@@ -22200,7 +22204,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="760" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A760" t="s">
         <v>470</v>
       </c>
@@ -22226,7 +22230,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="761" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A761" t="s">
         <v>470</v>
       </c>
@@ -22252,7 +22256,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="762" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A762" t="s">
         <v>470</v>
       </c>
@@ -22278,7 +22282,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="763" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A763" t="s">
         <v>470</v>
       </c>
@@ -22304,7 +22308,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="764" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A764" t="s">
         <v>472</v>
       </c>
@@ -22330,7 +22334,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="765" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A765" t="s">
         <v>472</v>
       </c>
@@ -22356,7 +22360,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="766" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A766" t="s">
         <v>472</v>
       </c>
@@ -22382,7 +22386,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="767" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A767" t="s">
         <v>472</v>
       </c>
@@ -22408,7 +22412,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="768" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A768" t="s">
         <v>472</v>
       </c>
@@ -22434,7 +22438,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="769" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A769" t="s">
         <v>472</v>
       </c>
@@ -22460,7 +22464,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="770" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A770" t="s">
         <v>473</v>
       </c>
@@ -22486,7 +22490,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="771" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A771" t="s">
         <v>473</v>
       </c>
@@ -22512,7 +22516,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="772" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A772" t="s">
         <v>473</v>
       </c>
@@ -22538,7 +22542,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="773" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A773" t="s">
         <v>473</v>
       </c>
@@ -22564,7 +22568,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="774" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A774" t="s">
         <v>473</v>
       </c>
@@ -22590,7 +22594,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="775" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A775" t="s">
         <v>473</v>
       </c>
@@ -22616,7 +22620,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="776" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A776" t="s">
         <v>476</v>
       </c>
@@ -22642,7 +22646,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="777" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A777" t="s">
         <v>476</v>
       </c>
@@ -22668,7 +22672,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="778" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A778" t="s">
         <v>476</v>
       </c>
@@ -22694,7 +22698,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="779" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A779" t="s">
         <v>476</v>
       </c>
@@ -22720,7 +22724,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="780" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A780" t="s">
         <v>476</v>
       </c>
@@ -22746,7 +22750,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="781" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A781" t="s">
         <v>476</v>
       </c>
@@ -22772,7 +22776,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="782" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A782" t="s">
         <v>478</v>
       </c>
@@ -22798,7 +22802,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="783" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A783" t="s">
         <v>478</v>
       </c>
@@ -22824,7 +22828,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="784" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A784" t="s">
         <v>478</v>
       </c>
@@ -22850,7 +22854,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="785" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A785" t="s">
         <v>478</v>
       </c>
@@ -22876,7 +22880,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="786" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A786" t="s">
         <v>478</v>
       </c>
@@ -22902,7 +22906,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="787" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A787" t="s">
         <v>478</v>
       </c>
@@ -22928,7 +22932,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="788" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A788" t="s">
         <v>482</v>
       </c>
@@ -22954,7 +22958,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="789" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A789" t="s">
         <v>482</v>
       </c>
@@ -22980,7 +22984,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="790" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A790" t="s">
         <v>482</v>
       </c>
@@ -23006,7 +23010,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="791" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A791" t="s">
         <v>482</v>
       </c>
@@ -23032,7 +23036,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="792" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A792" t="s">
         <v>482</v>
       </c>
@@ -23058,7 +23062,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="793" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A793" t="s">
         <v>482</v>
       </c>
@@ -23084,7 +23088,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="794" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A794" t="s">
         <v>486</v>
       </c>
@@ -23110,7 +23114,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="795" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A795" t="s">
         <v>486</v>
       </c>
@@ -23136,7 +23140,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="796" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A796" t="s">
         <v>486</v>
       </c>
@@ -23188,7 +23192,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="798" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A798" t="s">
         <v>486</v>
       </c>
@@ -23214,7 +23218,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="799" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A799" t="s">
         <v>486</v>
       </c>
@@ -23240,7 +23244,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="800" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A800" t="s">
         <v>490</v>
       </c>
@@ -23266,7 +23270,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="801" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A801" t="s">
         <v>490</v>
       </c>
@@ -23292,7 +23296,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="802" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A802" t="s">
         <v>490</v>
       </c>
@@ -23318,7 +23322,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="803" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A803" t="s">
         <v>490</v>
       </c>
@@ -23344,7 +23348,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="804" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A804" t="s">
         <v>490</v>
       </c>
@@ -23370,7 +23374,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="805" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A805" t="s">
         <v>490</v>
       </c>
@@ -23396,7 +23400,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="806" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A806" t="s">
         <v>494</v>
       </c>
@@ -23422,7 +23426,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="807" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A807" t="s">
         <v>494</v>
       </c>
@@ -23448,7 +23452,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="808" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A808" t="s">
         <v>494</v>
       </c>
@@ -23474,7 +23478,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="809" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A809" t="s">
         <v>494</v>
       </c>
@@ -23500,7 +23504,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="810" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A810" t="s">
         <v>494</v>
       </c>
@@ -23526,7 +23530,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="811" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A811" t="s">
         <v>494</v>
       </c>
@@ -23552,7 +23556,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="812" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A812" t="s">
         <v>499</v>
       </c>
@@ -23578,7 +23582,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="813" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A813" t="s">
         <v>499</v>
       </c>
@@ -23604,7 +23608,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="814" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A814" t="s">
         <v>499</v>
       </c>
@@ -23630,7 +23634,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="815" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A815" t="s">
         <v>499</v>
       </c>
@@ -23656,7 +23660,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="816" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A816" t="s">
         <v>499</v>
       </c>
@@ -23682,7 +23686,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="817" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A817" t="s">
         <v>499</v>
       </c>
@@ -23708,7 +23712,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="818" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A818" t="s">
         <v>501</v>
       </c>
@@ -23734,7 +23738,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="819" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A819" t="s">
         <v>501</v>
       </c>
@@ -23760,7 +23764,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="820" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A820" t="s">
         <v>501</v>
       </c>
@@ -23786,7 +23790,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="821" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A821" t="s">
         <v>501</v>
       </c>
@@ -23812,7 +23816,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="822" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A822" t="s">
         <v>501</v>
       </c>
@@ -23838,7 +23842,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="823" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A823" t="s">
         <v>501</v>
       </c>
@@ -23864,7 +23868,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="824" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A824" t="s">
         <v>502</v>
       </c>
@@ -23890,7 +23894,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="825" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A825" t="s">
         <v>502</v>
       </c>
@@ -23916,7 +23920,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="826" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A826" t="s">
         <v>502</v>
       </c>
@@ -23942,7 +23946,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="827" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A827" t="s">
         <v>502</v>
       </c>
@@ -23968,7 +23972,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="828" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A828" t="s">
         <v>502</v>
       </c>
@@ -23994,7 +23998,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="829" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A829" t="s">
         <v>502</v>
       </c>
@@ -24020,7 +24024,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="830" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A830" t="s">
         <v>504</v>
       </c>
@@ -24046,7 +24050,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="831" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A831" t="s">
         <v>504</v>
       </c>
@@ -24072,7 +24076,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="832" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A832" t="s">
         <v>504</v>
       </c>
@@ -24098,7 +24102,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="833" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A833" t="s">
         <v>504</v>
       </c>
@@ -24124,7 +24128,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="834" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A834" t="s">
         <v>504</v>
       </c>
@@ -24150,7 +24154,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="835" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A835" t="s">
         <v>504</v>
       </c>
@@ -24176,7 +24180,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="836" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A836" t="s">
         <v>507</v>
       </c>
@@ -24202,7 +24206,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="837" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A837" t="s">
         <v>507</v>
       </c>
@@ -24228,7 +24232,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="838" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A838" t="s">
         <v>507</v>
       </c>
@@ -24254,7 +24258,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="839" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A839" t="s">
         <v>507</v>
       </c>
@@ -24280,7 +24284,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="840" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A840" t="s">
         <v>507</v>
       </c>
@@ -24306,7 +24310,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="841" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A841" t="s">
         <v>507</v>
       </c>
@@ -24332,7 +24336,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="842" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A842" t="s">
         <v>510</v>
       </c>
@@ -24358,7 +24362,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="843" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A843" t="s">
         <v>510</v>
       </c>
@@ -24384,7 +24388,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="844" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A844" t="s">
         <v>510</v>
       </c>
@@ -24410,7 +24414,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="845" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A845" t="s">
         <v>510</v>
       </c>
@@ -24436,7 +24440,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="846" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A846" t="s">
         <v>510</v>
       </c>
@@ -24462,7 +24466,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="847" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A847" t="s">
         <v>510</v>
       </c>
@@ -24488,7 +24492,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="848" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A848" t="s">
         <v>511</v>
       </c>
@@ -24514,7 +24518,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="849" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A849" t="s">
         <v>511</v>
       </c>
@@ -24540,7 +24544,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="850" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A850" t="s">
         <v>511</v>
       </c>
@@ -24566,7 +24570,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="851" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A851" t="s">
         <v>511</v>
       </c>
@@ -24592,7 +24596,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="852" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A852" t="s">
         <v>511</v>
       </c>
@@ -24618,7 +24622,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="853" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A853" t="s">
         <v>511</v>
       </c>
@@ -24644,7 +24648,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="854" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A854" t="s">
         <v>514</v>
       </c>
@@ -24670,7 +24674,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="855" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A855" t="s">
         <v>514</v>
       </c>
@@ -24696,7 +24700,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="856" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A856" t="s">
         <v>514</v>
       </c>
@@ -24722,7 +24726,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="857" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A857" t="s">
         <v>514</v>
       </c>
@@ -24748,7 +24752,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="858" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A858" t="s">
         <v>514</v>
       </c>
@@ -24774,7 +24778,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="859" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A859" t="s">
         <v>514</v>
       </c>
@@ -24800,7 +24804,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="860" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A860" t="s">
         <v>516</v>
       </c>
@@ -24826,7 +24830,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="861" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A861" t="s">
         <v>516</v>
       </c>
@@ -24852,7 +24856,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="862" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A862" t="s">
         <v>516</v>
       </c>
@@ -24878,7 +24882,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="863" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A863" t="s">
         <v>516</v>
       </c>
@@ -24904,7 +24908,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="864" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A864" t="s">
         <v>516</v>
       </c>
@@ -24930,7 +24934,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="865" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A865" t="s">
         <v>516</v>
       </c>
@@ -24956,7 +24960,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="866" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A866" t="s">
         <v>518</v>
       </c>
@@ -24982,7 +24986,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="867" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A867" t="s">
         <v>518</v>
       </c>
@@ -25008,7 +25012,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="868" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A868" t="s">
         <v>518</v>
       </c>
@@ -25034,7 +25038,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="869" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A869" t="s">
         <v>518</v>
       </c>
@@ -25060,7 +25064,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="870" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A870" t="s">
         <v>518</v>
       </c>
@@ -25086,7 +25090,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="871" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A871" t="s">
         <v>518</v>
       </c>
@@ -25112,7 +25116,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="872" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A872" t="s">
         <v>519</v>
       </c>
@@ -25138,7 +25142,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="873" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A873" t="s">
         <v>519</v>
       </c>
@@ -25164,7 +25168,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="874" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A874" t="s">
         <v>519</v>
       </c>
@@ -25190,7 +25194,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="875" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A875" t="s">
         <v>519</v>
       </c>
@@ -25216,7 +25220,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="876" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A876" t="s">
         <v>519</v>
       </c>
@@ -25242,7 +25246,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="877" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A877" t="s">
         <v>519</v>
       </c>
@@ -25268,7 +25272,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="878" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A878" t="s">
         <v>522</v>
       </c>
@@ -25294,7 +25298,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="879" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A879" t="s">
         <v>522</v>
       </c>
@@ -25320,7 +25324,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="880" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A880" t="s">
         <v>522</v>
       </c>
@@ -25346,7 +25350,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="881" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A881" t="s">
         <v>522</v>
       </c>
@@ -25372,7 +25376,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="882" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A882" t="s">
         <v>522</v>
       </c>
@@ -25398,7 +25402,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="883" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A883" t="s">
         <v>522</v>
       </c>
@@ -25424,7 +25428,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="884" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A884" t="s">
         <v>526</v>
       </c>
@@ -25450,7 +25454,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="885" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A885" t="s">
         <v>526</v>
       </c>
@@ -25476,7 +25480,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="886" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A886" t="s">
         <v>526</v>
       </c>
@@ -25502,7 +25506,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="887" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A887" t="s">
         <v>526</v>
       </c>
@@ -25528,7 +25532,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="888" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A888" t="s">
         <v>526</v>
       </c>
@@ -25554,7 +25558,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="889" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="889" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A889" t="s">
         <v>526</v>
       </c>
@@ -25580,7 +25584,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="890" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="890" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A890" t="s">
         <v>529</v>
       </c>
@@ -25606,7 +25610,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="891" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A891" t="s">
         <v>529</v>
       </c>
@@ -25632,7 +25636,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="892" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A892" t="s">
         <v>529</v>
       </c>
@@ -25658,7 +25662,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="893" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A893" t="s">
         <v>529</v>
       </c>
@@ -25684,7 +25688,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="894" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A894" t="s">
         <v>529</v>
       </c>
@@ -25710,7 +25714,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="895" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A895" t="s">
         <v>529</v>
       </c>
@@ -25736,7 +25740,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="896" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A896" t="s">
         <v>533</v>
       </c>
@@ -25762,7 +25766,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="897" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A897" t="s">
         <v>533</v>
       </c>
@@ -25788,7 +25792,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="898" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A898" t="s">
         <v>533</v>
       </c>
@@ -25814,7 +25818,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="899" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A899" t="s">
         <v>533</v>
       </c>
@@ -25840,7 +25844,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="900" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A900" t="s">
         <v>533</v>
       </c>
@@ -25892,7 +25896,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="902" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="902" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A902" t="s">
         <v>536</v>
       </c>
@@ -25918,7 +25922,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="903" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A903" t="s">
         <v>536</v>
       </c>
@@ -25944,7 +25948,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="904" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A904" t="s">
         <v>536</v>
       </c>
@@ -25970,7 +25974,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="905" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="905" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A905" t="s">
         <v>536</v>
       </c>
@@ -25996,7 +26000,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="906" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A906" t="s">
         <v>536</v>
       </c>
@@ -26022,7 +26026,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="907" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A907" t="s">
         <v>536</v>
       </c>
@@ -26048,7 +26052,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="908" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="908" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A908" t="s">
         <v>538</v>
       </c>
@@ -26074,7 +26078,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="909" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="909" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A909" t="s">
         <v>538</v>
       </c>
@@ -26100,7 +26104,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="910" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="910" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A910" t="s">
         <v>538</v>
       </c>
@@ -26126,7 +26130,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="911" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="911" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A911" t="s">
         <v>538</v>
       </c>
@@ -26152,7 +26156,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="912" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="912" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A912" t="s">
         <v>538</v>
       </c>
@@ -26178,7 +26182,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="913" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="913" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A913" t="s">
         <v>538</v>
       </c>
@@ -26204,7 +26208,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="914" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="914" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A914" t="s">
         <v>540</v>
       </c>
@@ -26230,7 +26234,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="915" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="915" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A915" t="s">
         <v>540</v>
       </c>
@@ -26256,7 +26260,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="916" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="916" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A916" t="s">
         <v>540</v>
       </c>
@@ -26282,7 +26286,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="917" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="917" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A917" t="s">
         <v>540</v>
       </c>
@@ -26308,7 +26312,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="918" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="918" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A918" t="s">
         <v>540</v>
       </c>
@@ -26334,7 +26338,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="919" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="919" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A919" t="s">
         <v>540</v>
       </c>
@@ -26360,7 +26364,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="920" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="920" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A920" t="s">
         <v>541</v>
       </c>
@@ -26386,7 +26390,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="921" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="921" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A921" t="s">
         <v>541</v>
       </c>
@@ -26412,7 +26416,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="922" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="922" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A922" t="s">
         <v>541</v>
       </c>
@@ -26438,7 +26442,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="923" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="923" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A923" t="s">
         <v>541</v>
       </c>
@@ -26464,7 +26468,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="924" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="924" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A924" t="s">
         <v>541</v>
       </c>
@@ -26490,7 +26494,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="925" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="925" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A925" t="s">
         <v>541</v>
       </c>
@@ -26516,7 +26520,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="926" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="926" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A926" t="s">
         <v>542</v>
       </c>
@@ -26542,7 +26546,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="927" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="927" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A927" t="s">
         <v>542</v>
       </c>
@@ -26568,7 +26572,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="928" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="928" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A928" t="s">
         <v>542</v>
       </c>
@@ -26594,7 +26598,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="929" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="929" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A929" t="s">
         <v>542</v>
       </c>
@@ -26620,7 +26624,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="930" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="930" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A930" t="s">
         <v>542</v>
       </c>
@@ -26646,7 +26650,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="931" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="931" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A931" t="s">
         <v>542</v>
       </c>
@@ -26672,7 +26676,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="932" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="932" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A932" t="s">
         <v>543</v>
       </c>
@@ -26698,7 +26702,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="933" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="933" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A933" t="s">
         <v>543</v>
       </c>
@@ -26724,7 +26728,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="934" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="934" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A934" t="s">
         <v>543</v>
       </c>
@@ -26750,7 +26754,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="935" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="935" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A935" t="s">
         <v>543</v>
       </c>
@@ -26776,7 +26780,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="936" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="936" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A936" t="s">
         <v>543</v>
       </c>
@@ -26802,7 +26806,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="937" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="937" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A937" t="s">
         <v>543</v>
       </c>
@@ -26828,7 +26832,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="938" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="938" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A938" t="s">
         <v>544</v>
       </c>
@@ -26854,7 +26858,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="939" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="939" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A939" t="s">
         <v>544</v>
       </c>
@@ -26880,7 +26884,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="940" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="940" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A940" t="s">
         <v>544</v>
       </c>
@@ -26906,7 +26910,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="941" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="941" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A941" t="s">
         <v>544</v>
       </c>
@@ -26932,7 +26936,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="942" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="942" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A942" t="s">
         <v>544</v>
       </c>
@@ -26958,7 +26962,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="943" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="943" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A943" t="s">
         <v>544</v>
       </c>
@@ -26984,7 +26988,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="944" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="944" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A944" t="s">
         <v>546</v>
       </c>
@@ -27010,7 +27014,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="945" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="945" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A945" t="s">
         <v>546</v>
       </c>
@@ -27036,7 +27040,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="946" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="946" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A946" t="s">
         <v>546</v>
       </c>
@@ -27062,7 +27066,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="947" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="947" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A947" t="s">
         <v>546</v>
       </c>
@@ -27088,7 +27092,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="948" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="948" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A948" t="s">
         <v>546</v>
       </c>
@@ -27114,7 +27118,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="949" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="949" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A949" t="s">
         <v>546</v>
       </c>
@@ -27140,7 +27144,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="950" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="950" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A950" t="s">
         <v>548</v>
       </c>
@@ -27166,7 +27170,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="951" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="951" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A951" t="s">
         <v>548</v>
       </c>
@@ -27192,7 +27196,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="952" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="952" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A952" t="s">
         <v>548</v>
       </c>
@@ -27218,7 +27222,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="953" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="953" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A953" t="s">
         <v>548</v>
       </c>
@@ -27244,7 +27248,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="954" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="954" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A954" t="s">
         <v>548</v>
       </c>
@@ -27270,7 +27274,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="955" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="955" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A955" t="s">
         <v>548</v>
       </c>
@@ -27296,7 +27300,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="956" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="956" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A956" t="s">
         <v>549</v>
       </c>
@@ -27322,7 +27326,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="957" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="957" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A957" t="s">
         <v>549</v>
       </c>
@@ -27348,7 +27352,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="958" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="958" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A958" t="s">
         <v>549</v>
       </c>
@@ -27374,7 +27378,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="959" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="959" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A959" t="s">
         <v>549</v>
       </c>
@@ -27400,7 +27404,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="960" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="960" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A960" t="s">
         <v>549</v>
       </c>
@@ -27426,7 +27430,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="961" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="961" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A961" t="s">
         <v>549</v>
       </c>
@@ -27452,7 +27456,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="962" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="962" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A962" t="s">
         <v>551</v>
       </c>
@@ -27478,7 +27482,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="963" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="963" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A963" t="s">
         <v>551</v>
       </c>
@@ -27504,7 +27508,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="964" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="964" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A964" t="s">
         <v>551</v>
       </c>
@@ -27530,7 +27534,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="965" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="965" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A965" t="s">
         <v>551</v>
       </c>
@@ -27556,7 +27560,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="966" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="966" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A966" t="s">
         <v>551</v>
       </c>
@@ -27582,7 +27586,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="967" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="967" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A967" t="s">
         <v>551</v>
       </c>
@@ -27608,7 +27612,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="968" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="968" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A968" t="s">
         <v>553</v>
       </c>
@@ -27634,7 +27638,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="969" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="969" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A969" t="s">
         <v>553</v>
       </c>
@@ -27660,7 +27664,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="970" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="970" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A970" t="s">
         <v>553</v>
       </c>
@@ -27686,7 +27690,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="971" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="971" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A971" t="s">
         <v>553</v>
       </c>
@@ -27712,7 +27716,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="972" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="972" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A972" t="s">
         <v>553</v>
       </c>
@@ -27738,7 +27742,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="973" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="973" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A973" t="s">
         <v>553</v>
       </c>
@@ -27764,7 +27768,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="974" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="974" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A974" t="s">
         <v>555</v>
       </c>
@@ -27790,7 +27794,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="975" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="975" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A975" t="s">
         <v>555</v>
       </c>
@@ -27816,7 +27820,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="976" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="976" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A976" t="s">
         <v>555</v>
       </c>
@@ -27842,7 +27846,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="977" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="977" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A977" t="s">
         <v>555</v>
       </c>
@@ -27868,7 +27872,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="978" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="978" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A978" t="s">
         <v>555</v>
       </c>
@@ -27894,7 +27898,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="979" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="979" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A979" t="s">
         <v>555</v>
       </c>
@@ -27920,7 +27924,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="980" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="980" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A980" t="s">
         <v>556</v>
       </c>
@@ -27946,7 +27950,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="981" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="981" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A981" t="s">
         <v>556</v>
       </c>
@@ -27972,7 +27976,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="982" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="982" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A982" t="s">
         <v>556</v>
       </c>
@@ -27998,7 +28002,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="983" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="983" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A983" t="s">
         <v>556</v>
       </c>
@@ -28024,7 +28028,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="984" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="984" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A984" t="s">
         <v>556</v>
       </c>
@@ -28050,7 +28054,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="985" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="985" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A985" t="s">
         <v>556</v>
       </c>
@@ -28076,7 +28080,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="986" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="986" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A986" t="s">
         <v>559</v>
       </c>
@@ -28102,7 +28106,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="987" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="987" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A987" t="s">
         <v>559</v>
       </c>
@@ -28128,7 +28132,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="988" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="988" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A988" t="s">
         <v>559</v>
       </c>
@@ -28154,7 +28158,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="989" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="989" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A989" t="s">
         <v>559</v>
       </c>
@@ -28180,7 +28184,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="990" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="990" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A990" t="s">
         <v>559</v>
       </c>
@@ -28206,7 +28210,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="991" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="991" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A991" t="s">
         <v>559</v>
       </c>
@@ -28232,7 +28236,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="992" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="992" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A992" t="s">
         <v>561</v>
       </c>
@@ -28258,7 +28262,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="993" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="993" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A993" t="s">
         <v>561</v>
       </c>
@@ -28284,7 +28288,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="994" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="994" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A994" t="s">
         <v>561</v>
       </c>
@@ -28310,7 +28314,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="995" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="995" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A995" t="s">
         <v>561</v>
       </c>
@@ -28336,7 +28340,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="996" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="996" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A996" t="s">
         <v>561</v>
       </c>
@@ -28362,7 +28366,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="997" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="997" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A997" t="s">
         <v>561</v>
       </c>
@@ -28388,7 +28392,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="998" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="998" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A998" t="s">
         <v>563</v>
       </c>
@@ -28414,7 +28418,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="999" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="999" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A999" t="s">
         <v>563</v>
       </c>
@@ -28440,7 +28444,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1000" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1000" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1000" t="s">
         <v>563</v>
       </c>
@@ -28466,7 +28470,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1001" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1001" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1001" t="s">
         <v>563</v>
       </c>
@@ -28492,7 +28496,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1002" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1002" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1002" t="s">
         <v>563</v>
       </c>
@@ -28518,7 +28522,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="1003" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1003" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1003" t="s">
         <v>563</v>
       </c>
@@ -28544,7 +28548,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1004" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1004" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1004" t="s">
         <v>564</v>
       </c>
@@ -28570,7 +28574,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1005" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1005" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1005" t="s">
         <v>564</v>
       </c>
@@ -28596,7 +28600,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1006" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1006" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1006" t="s">
         <v>564</v>
       </c>
@@ -28622,7 +28626,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1007" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1007" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1007" t="s">
         <v>564</v>
       </c>
@@ -28648,7 +28652,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1008" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1008" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1008" t="s">
         <v>564</v>
       </c>
@@ -28674,7 +28678,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1009" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1009" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1009" t="s">
         <v>564</v>
       </c>
@@ -28700,7 +28704,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1010" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1010" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1010" t="s">
         <v>566</v>
       </c>
@@ -28726,7 +28730,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1011" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1011" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1011" t="s">
         <v>566</v>
       </c>
@@ -28752,7 +28756,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1012" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1012" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1012" t="s">
         <v>566</v>
       </c>
@@ -28778,7 +28782,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1013" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1013" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1013" t="s">
         <v>566</v>
       </c>
@@ -28804,7 +28808,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1014" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1014" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1014" t="s">
         <v>566</v>
       </c>
@@ -28830,7 +28834,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1015" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1015" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1015" t="s">
         <v>566</v>
       </c>
@@ -28856,7 +28860,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1016" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1016" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1016" t="s">
         <v>568</v>
       </c>
@@ -28882,7 +28886,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1017" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1017" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1017" t="s">
         <v>568</v>
       </c>
@@ -28908,7 +28912,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1018" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1018" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1018" t="s">
         <v>568</v>
       </c>
@@ -28934,7 +28938,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1019" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1019" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1019" t="s">
         <v>568</v>
       </c>
@@ -28960,7 +28964,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1020" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1020" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1020" t="s">
         <v>568</v>
       </c>
@@ -28986,7 +28990,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1021" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1021" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1021" t="s">
         <v>568</v>
       </c>
@@ -29012,7 +29016,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1022" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1022" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1022" t="s">
         <v>569</v>
       </c>
@@ -29038,7 +29042,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1023" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1023" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1023" t="s">
         <v>569</v>
       </c>
@@ -29064,7 +29068,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1024" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1024" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1024" t="s">
         <v>569</v>
       </c>
@@ -29090,7 +29094,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1025" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1025" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1025" t="s">
         <v>569</v>
       </c>
@@ -29116,7 +29120,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1026" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1026" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1026" t="s">
         <v>569</v>
       </c>
@@ -29142,7 +29146,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1027" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1027" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1027" t="s">
         <v>569</v>
       </c>
@@ -29168,7 +29172,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1028" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1028" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1028" t="s">
         <v>570</v>
       </c>
@@ -29194,7 +29198,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1029" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1029" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1029" t="s">
         <v>570</v>
       </c>
@@ -29220,7 +29224,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1030" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1030" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1030" t="s">
         <v>570</v>
       </c>
@@ -29246,7 +29250,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1031" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1031" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1031" t="s">
         <v>570</v>
       </c>
@@ -29272,7 +29276,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1032" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1032" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1032" t="s">
         <v>570</v>
       </c>
@@ -29298,7 +29302,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1033" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1033" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1033" t="s">
         <v>570</v>
       </c>
@@ -29324,7 +29328,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1034" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1034" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1034" t="s">
         <v>571</v>
       </c>
@@ -29350,7 +29354,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1035" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1035" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1035" t="s">
         <v>571</v>
       </c>
@@ -29376,7 +29380,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1036" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1036" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1036" t="s">
         <v>571</v>
       </c>
@@ -29402,7 +29406,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1037" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1037" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1037" t="s">
         <v>571</v>
       </c>
@@ -29428,7 +29432,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1038" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1038" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1038" t="s">
         <v>571</v>
       </c>
@@ -29454,7 +29458,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1039" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1039" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1039" t="s">
         <v>571</v>
       </c>
@@ -29480,7 +29484,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1040" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1040" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1040" t="s">
         <v>573</v>
       </c>
@@ -29506,7 +29510,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1041" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1041" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1041" t="s">
         <v>573</v>
       </c>
@@ -29532,7 +29536,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1042" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1042" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1042" t="s">
         <v>573</v>
       </c>
@@ -29558,7 +29562,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1043" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1043" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1043" t="s">
         <v>573</v>
       </c>
@@ -29584,7 +29588,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1044" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1044" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1044" t="s">
         <v>573</v>
       </c>
@@ -29610,7 +29614,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1045" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1045" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1045" t="s">
         <v>573</v>
       </c>
@@ -29636,7 +29640,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1046" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1046" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1046" t="s">
         <v>577</v>
       </c>
@@ -29662,7 +29666,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="1047" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1047" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1047" t="s">
         <v>577</v>
       </c>
@@ -29688,7 +29692,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="1048" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1048" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1048" t="s">
         <v>577</v>
       </c>
@@ -29714,7 +29718,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1049" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1049" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1049" t="s">
         <v>577</v>
       </c>
@@ -29740,7 +29744,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1050" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1050" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1050" t="s">
         <v>577</v>
       </c>
@@ -29766,7 +29770,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1051" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1051" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1051" t="s">
         <v>577</v>
       </c>
@@ -29793,6 +29797,14 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H1051" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Tauros-Paldea-Aqua"/>
+        <filter val="Tauros-Paldea-Blaze"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/tiers_gen9nationaldexdoubles.xlsx
+++ b/tiers_gen9nationaldexdoubles.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\power bi\webhook\Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{541AE986-438F-4084-AB05-C8D1AF75B36F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD8546FF-8129-4BAA-A082-E66C99982852}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pokemon" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Pokemon!$A$1:$H$1051</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Teams!$A$1:$E$41</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
@@ -2456,7 +2457,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:H1051"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2496,7 +2496,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -2522,7 +2522,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -2548,7 +2548,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -2574,7 +2574,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -2600,7 +2600,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -2626,7 +2626,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -2652,7 +2652,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -2678,7 +2678,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -2704,7 +2704,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -2730,7 +2730,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -2756,7 +2756,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -2782,7 +2782,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -2808,7 +2808,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -2834,7 +2834,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>26</v>
       </c>
@@ -2860,7 +2860,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>26</v>
       </c>
@@ -2886,7 +2886,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -2912,7 +2912,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>26</v>
       </c>
@@ -2938,7 +2938,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>26</v>
       </c>
@@ -2964,7 +2964,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -2990,7 +2990,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>33</v>
       </c>
@@ -3016,7 +3016,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>33</v>
       </c>
@@ -3042,7 +3042,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>33</v>
       </c>
@@ -3068,7 +3068,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>33</v>
       </c>
@@ -3094,7 +3094,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>33</v>
       </c>
@@ -3120,7 +3120,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>39</v>
       </c>
@@ -3146,7 +3146,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>39</v>
       </c>
@@ -3172,7 +3172,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>39</v>
       </c>
@@ -3198,7 +3198,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>39</v>
       </c>
@@ -3224,7 +3224,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>39</v>
       </c>
@@ -3250,7 +3250,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>39</v>
       </c>
@@ -3276,7 +3276,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>46</v>
       </c>
@@ -3302,7 +3302,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>46</v>
       </c>
@@ -3328,7 +3328,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>46</v>
       </c>
@@ -3354,7 +3354,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>46</v>
       </c>
@@ -3380,7 +3380,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>46</v>
       </c>
@@ -3406,7 +3406,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>46</v>
       </c>
@@ -3432,7 +3432,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>51</v>
       </c>
@@ -3458,7 +3458,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>51</v>
       </c>
@@ -3484,7 +3484,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>51</v>
       </c>
@@ -3510,7 +3510,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>51</v>
       </c>
@@ -3536,7 +3536,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>51</v>
       </c>
@@ -3562,7 +3562,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>51</v>
       </c>
@@ -3588,7 +3588,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>56</v>
       </c>
@@ -3614,7 +3614,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>56</v>
       </c>
@@ -3640,7 +3640,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>56</v>
       </c>
@@ -3666,7 +3666,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>56</v>
       </c>
@@ -3692,7 +3692,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="48" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>56</v>
       </c>
@@ -3718,7 +3718,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>56</v>
       </c>
@@ -3744,7 +3744,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>63</v>
       </c>
@@ -3770,7 +3770,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>63</v>
       </c>
@@ -3796,7 +3796,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>63</v>
       </c>
@@ -3822,7 +3822,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>63</v>
       </c>
@@ -3848,7 +3848,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>63</v>
       </c>
@@ -3874,7 +3874,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>63</v>
       </c>
@@ -3900,7 +3900,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="56" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>69</v>
       </c>
@@ -3926,7 +3926,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>69</v>
       </c>
@@ -3952,7 +3952,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>69</v>
       </c>
@@ -3978,7 +3978,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="59" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>69</v>
       </c>
@@ -4004,7 +4004,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="60" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>69</v>
       </c>
@@ -4030,7 +4030,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>69</v>
       </c>
@@ -4056,7 +4056,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="62" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>74</v>
       </c>
@@ -4082,7 +4082,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="63" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>74</v>
       </c>
@@ -4108,7 +4108,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="64" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>74</v>
       </c>
@@ -4134,7 +4134,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="65" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>74</v>
       </c>
@@ -4160,7 +4160,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>74</v>
       </c>
@@ -4186,7 +4186,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>74</v>
       </c>
@@ -4212,7 +4212,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>81</v>
       </c>
@@ -4238,7 +4238,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>81</v>
       </c>
@@ -4264,7 +4264,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>81</v>
       </c>
@@ -4290,7 +4290,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>81</v>
       </c>
@@ -4316,7 +4316,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>81</v>
       </c>
@@ -4342,7 +4342,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>81</v>
       </c>
@@ -4368,7 +4368,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>87</v>
       </c>
@@ -4394,7 +4394,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>87</v>
       </c>
@@ -4420,7 +4420,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>87</v>
       </c>
@@ -4446,7 +4446,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>87</v>
       </c>
@@ -4472,7 +4472,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>87</v>
       </c>
@@ -4498,7 +4498,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>87</v>
       </c>
@@ -4524,7 +4524,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>92</v>
       </c>
@@ -4550,7 +4550,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="81" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>92</v>
       </c>
@@ -4576,7 +4576,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="82" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>92</v>
       </c>
@@ -4602,7 +4602,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="83" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>92</v>
       </c>
@@ -4628,7 +4628,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="84" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>92</v>
       </c>
@@ -4654,7 +4654,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="85" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>92</v>
       </c>
@@ -4680,7 +4680,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="86" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>99</v>
       </c>
@@ -4706,7 +4706,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="87" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>99</v>
       </c>
@@ -4732,7 +4732,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="88" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>99</v>
       </c>
@@ -4758,7 +4758,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="89" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>99</v>
       </c>
@@ -4784,7 +4784,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>99</v>
       </c>
@@ -4810,7 +4810,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="91" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>99</v>
       </c>
@@ -4836,7 +4836,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="92" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>104</v>
       </c>
@@ -4862,7 +4862,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="93" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>104</v>
       </c>
@@ -4888,7 +4888,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="94" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>104</v>
       </c>
@@ -4914,7 +4914,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="95" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>104</v>
       </c>
@@ -4940,7 +4940,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="96" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>104</v>
       </c>
@@ -4966,7 +4966,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="97" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>104</v>
       </c>
@@ -4992,7 +4992,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="98" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>107</v>
       </c>
@@ -5018,7 +5018,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="99" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>107</v>
       </c>
@@ -5044,7 +5044,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="100" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>107</v>
       </c>
@@ -5070,7 +5070,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="101" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>107</v>
       </c>
@@ -5096,7 +5096,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="102" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>107</v>
       </c>
@@ -5122,7 +5122,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="103" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>107</v>
       </c>
@@ -5148,7 +5148,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="104" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>114</v>
       </c>
@@ -5174,7 +5174,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="105" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>114</v>
       </c>
@@ -5200,7 +5200,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="106" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>114</v>
       </c>
@@ -5226,7 +5226,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="107" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>114</v>
       </c>
@@ -5252,7 +5252,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="108" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>114</v>
       </c>
@@ -5278,7 +5278,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="109" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>114</v>
       </c>
@@ -5304,7 +5304,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="110" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>120</v>
       </c>
@@ -5330,7 +5330,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="111" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>120</v>
       </c>
@@ -5356,7 +5356,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="112" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>120</v>
       </c>
@@ -5382,7 +5382,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="113" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>120</v>
       </c>
@@ -5408,7 +5408,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="114" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>120</v>
       </c>
@@ -5434,7 +5434,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="115" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>120</v>
       </c>
@@ -5460,7 +5460,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="116" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>126</v>
       </c>
@@ -5486,7 +5486,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="117" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>126</v>
       </c>
@@ -5512,7 +5512,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="118" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>126</v>
       </c>
@@ -5538,7 +5538,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="119" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>126</v>
       </c>
@@ -5564,7 +5564,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="120" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>126</v>
       </c>
@@ -5590,7 +5590,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="121" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>126</v>
       </c>
@@ -5616,7 +5616,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="122" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>132</v>
       </c>
@@ -5642,7 +5642,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="123" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>132</v>
       </c>
@@ -5668,7 +5668,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="124" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>132</v>
       </c>
@@ -5694,7 +5694,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="125" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>132</v>
       </c>
@@ -5720,7 +5720,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="126" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>132</v>
       </c>
@@ -5746,7 +5746,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="127" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>132</v>
       </c>
@@ -5772,7 +5772,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="128" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>137</v>
       </c>
@@ -5798,7 +5798,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="129" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>137</v>
       </c>
@@ -5824,7 +5824,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="130" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>137</v>
       </c>
@@ -5850,7 +5850,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="131" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>137</v>
       </c>
@@ -5876,7 +5876,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="132" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>137</v>
       </c>
@@ -5902,7 +5902,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="133" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>137</v>
       </c>
@@ -5928,7 +5928,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="134" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>140</v>
       </c>
@@ -5954,7 +5954,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="135" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>140</v>
       </c>
@@ -5980,7 +5980,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="136" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>140</v>
       </c>
@@ -6006,7 +6006,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="137" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>140</v>
       </c>
@@ -6032,7 +6032,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="138" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>140</v>
       </c>
@@ -6058,7 +6058,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="139" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>140</v>
       </c>
@@ -6084,7 +6084,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="140" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>146</v>
       </c>
@@ -6110,7 +6110,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="141" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>146</v>
       </c>
@@ -6136,7 +6136,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="142" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>146</v>
       </c>
@@ -6162,7 +6162,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="143" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>146</v>
       </c>
@@ -6188,7 +6188,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="144" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>146</v>
       </c>
@@ -6214,7 +6214,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="145" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>146</v>
       </c>
@@ -6240,7 +6240,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="146" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>150</v>
       </c>
@@ -6266,7 +6266,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="147" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>150</v>
       </c>
@@ -6292,7 +6292,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="148" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>150</v>
       </c>
@@ -6318,7 +6318,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="149" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>150</v>
       </c>
@@ -6344,7 +6344,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="150" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>150</v>
       </c>
@@ -6370,7 +6370,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="151" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>150</v>
       </c>
@@ -6396,7 +6396,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="152" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>152</v>
       </c>
@@ -6422,7 +6422,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="153" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>152</v>
       </c>
@@ -6448,7 +6448,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="154" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>152</v>
       </c>
@@ -6474,7 +6474,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="155" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>152</v>
       </c>
@@ -6500,7 +6500,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="156" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>152</v>
       </c>
@@ -6526,7 +6526,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="157" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>152</v>
       </c>
@@ -6552,7 +6552,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="158" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>156</v>
       </c>
@@ -6578,7 +6578,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="159" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>156</v>
       </c>
@@ -6604,7 +6604,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="160" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>156</v>
       </c>
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="161" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>156</v>
       </c>
@@ -6656,7 +6656,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="162" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>156</v>
       </c>
@@ -6682,7 +6682,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="163" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>156</v>
       </c>
@@ -6708,7 +6708,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="164" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>158</v>
       </c>
@@ -6734,7 +6734,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="165" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>158</v>
       </c>
@@ -6760,7 +6760,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="166" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>158</v>
       </c>
@@ -6786,7 +6786,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="167" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>158</v>
       </c>
@@ -6812,7 +6812,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="168" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>158</v>
       </c>
@@ -6838,7 +6838,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="169" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>158</v>
       </c>
@@ -6864,7 +6864,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="170" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>160</v>
       </c>
@@ -6890,7 +6890,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="171" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>160</v>
       </c>
@@ -6916,7 +6916,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="172" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>160</v>
       </c>
@@ -6942,7 +6942,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="173" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>160</v>
       </c>
@@ -6968,7 +6968,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="174" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>160</v>
       </c>
@@ -6994,7 +6994,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="175" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>160</v>
       </c>
@@ -7020,7 +7020,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="176" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>165</v>
       </c>
@@ -7046,7 +7046,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="177" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>165</v>
       </c>
@@ -7072,7 +7072,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="178" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>165</v>
       </c>
@@ -7098,7 +7098,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="179" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>165</v>
       </c>
@@ -7124,7 +7124,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="180" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>165</v>
       </c>
@@ -7150,7 +7150,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="181" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>165</v>
       </c>
@@ -7176,7 +7176,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="182" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>170</v>
       </c>
@@ -7202,7 +7202,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="183" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>170</v>
       </c>
@@ -7228,7 +7228,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="184" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>170</v>
       </c>
@@ -7254,7 +7254,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="185" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>170</v>
       </c>
@@ -7280,7 +7280,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="186" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>170</v>
       </c>
@@ -7306,7 +7306,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="187" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>170</v>
       </c>
@@ -7332,7 +7332,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="188" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>175</v>
       </c>
@@ -7358,7 +7358,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="189" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>175</v>
       </c>
@@ -7384,7 +7384,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="190" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>175</v>
       </c>
@@ -7410,7 +7410,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="191" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>175</v>
       </c>
@@ -7436,7 +7436,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="192" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>175</v>
       </c>
@@ -7462,7 +7462,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="193" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>175</v>
       </c>
@@ -7488,7 +7488,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="194" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>182</v>
       </c>
@@ -7514,7 +7514,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="195" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>182</v>
       </c>
@@ -7540,7 +7540,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="196" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>182</v>
       </c>
@@ -7592,7 +7592,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="198" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>182</v>
       </c>
@@ -7618,7 +7618,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="199" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>182</v>
       </c>
@@ -7644,7 +7644,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="200" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>185</v>
       </c>
@@ -7670,7 +7670,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="201" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>185</v>
       </c>
@@ -7696,7 +7696,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="202" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>185</v>
       </c>
@@ -7722,7 +7722,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="203" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>185</v>
       </c>
@@ -7748,7 +7748,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="204" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>185</v>
       </c>
@@ -7774,7 +7774,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="205" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>185</v>
       </c>
@@ -7800,7 +7800,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="206" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>186</v>
       </c>
@@ -7826,7 +7826,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="207" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>186</v>
       </c>
@@ -7852,7 +7852,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="208" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>186</v>
       </c>
@@ -7878,7 +7878,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="209" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>186</v>
       </c>
@@ -7904,7 +7904,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="210" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>186</v>
       </c>
@@ -7930,7 +7930,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="211" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>186</v>
       </c>
@@ -7956,7 +7956,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="212" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>187</v>
       </c>
@@ -7982,7 +7982,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="213" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>187</v>
       </c>
@@ -8008,7 +8008,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="214" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>187</v>
       </c>
@@ -8034,7 +8034,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="215" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>187</v>
       </c>
@@ -8060,7 +8060,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="216" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>187</v>
       </c>
@@ -8086,7 +8086,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="217" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>187</v>
       </c>
@@ -8112,7 +8112,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="218" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>188</v>
       </c>
@@ -8138,7 +8138,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="219" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>188</v>
       </c>
@@ -8164,7 +8164,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="220" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>188</v>
       </c>
@@ -8190,7 +8190,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="221" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>188</v>
       </c>
@@ -8216,7 +8216,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="222" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>188</v>
       </c>
@@ -8242,7 +8242,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="223" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>188</v>
       </c>
@@ -8268,7 +8268,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="224" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>190</v>
       </c>
@@ -8294,7 +8294,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="225" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>190</v>
       </c>
@@ -8320,7 +8320,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="226" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>190</v>
       </c>
@@ -8372,7 +8372,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="228" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>190</v>
       </c>
@@ -8398,7 +8398,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="229" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>190</v>
       </c>
@@ -8424,7 +8424,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="230" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>191</v>
       </c>
@@ -8450,7 +8450,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="231" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>191</v>
       </c>
@@ -8476,7 +8476,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="232" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>191</v>
       </c>
@@ -8502,7 +8502,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="233" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>191</v>
       </c>
@@ -8528,7 +8528,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="234" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>191</v>
       </c>
@@ -8554,7 +8554,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="235" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>191</v>
       </c>
@@ -8580,7 +8580,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="236" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>195</v>
       </c>
@@ -8606,7 +8606,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="237" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>195</v>
       </c>
@@ -8632,7 +8632,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="238" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>195</v>
       </c>
@@ -8658,7 +8658,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="239" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>195</v>
       </c>
@@ -8684,7 +8684,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="240" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>195</v>
       </c>
@@ -8710,7 +8710,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="241" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>195</v>
       </c>
@@ -8736,7 +8736,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="242" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>197</v>
       </c>
@@ -8762,7 +8762,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="243" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>197</v>
       </c>
@@ -8788,7 +8788,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="244" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>197</v>
       </c>
@@ -8814,7 +8814,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="245" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>197</v>
       </c>
@@ -8840,7 +8840,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="246" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>197</v>
       </c>
@@ -8866,7 +8866,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="247" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>197</v>
       </c>
@@ -8892,7 +8892,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="248" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>198</v>
       </c>
@@ -8918,7 +8918,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="249" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>198</v>
       </c>
@@ -8944,7 +8944,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="250" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>198</v>
       </c>
@@ -8970,7 +8970,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="251" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>198</v>
       </c>
@@ -8996,7 +8996,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="252" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>198</v>
       </c>
@@ -9022,7 +9022,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="253" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>198</v>
       </c>
@@ -9048,7 +9048,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="254" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>199</v>
       </c>
@@ -9074,7 +9074,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="255" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>199</v>
       </c>
@@ -9100,7 +9100,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="256" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>199</v>
       </c>
@@ -9126,7 +9126,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="257" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>199</v>
       </c>
@@ -9152,7 +9152,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="258" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>199</v>
       </c>
@@ -9178,7 +9178,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="259" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>199</v>
       </c>
@@ -9204,7 +9204,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="260" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>203</v>
       </c>
@@ -9230,7 +9230,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="261" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>203</v>
       </c>
@@ -9256,7 +9256,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="262" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>203</v>
       </c>
@@ -9282,7 +9282,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="263" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>203</v>
       </c>
@@ -9308,7 +9308,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="264" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>203</v>
       </c>
@@ -9334,7 +9334,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="265" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>203</v>
       </c>
@@ -9360,7 +9360,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="266" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>208</v>
       </c>
@@ -9386,7 +9386,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="267" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>208</v>
       </c>
@@ -9412,7 +9412,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="268" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>208</v>
       </c>
@@ -9438,7 +9438,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="269" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>208</v>
       </c>
@@ -9464,7 +9464,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="270" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>208</v>
       </c>
@@ -9490,7 +9490,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="271" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>208</v>
       </c>
@@ -9516,7 +9516,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="272" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>211</v>
       </c>
@@ -9542,7 +9542,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="273" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>211</v>
       </c>
@@ -9568,7 +9568,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="274" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>211</v>
       </c>
@@ -9594,7 +9594,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="275" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>211</v>
       </c>
@@ -9620,7 +9620,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="276" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>211</v>
       </c>
@@ -9646,7 +9646,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="277" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>211</v>
       </c>
@@ -9672,7 +9672,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="278" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>215</v>
       </c>
@@ -9698,7 +9698,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="279" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>215</v>
       </c>
@@ -9724,7 +9724,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="280" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>215</v>
       </c>
@@ -9750,7 +9750,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="281" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>215</v>
       </c>
@@ -9776,7 +9776,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="282" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>215</v>
       </c>
@@ -9802,7 +9802,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="283" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>215</v>
       </c>
@@ -9828,7 +9828,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="284" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>220</v>
       </c>
@@ -9854,7 +9854,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="285" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>220</v>
       </c>
@@ -9880,7 +9880,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="286" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>220</v>
       </c>
@@ -9906,7 +9906,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="287" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>220</v>
       </c>
@@ -9932,7 +9932,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="288" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>220</v>
       </c>
@@ -9958,7 +9958,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="289" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>220</v>
       </c>
@@ -9984,7 +9984,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="290" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>223</v>
       </c>
@@ -10010,7 +10010,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="291" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>223</v>
       </c>
@@ -10036,7 +10036,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="292" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>223</v>
       </c>
@@ -10062,7 +10062,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="293" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>223</v>
       </c>
@@ -10088,7 +10088,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="294" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>223</v>
       </c>
@@ -10114,7 +10114,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="295" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>223</v>
       </c>
@@ -10140,7 +10140,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="296" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>227</v>
       </c>
@@ -10166,7 +10166,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="297" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>227</v>
       </c>
@@ -10192,7 +10192,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="298" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>227</v>
       </c>
@@ -10218,7 +10218,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="299" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>227</v>
       </c>
@@ -10244,7 +10244,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="300" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>227</v>
       </c>
@@ -10270,7 +10270,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="301" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>227</v>
       </c>
@@ -10296,7 +10296,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="302" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>231</v>
       </c>
@@ -10322,7 +10322,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="303" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>231</v>
       </c>
@@ -10348,7 +10348,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="304" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>231</v>
       </c>
@@ -10374,7 +10374,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="305" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>231</v>
       </c>
@@ -10400,7 +10400,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="306" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>231</v>
       </c>
@@ -10426,7 +10426,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="307" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>231</v>
       </c>
@@ -10452,7 +10452,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="308" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>235</v>
       </c>
@@ -10478,7 +10478,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="309" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>235</v>
       </c>
@@ -10504,7 +10504,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="310" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>235</v>
       </c>
@@ -10530,7 +10530,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="311" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>235</v>
       </c>
@@ -10556,7 +10556,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="312" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>235</v>
       </c>
@@ -10582,7 +10582,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="313" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>235</v>
       </c>
@@ -10608,7 +10608,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="314" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>240</v>
       </c>
@@ -10634,7 +10634,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="315" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>240</v>
       </c>
@@ -10660,7 +10660,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="316" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>240</v>
       </c>
@@ -10686,7 +10686,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="317" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>240</v>
       </c>
@@ -10712,7 +10712,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="318" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>240</v>
       </c>
@@ -10738,7 +10738,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="319" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>240</v>
       </c>
@@ -10764,7 +10764,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="320" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>245</v>
       </c>
@@ -10790,7 +10790,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="321" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>245</v>
       </c>
@@ -10816,7 +10816,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="322" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>245</v>
       </c>
@@ -10842,7 +10842,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="323" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>245</v>
       </c>
@@ -10868,7 +10868,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="324" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>245</v>
       </c>
@@ -10894,7 +10894,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="325" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>245</v>
       </c>
@@ -10920,7 +10920,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="326" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>249</v>
       </c>
@@ -10946,7 +10946,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="327" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>249</v>
       </c>
@@ -10972,7 +10972,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="328" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>249</v>
       </c>
@@ -10998,7 +10998,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="329" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>249</v>
       </c>
@@ -11024,7 +11024,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="330" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>249</v>
       </c>
@@ -11050,7 +11050,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="331" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>249</v>
       </c>
@@ -11076,7 +11076,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="332" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>254</v>
       </c>
@@ -11102,7 +11102,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="333" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>254</v>
       </c>
@@ -11128,7 +11128,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="334" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>254</v>
       </c>
@@ -11154,7 +11154,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="335" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>254</v>
       </c>
@@ -11180,7 +11180,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="336" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>254</v>
       </c>
@@ -11206,7 +11206,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="337" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>254</v>
       </c>
@@ -11232,7 +11232,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="338" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>257</v>
       </c>
@@ -11258,7 +11258,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="339" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>257</v>
       </c>
@@ -11284,7 +11284,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="340" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>257</v>
       </c>
@@ -11310,7 +11310,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="341" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>257</v>
       </c>
@@ -11336,7 +11336,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="342" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>257</v>
       </c>
@@ -11362,7 +11362,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="343" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>257</v>
       </c>
@@ -11388,7 +11388,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="344" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>261</v>
       </c>
@@ -11414,7 +11414,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="345" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>261</v>
       </c>
@@ -11440,7 +11440,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="346" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>261</v>
       </c>
@@ -11466,7 +11466,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="347" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>261</v>
       </c>
@@ -11492,7 +11492,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="348" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>261</v>
       </c>
@@ -11518,7 +11518,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="349" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>261</v>
       </c>
@@ -11544,7 +11544,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="350" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>265</v>
       </c>
@@ -11570,7 +11570,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="351" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>265</v>
       </c>
@@ -11596,7 +11596,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="352" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>265</v>
       </c>
@@ -11622,7 +11622,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="353" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>265</v>
       </c>
@@ -11648,7 +11648,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="354" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>265</v>
       </c>
@@ -11674,7 +11674,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="355" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>265</v>
       </c>
@@ -11700,7 +11700,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="356" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>267</v>
       </c>
@@ -11726,7 +11726,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="357" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>267</v>
       </c>
@@ -11752,7 +11752,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="358" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>267</v>
       </c>
@@ -11778,7 +11778,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="359" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>267</v>
       </c>
@@ -11804,7 +11804,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="360" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>267</v>
       </c>
@@ -11830,7 +11830,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="361" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>267</v>
       </c>
@@ -11856,7 +11856,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="362" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>270</v>
       </c>
@@ -11882,7 +11882,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="363" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>270</v>
       </c>
@@ -11908,7 +11908,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="364" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>270</v>
       </c>
@@ -11934,7 +11934,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="365" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>270</v>
       </c>
@@ -11960,7 +11960,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="366" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>270</v>
       </c>
@@ -11986,7 +11986,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="367" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>270</v>
       </c>
@@ -12012,7 +12012,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="368" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>275</v>
       </c>
@@ -12038,7 +12038,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="369" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>275</v>
       </c>
@@ -12064,7 +12064,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="370" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>275</v>
       </c>
@@ -12090,7 +12090,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="371" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>275</v>
       </c>
@@ -12116,7 +12116,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="372" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>275</v>
       </c>
@@ -12142,7 +12142,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="373" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>275</v>
       </c>
@@ -12168,7 +12168,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="374" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>279</v>
       </c>
@@ -12194,7 +12194,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="375" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>279</v>
       </c>
@@ -12220,7 +12220,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="376" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>279</v>
       </c>
@@ -12246,7 +12246,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="377" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>279</v>
       </c>
@@ -12272,7 +12272,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="378" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>279</v>
       </c>
@@ -12298,7 +12298,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="379" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>279</v>
       </c>
@@ -12324,7 +12324,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="380" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>282</v>
       </c>
@@ -12350,7 +12350,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="381" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>282</v>
       </c>
@@ -12376,7 +12376,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="382" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>282</v>
       </c>
@@ -12402,7 +12402,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="383" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>282</v>
       </c>
@@ -12428,7 +12428,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="384" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>282</v>
       </c>
@@ -12454,7 +12454,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="385" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>282</v>
       </c>
@@ -12480,7 +12480,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="386" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>285</v>
       </c>
@@ -12506,7 +12506,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="387" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>285</v>
       </c>
@@ -12532,7 +12532,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="388" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>285</v>
       </c>
@@ -12558,7 +12558,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="389" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>285</v>
       </c>
@@ -12584,7 +12584,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="390" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>285</v>
       </c>
@@ -12610,7 +12610,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="391" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>285</v>
       </c>
@@ -12636,7 +12636,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="392" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>291</v>
       </c>
@@ -12662,7 +12662,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="393" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>291</v>
       </c>
@@ -12688,7 +12688,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="394" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>291</v>
       </c>
@@ -12714,7 +12714,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="395" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>291</v>
       </c>
@@ -12740,7 +12740,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="396" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>291</v>
       </c>
@@ -12766,7 +12766,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="397" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>291</v>
       </c>
@@ -12792,7 +12792,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="398" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>295</v>
       </c>
@@ -12818,7 +12818,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="399" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>295</v>
       </c>
@@ -12844,7 +12844,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="400" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>295</v>
       </c>
@@ -12870,7 +12870,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="401" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>295</v>
       </c>
@@ -12896,7 +12896,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="402" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>295</v>
       </c>
@@ -12922,7 +12922,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="403" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>295</v>
       </c>
@@ -12948,7 +12948,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="404" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>297</v>
       </c>
@@ -12974,7 +12974,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="405" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>297</v>
       </c>
@@ -13000,7 +13000,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="406" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>297</v>
       </c>
@@ -13026,7 +13026,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="407" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>297</v>
       </c>
@@ -13052,7 +13052,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="408" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>297</v>
       </c>
@@ -13078,7 +13078,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="409" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>297</v>
       </c>
@@ -13104,7 +13104,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="410" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>303</v>
       </c>
@@ -13130,7 +13130,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="411" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>303</v>
       </c>
@@ -13156,7 +13156,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="412" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>303</v>
       </c>
@@ -13182,7 +13182,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="413" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>303</v>
       </c>
@@ -13208,7 +13208,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="414" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>303</v>
       </c>
@@ -13234,7 +13234,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="415" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>303</v>
       </c>
@@ -13260,7 +13260,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="416" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>308</v>
       </c>
@@ -13286,7 +13286,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="417" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>308</v>
       </c>
@@ -13312,7 +13312,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="418" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>308</v>
       </c>
@@ -13338,7 +13338,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="419" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>308</v>
       </c>
@@ -13364,7 +13364,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="420" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>308</v>
       </c>
@@ -13390,7 +13390,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="421" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>308</v>
       </c>
@@ -13416,7 +13416,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="422" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>312</v>
       </c>
@@ -13442,7 +13442,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="423" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>312</v>
       </c>
@@ -13468,7 +13468,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="424" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>312</v>
       </c>
@@ -13494,7 +13494,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="425" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>312</v>
       </c>
@@ -13520,7 +13520,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="426" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>312</v>
       </c>
@@ -13546,7 +13546,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="427" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>312</v>
       </c>
@@ -13572,7 +13572,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="428" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>316</v>
       </c>
@@ -13598,7 +13598,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="429" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>316</v>
       </c>
@@ -13624,7 +13624,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="430" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>316</v>
       </c>
@@ -13650,7 +13650,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="431" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>316</v>
       </c>
@@ -13676,7 +13676,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="432" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>316</v>
       </c>
@@ -13702,7 +13702,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="433" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>316</v>
       </c>
@@ -13728,7 +13728,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="434" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>319</v>
       </c>
@@ -13754,7 +13754,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="435" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>319</v>
       </c>
@@ -13780,7 +13780,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="436" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>319</v>
       </c>
@@ -13806,7 +13806,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="437" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>319</v>
       </c>
@@ -13832,7 +13832,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="438" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>319</v>
       </c>
@@ -13858,7 +13858,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="439" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>319</v>
       </c>
@@ -13884,7 +13884,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="440" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>322</v>
       </c>
@@ -13910,7 +13910,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="441" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>322</v>
       </c>
@@ -13936,7 +13936,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="442" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>322</v>
       </c>
@@ -13962,7 +13962,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="443" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>322</v>
       </c>
@@ -13988,7 +13988,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="444" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>322</v>
       </c>
@@ -14014,7 +14014,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="445" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>322</v>
       </c>
@@ -14040,7 +14040,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="446" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>324</v>
       </c>
@@ -14066,7 +14066,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="447" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>324</v>
       </c>
@@ -14092,7 +14092,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="448" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>324</v>
       </c>
@@ -14118,7 +14118,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="449" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>324</v>
       </c>
@@ -14144,7 +14144,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="450" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>324</v>
       </c>
@@ -14170,7 +14170,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="451" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>324</v>
       </c>
@@ -14196,7 +14196,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="452" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>326</v>
       </c>
@@ -14222,7 +14222,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="453" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>326</v>
       </c>
@@ -14248,7 +14248,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="454" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>326</v>
       </c>
@@ -14274,7 +14274,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="455" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>326</v>
       </c>
@@ -14300,7 +14300,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="456" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>326</v>
       </c>
@@ -14326,7 +14326,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="457" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>326</v>
       </c>
@@ -14352,7 +14352,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="458" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>327</v>
       </c>
@@ -14378,7 +14378,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="459" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>327</v>
       </c>
@@ -14404,7 +14404,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="460" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>327</v>
       </c>
@@ -14430,7 +14430,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="461" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>327</v>
       </c>
@@ -14456,7 +14456,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="462" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>327</v>
       </c>
@@ -14482,7 +14482,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="463" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>327</v>
       </c>
@@ -14508,7 +14508,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="464" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>332</v>
       </c>
@@ -14534,7 +14534,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="465" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>332</v>
       </c>
@@ -14560,7 +14560,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="466" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>332</v>
       </c>
@@ -14586,7 +14586,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="467" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>332</v>
       </c>
@@ -14612,7 +14612,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="468" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>332</v>
       </c>
@@ -14638,7 +14638,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="469" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>332</v>
       </c>
@@ -14664,7 +14664,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="470" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>335</v>
       </c>
@@ -14690,7 +14690,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="471" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>335</v>
       </c>
@@ -14716,7 +14716,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="472" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>335</v>
       </c>
@@ -14742,7 +14742,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="473" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>335</v>
       </c>
@@ -14768,7 +14768,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="474" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>335</v>
       </c>
@@ -14794,7 +14794,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="475" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>335</v>
       </c>
@@ -14820,7 +14820,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="476" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>338</v>
       </c>
@@ -14846,7 +14846,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="477" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>338</v>
       </c>
@@ -14872,7 +14872,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="478" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>338</v>
       </c>
@@ -14898,7 +14898,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="479" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>338</v>
       </c>
@@ -14924,7 +14924,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="480" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>338</v>
       </c>
@@ -14950,7 +14950,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="481" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>338</v>
       </c>
@@ -14976,7 +14976,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="482" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>342</v>
       </c>
@@ -15002,7 +15002,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="483" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
         <v>342</v>
       </c>
@@ -15028,7 +15028,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="484" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
         <v>342</v>
       </c>
@@ -15054,7 +15054,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="485" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
         <v>342</v>
       </c>
@@ -15080,7 +15080,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="486" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
         <v>342</v>
       </c>
@@ -15106,7 +15106,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="487" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
         <v>342</v>
       </c>
@@ -15132,7 +15132,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="488" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
         <v>346</v>
       </c>
@@ -15158,7 +15158,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="489" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
         <v>346</v>
       </c>
@@ -15184,7 +15184,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="490" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
         <v>346</v>
       </c>
@@ -15210,7 +15210,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="491" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
         <v>346</v>
       </c>
@@ -15236,7 +15236,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="492" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
         <v>346</v>
       </c>
@@ -15262,7 +15262,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="493" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
         <v>346</v>
       </c>
@@ -15288,7 +15288,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="494" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
         <v>350</v>
       </c>
@@ -15314,7 +15314,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="495" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
         <v>350</v>
       </c>
@@ -15340,7 +15340,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="496" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
         <v>350</v>
       </c>
@@ -15366,7 +15366,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="497" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
         <v>350</v>
       </c>
@@ -15392,7 +15392,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="498" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
         <v>350</v>
       </c>
@@ -15418,7 +15418,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="499" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
         <v>350</v>
       </c>
@@ -15444,7 +15444,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="500" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>351</v>
       </c>
@@ -15470,7 +15470,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="501" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
         <v>351</v>
       </c>
@@ -15496,7 +15496,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="502" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
         <v>351</v>
       </c>
@@ -15522,7 +15522,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="503" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
         <v>351</v>
       </c>
@@ -15548,7 +15548,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="504" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
         <v>351</v>
       </c>
@@ -15574,7 +15574,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="505" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
         <v>351</v>
       </c>
@@ -15600,7 +15600,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="506" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
         <v>354</v>
       </c>
@@ -15626,7 +15626,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="507" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
         <v>354</v>
       </c>
@@ -15652,7 +15652,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="508" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
         <v>354</v>
       </c>
@@ -15678,7 +15678,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="509" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
         <v>354</v>
       </c>
@@ -15704,7 +15704,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="510" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
         <v>354</v>
       </c>
@@ -15730,7 +15730,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="511" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
         <v>354</v>
       </c>
@@ -15756,7 +15756,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="512" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
         <v>356</v>
       </c>
@@ -15782,7 +15782,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="513" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
         <v>356</v>
       </c>
@@ -15808,7 +15808,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="514" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
         <v>356</v>
       </c>
@@ -15834,7 +15834,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="515" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
         <v>356</v>
       </c>
@@ -15860,7 +15860,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="516" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
         <v>356</v>
       </c>
@@ -15886,7 +15886,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="517" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
         <v>356</v>
       </c>
@@ -15912,7 +15912,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="518" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
         <v>358</v>
       </c>
@@ -15938,7 +15938,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="519" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
         <v>358</v>
       </c>
@@ -15964,7 +15964,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="520" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
         <v>358</v>
       </c>
@@ -15990,7 +15990,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="521" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
         <v>358</v>
       </c>
@@ -16016,7 +16016,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="522" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
         <v>358</v>
       </c>
@@ -16042,7 +16042,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="523" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
         <v>358</v>
       </c>
@@ -16068,7 +16068,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="524" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
         <v>360</v>
       </c>
@@ -16094,7 +16094,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="525" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
         <v>360</v>
       </c>
@@ -16120,7 +16120,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="526" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
         <v>360</v>
       </c>
@@ -16146,7 +16146,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="527" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
         <v>360</v>
       </c>
@@ -16172,7 +16172,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="528" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
         <v>360</v>
       </c>
@@ -16198,7 +16198,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="529" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
         <v>360</v>
       </c>
@@ -16224,7 +16224,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="530" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
         <v>364</v>
       </c>
@@ -16250,7 +16250,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="531" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
         <v>364</v>
       </c>
@@ -16276,7 +16276,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="532" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
         <v>364</v>
       </c>
@@ -16302,7 +16302,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="533" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
         <v>364</v>
       </c>
@@ -16328,7 +16328,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="534" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
         <v>364</v>
       </c>
@@ -16354,7 +16354,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="535" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
         <v>364</v>
       </c>
@@ -16380,7 +16380,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="536" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
         <v>366</v>
       </c>
@@ -16406,7 +16406,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="537" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
         <v>366</v>
       </c>
@@ -16432,7 +16432,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="538" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
         <v>366</v>
       </c>
@@ -16458,7 +16458,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="539" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
         <v>366</v>
       </c>
@@ -16484,7 +16484,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="540" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
         <v>366</v>
       </c>
@@ -16510,7 +16510,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="541" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
         <v>366</v>
       </c>
@@ -16536,7 +16536,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="542" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
         <v>369</v>
       </c>
@@ -16562,7 +16562,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="543" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
         <v>369</v>
       </c>
@@ -16588,7 +16588,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="544" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
         <v>369</v>
       </c>
@@ -16614,7 +16614,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="545" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
         <v>369</v>
       </c>
@@ -16640,7 +16640,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="546" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
         <v>369</v>
       </c>
@@ -16666,7 +16666,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="547" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
         <v>369</v>
       </c>
@@ -16692,7 +16692,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="548" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
         <v>372</v>
       </c>
@@ -16718,7 +16718,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="549" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
         <v>372</v>
       </c>
@@ -16744,7 +16744,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="550" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
         <v>372</v>
       </c>
@@ -16770,7 +16770,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="551" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
         <v>372</v>
       </c>
@@ -16796,7 +16796,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="552" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
         <v>372</v>
       </c>
@@ -16822,7 +16822,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="553" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
         <v>372</v>
       </c>
@@ -16848,7 +16848,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="554" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
         <v>376</v>
       </c>
@@ -16874,7 +16874,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="555" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
         <v>376</v>
       </c>
@@ -16900,7 +16900,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="556" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
         <v>376</v>
       </c>
@@ -16926,7 +16926,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="557" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
         <v>376</v>
       </c>
@@ -16952,7 +16952,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="558" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
         <v>376</v>
       </c>
@@ -16978,7 +16978,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="559" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
         <v>376</v>
       </c>
@@ -17004,7 +17004,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="560" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
         <v>377</v>
       </c>
@@ -17030,7 +17030,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="561" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
         <v>377</v>
       </c>
@@ -17056,7 +17056,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="562" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
         <v>377</v>
       </c>
@@ -17082,7 +17082,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="563" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
         <v>377</v>
       </c>
@@ -17108,7 +17108,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="564" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
         <v>377</v>
       </c>
@@ -17134,7 +17134,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="565" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
         <v>377</v>
       </c>
@@ -17160,7 +17160,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="566" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
         <v>378</v>
       </c>
@@ -17186,7 +17186,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="567" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
         <v>378</v>
       </c>
@@ -17212,7 +17212,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="568" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
         <v>378</v>
       </c>
@@ -17238,7 +17238,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="569" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
         <v>378</v>
       </c>
@@ -17264,7 +17264,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="570" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
         <v>378</v>
       </c>
@@ -17290,7 +17290,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="571" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
         <v>378</v>
       </c>
@@ -17316,7 +17316,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="572" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
         <v>382</v>
       </c>
@@ -17342,7 +17342,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="573" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
         <v>382</v>
       </c>
@@ -17368,7 +17368,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="574" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
         <v>382</v>
       </c>
@@ -17394,7 +17394,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="575" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
         <v>382</v>
       </c>
@@ -17420,7 +17420,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="576" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
         <v>382</v>
       </c>
@@ -17446,7 +17446,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="577" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
         <v>382</v>
       </c>
@@ -17472,7 +17472,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="578" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
         <v>386</v>
       </c>
@@ -17498,7 +17498,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="579" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
         <v>386</v>
       </c>
@@ -17524,7 +17524,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="580" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
         <v>386</v>
       </c>
@@ -17550,7 +17550,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="581" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
         <v>386</v>
       </c>
@@ -17576,7 +17576,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="582" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
         <v>386</v>
       </c>
@@ -17602,7 +17602,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="583" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
         <v>386</v>
       </c>
@@ -17628,7 +17628,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="584" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
         <v>390</v>
       </c>
@@ -17654,7 +17654,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="585" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
         <v>390</v>
       </c>
@@ -17680,7 +17680,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="586" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
         <v>390</v>
       </c>
@@ -17706,7 +17706,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="587" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
         <v>390</v>
       </c>
@@ -17732,7 +17732,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="588" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
         <v>390</v>
       </c>
@@ -17758,7 +17758,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="589" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
         <v>390</v>
       </c>
@@ -17784,7 +17784,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="590" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
         <v>392</v>
       </c>
@@ -17810,7 +17810,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="591" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
         <v>392</v>
       </c>
@@ -17836,7 +17836,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="592" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
         <v>392</v>
       </c>
@@ -17862,7 +17862,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="593" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
         <v>392</v>
       </c>
@@ -17888,7 +17888,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="594" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
         <v>392</v>
       </c>
@@ -17914,7 +17914,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="595" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
         <v>392</v>
       </c>
@@ -17940,7 +17940,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="596" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
         <v>397</v>
       </c>
@@ -17966,7 +17966,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="597" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
         <v>397</v>
       </c>
@@ -17992,7 +17992,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="598" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
         <v>397</v>
       </c>
@@ -18018,7 +18018,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="599" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
         <v>397</v>
       </c>
@@ -18044,7 +18044,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="600" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
         <v>397</v>
       </c>
@@ -18070,7 +18070,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="601" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
         <v>397</v>
       </c>
@@ -18096,7 +18096,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="602" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
         <v>399</v>
       </c>
@@ -18122,7 +18122,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="603" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
         <v>399</v>
       </c>
@@ -18148,7 +18148,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="604" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
         <v>399</v>
       </c>
@@ -18174,7 +18174,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="605" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
         <v>399</v>
       </c>
@@ -18200,7 +18200,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="606" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
         <v>399</v>
       </c>
@@ -18226,7 +18226,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="607" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
         <v>399</v>
       </c>
@@ -18252,7 +18252,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="608" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
         <v>403</v>
       </c>
@@ -18278,7 +18278,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="609" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
         <v>403</v>
       </c>
@@ -18304,7 +18304,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="610" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
         <v>403</v>
       </c>
@@ -18330,7 +18330,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="611" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
         <v>403</v>
       </c>
@@ -18356,7 +18356,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="612" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
         <v>403</v>
       </c>
@@ -18382,7 +18382,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="613" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
         <v>403</v>
       </c>
@@ -18408,7 +18408,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="614" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
         <v>408</v>
       </c>
@@ -18434,7 +18434,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="615" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
         <v>408</v>
       </c>
@@ -18460,7 +18460,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="616" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
         <v>408</v>
       </c>
@@ -18486,7 +18486,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="617" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
         <v>408</v>
       </c>
@@ -18512,7 +18512,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="618" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
         <v>408</v>
       </c>
@@ -18538,7 +18538,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="619" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
         <v>408</v>
       </c>
@@ -18564,7 +18564,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="620" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
         <v>411</v>
       </c>
@@ -18590,7 +18590,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="621" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
         <v>411</v>
       </c>
@@ -18616,7 +18616,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="622" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
         <v>411</v>
       </c>
@@ -18642,7 +18642,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="623" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
         <v>411</v>
       </c>
@@ -18668,7 +18668,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="624" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
         <v>411</v>
       </c>
@@ -18694,7 +18694,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="625" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
         <v>411</v>
       </c>
@@ -18720,7 +18720,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="626" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
         <v>412</v>
       </c>
@@ -18746,7 +18746,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="627" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
         <v>412</v>
       </c>
@@ -18772,7 +18772,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="628" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
         <v>412</v>
       </c>
@@ -18798,7 +18798,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="629" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
         <v>412</v>
       </c>
@@ -18824,7 +18824,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="630" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
         <v>412</v>
       </c>
@@ -18850,7 +18850,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="631" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
         <v>412</v>
       </c>
@@ -18876,7 +18876,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="632" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
         <v>414</v>
       </c>
@@ -18902,7 +18902,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="633" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
         <v>414</v>
       </c>
@@ -18928,7 +18928,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="634" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
         <v>414</v>
       </c>
@@ -18954,7 +18954,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="635" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
         <v>414</v>
       </c>
@@ -18980,7 +18980,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="636" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
         <v>414</v>
       </c>
@@ -19006,7 +19006,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="637" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
         <v>414</v>
       </c>
@@ -19032,7 +19032,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="638" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
         <v>416</v>
       </c>
@@ -19058,7 +19058,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="639" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
         <v>416</v>
       </c>
@@ -19084,7 +19084,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="640" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
         <v>416</v>
       </c>
@@ -19110,7 +19110,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="641" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
         <v>416</v>
       </c>
@@ -19136,7 +19136,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="642" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
         <v>416</v>
       </c>
@@ -19162,7 +19162,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="643" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
         <v>416</v>
       </c>
@@ -19188,7 +19188,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="644" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
         <v>421</v>
       </c>
@@ -19214,7 +19214,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="645" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
         <v>421</v>
       </c>
@@ -19240,7 +19240,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="646" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
         <v>421</v>
       </c>
@@ -19266,7 +19266,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="647" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
         <v>421</v>
       </c>
@@ -19292,7 +19292,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="648" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
         <v>421</v>
       </c>
@@ -19318,7 +19318,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="649" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
         <v>421</v>
       </c>
@@ -19344,7 +19344,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="650" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
         <v>423</v>
       </c>
@@ -19370,7 +19370,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="651" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
         <v>423</v>
       </c>
@@ -19396,7 +19396,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="652" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
         <v>423</v>
       </c>
@@ -19422,7 +19422,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="653" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
         <v>423</v>
       </c>
@@ -19448,7 +19448,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="654" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
         <v>423</v>
       </c>
@@ -19474,7 +19474,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="655" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
         <v>423</v>
       </c>
@@ -19500,7 +19500,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="656" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
         <v>425</v>
       </c>
@@ -19526,7 +19526,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="657" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
         <v>425</v>
       </c>
@@ -19552,7 +19552,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="658" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
         <v>425</v>
       </c>
@@ -19578,7 +19578,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="659" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
         <v>425</v>
       </c>
@@ -19604,7 +19604,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="660" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
         <v>425</v>
       </c>
@@ -19630,7 +19630,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="661" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
         <v>425</v>
       </c>
@@ -19656,7 +19656,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="662" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
         <v>431</v>
       </c>
@@ -19682,7 +19682,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="663" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
         <v>431</v>
       </c>
@@ -19708,7 +19708,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="664" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
         <v>431</v>
       </c>
@@ -19734,7 +19734,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="665" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
         <v>431</v>
       </c>
@@ -19760,7 +19760,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="666" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
         <v>431</v>
       </c>
@@ -19786,7 +19786,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="667" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
         <v>431</v>
       </c>
@@ -19812,7 +19812,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="668" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
         <v>434</v>
       </c>
@@ -19838,7 +19838,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="669" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
         <v>434</v>
       </c>
@@ -19864,7 +19864,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="670" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
         <v>434</v>
       </c>
@@ -19890,7 +19890,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="671" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
         <v>434</v>
       </c>
@@ -19916,7 +19916,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="672" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
         <v>434</v>
       </c>
@@ -19942,7 +19942,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="673" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
         <v>434</v>
       </c>
@@ -19968,7 +19968,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="674" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
         <v>435</v>
       </c>
@@ -19994,7 +19994,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="675" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
         <v>435</v>
       </c>
@@ -20020,7 +20020,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="676" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
         <v>435</v>
       </c>
@@ -20046,7 +20046,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="677" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
         <v>435</v>
       </c>
@@ -20072,7 +20072,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="678" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
         <v>435</v>
       </c>
@@ -20098,7 +20098,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="679" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
         <v>435</v>
       </c>
@@ -20124,7 +20124,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="680" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
         <v>437</v>
       </c>
@@ -20150,7 +20150,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="681" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
         <v>437</v>
       </c>
@@ -20176,7 +20176,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="682" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
         <v>437</v>
       </c>
@@ -20202,7 +20202,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="683" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
         <v>437</v>
       </c>
@@ -20228,7 +20228,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="684" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
         <v>437</v>
       </c>
@@ -20254,7 +20254,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="685" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
         <v>437</v>
       </c>
@@ -20280,7 +20280,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="686" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
         <v>438</v>
       </c>
@@ -20306,7 +20306,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="687" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
         <v>438</v>
       </c>
@@ -20332,7 +20332,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="688" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
         <v>438</v>
       </c>
@@ -20358,7 +20358,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="689" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
         <v>438</v>
       </c>
@@ -20384,7 +20384,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="690" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
         <v>438</v>
       </c>
@@ -20410,7 +20410,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="691" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
         <v>438</v>
       </c>
@@ -20436,7 +20436,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="692" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
         <v>440</v>
       </c>
@@ -20462,7 +20462,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="693" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
         <v>440</v>
       </c>
@@ -20488,7 +20488,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="694" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
         <v>440</v>
       </c>
@@ -20514,7 +20514,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="695" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
         <v>440</v>
       </c>
@@ -20540,7 +20540,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="696" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
         <v>440</v>
       </c>
@@ -20566,7 +20566,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="697" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
         <v>440</v>
       </c>
@@ -20592,7 +20592,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="698" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
         <v>441</v>
       </c>
@@ -20618,7 +20618,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="699" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
         <v>441</v>
       </c>
@@ -20644,7 +20644,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="700" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
         <v>441</v>
       </c>
@@ -20670,7 +20670,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="701" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
         <v>441</v>
       </c>
@@ -20696,7 +20696,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="702" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A702" t="s">
         <v>441</v>
       </c>
@@ -20722,7 +20722,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="703" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
         <v>441</v>
       </c>
@@ -20748,7 +20748,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="704" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A704" t="s">
         <v>443</v>
       </c>
@@ -20774,7 +20774,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="705" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
         <v>443</v>
       </c>
@@ -20800,7 +20800,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="706" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
         <v>443</v>
       </c>
@@ -20826,7 +20826,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="707" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
         <v>443</v>
       </c>
@@ -20852,7 +20852,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="708" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A708" t="s">
         <v>443</v>
       </c>
@@ -20878,7 +20878,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="709" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A709" t="s">
         <v>443</v>
       </c>
@@ -20904,7 +20904,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="710" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
         <v>446</v>
       </c>
@@ -20930,7 +20930,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="711" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A711" t="s">
         <v>446</v>
       </c>
@@ -20956,7 +20956,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="712" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A712" t="s">
         <v>446</v>
       </c>
@@ -20982,7 +20982,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="713" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A713" t="s">
         <v>446</v>
       </c>
@@ -21008,7 +21008,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="714" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A714" t="s">
         <v>446</v>
       </c>
@@ -21034,7 +21034,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="715" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A715" t="s">
         <v>446</v>
       </c>
@@ -21060,7 +21060,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="716" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A716" t="s">
         <v>448</v>
       </c>
@@ -21086,7 +21086,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="717" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A717" t="s">
         <v>448</v>
       </c>
@@ -21112,7 +21112,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="718" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A718" t="s">
         <v>448</v>
       </c>
@@ -21138,7 +21138,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="719" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A719" t="s">
         <v>448</v>
       </c>
@@ -21164,7 +21164,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="720" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A720" t="s">
         <v>448</v>
       </c>
@@ -21190,7 +21190,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="721" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A721" t="s">
         <v>448</v>
       </c>
@@ -21216,7 +21216,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="722" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A722" t="s">
         <v>452</v>
       </c>
@@ -21242,7 +21242,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="723" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A723" t="s">
         <v>452</v>
       </c>
@@ -21268,7 +21268,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="724" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A724" t="s">
         <v>452</v>
       </c>
@@ -21294,7 +21294,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="725" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A725" t="s">
         <v>452</v>
       </c>
@@ -21320,7 +21320,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="726" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A726" t="s">
         <v>452</v>
       </c>
@@ -21346,7 +21346,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="727" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A727" t="s">
         <v>452</v>
       </c>
@@ -21372,7 +21372,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="728" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A728" t="s">
         <v>455</v>
       </c>
@@ -21398,7 +21398,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="729" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A729" t="s">
         <v>455</v>
       </c>
@@ -21424,7 +21424,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="730" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A730" t="s">
         <v>455</v>
       </c>
@@ -21450,7 +21450,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="731" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A731" t="s">
         <v>455</v>
       </c>
@@ -21476,7 +21476,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="732" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A732" t="s">
         <v>455</v>
       </c>
@@ -21502,7 +21502,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="733" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A733" t="s">
         <v>455</v>
       </c>
@@ -21528,7 +21528,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="734" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A734" t="s">
         <v>457</v>
       </c>
@@ -21554,7 +21554,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="735" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A735" t="s">
         <v>457</v>
       </c>
@@ -21580,7 +21580,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="736" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A736" t="s">
         <v>457</v>
       </c>
@@ -21606,7 +21606,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="737" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A737" t="s">
         <v>457</v>
       </c>
@@ -21632,7 +21632,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="738" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A738" t="s">
         <v>457</v>
       </c>
@@ -21658,7 +21658,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="739" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A739" t="s">
         <v>457</v>
       </c>
@@ -21684,7 +21684,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="740" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A740" t="s">
         <v>459</v>
       </c>
@@ -21710,7 +21710,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="741" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A741" t="s">
         <v>459</v>
       </c>
@@ -21736,7 +21736,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="742" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A742" t="s">
         <v>459</v>
       </c>
@@ -21762,7 +21762,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="743" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A743" t="s">
         <v>459</v>
       </c>
@@ -21788,7 +21788,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="744" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A744" t="s">
         <v>459</v>
       </c>
@@ -21814,7 +21814,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="745" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A745" t="s">
         <v>459</v>
       </c>
@@ -21840,7 +21840,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="746" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A746" t="s">
         <v>464</v>
       </c>
@@ -21866,7 +21866,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="747" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A747" t="s">
         <v>464</v>
       </c>
@@ -21892,7 +21892,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="748" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A748" t="s">
         <v>464</v>
       </c>
@@ -21918,7 +21918,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="749" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A749" t="s">
         <v>464</v>
       </c>
@@ -21944,7 +21944,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="750" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A750" t="s">
         <v>464</v>
       </c>
@@ -21970,7 +21970,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="751" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A751" t="s">
         <v>464</v>
       </c>
@@ -21996,7 +21996,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="752" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A752" t="s">
         <v>467</v>
       </c>
@@ -22022,7 +22022,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="753" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A753" t="s">
         <v>467</v>
       </c>
@@ -22048,7 +22048,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="754" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A754" t="s">
         <v>467</v>
       </c>
@@ -22074,7 +22074,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="755" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A755" t="s">
         <v>467</v>
       </c>
@@ -22100,7 +22100,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="756" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A756" t="s">
         <v>467</v>
       </c>
@@ -22126,7 +22126,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="757" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A757" t="s">
         <v>467</v>
       </c>
@@ -22152,7 +22152,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="758" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A758" t="s">
         <v>469</v>
       </c>
@@ -22178,7 +22178,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="759" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A759" t="s">
         <v>469</v>
       </c>
@@ -22204,7 +22204,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="760" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A760" t="s">
         <v>469</v>
       </c>
@@ -22230,7 +22230,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="761" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A761" t="s">
         <v>469</v>
       </c>
@@ -22256,7 +22256,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="762" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A762" t="s">
         <v>469</v>
       </c>
@@ -22282,7 +22282,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="763" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A763" t="s">
         <v>469</v>
       </c>
@@ -22308,7 +22308,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="764" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A764" t="s">
         <v>471</v>
       </c>
@@ -22334,7 +22334,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="765" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A765" t="s">
         <v>471</v>
       </c>
@@ -22360,7 +22360,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="766" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A766" t="s">
         <v>471</v>
       </c>
@@ -22386,7 +22386,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="767" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A767" t="s">
         <v>471</v>
       </c>
@@ -22412,7 +22412,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="768" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A768" t="s">
         <v>471</v>
       </c>
@@ -22438,7 +22438,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="769" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A769" t="s">
         <v>471</v>
       </c>
@@ -22464,7 +22464,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="770" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A770" t="s">
         <v>472</v>
       </c>
@@ -22490,7 +22490,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="771" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A771" t="s">
         <v>472</v>
       </c>
@@ -22516,7 +22516,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="772" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A772" t="s">
         <v>472</v>
       </c>
@@ -22542,7 +22542,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="773" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A773" t="s">
         <v>472</v>
       </c>
@@ -22568,7 +22568,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="774" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A774" t="s">
         <v>472</v>
       </c>
@@ -22594,7 +22594,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="775" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A775" t="s">
         <v>472</v>
       </c>
@@ -22620,7 +22620,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="776" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A776" t="s">
         <v>475</v>
       </c>
@@ -22646,7 +22646,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="777" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A777" t="s">
         <v>475</v>
       </c>
@@ -22672,7 +22672,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="778" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A778" t="s">
         <v>475</v>
       </c>
@@ -22698,7 +22698,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="779" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A779" t="s">
         <v>475</v>
       </c>
@@ -22724,7 +22724,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="780" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A780" t="s">
         <v>475</v>
       </c>
@@ -22750,7 +22750,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="781" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A781" t="s">
         <v>475</v>
       </c>
@@ -22776,7 +22776,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="782" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A782" t="s">
         <v>477</v>
       </c>
@@ -22802,7 +22802,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="783" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A783" t="s">
         <v>477</v>
       </c>
@@ -22828,7 +22828,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="784" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A784" t="s">
         <v>477</v>
       </c>
@@ -22854,7 +22854,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="785" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A785" t="s">
         <v>477</v>
       </c>
@@ -22880,7 +22880,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="786" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A786" t="s">
         <v>477</v>
       </c>
@@ -22906,7 +22906,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="787" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A787" t="s">
         <v>477</v>
       </c>
@@ -22932,7 +22932,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="788" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A788" t="s">
         <v>481</v>
       </c>
@@ -22958,7 +22958,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="789" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A789" t="s">
         <v>481</v>
       </c>
@@ -22984,7 +22984,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="790" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A790" t="s">
         <v>481</v>
       </c>
@@ -23010,7 +23010,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="791" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A791" t="s">
         <v>481</v>
       </c>
@@ -23036,7 +23036,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="792" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A792" t="s">
         <v>481</v>
       </c>
@@ -23062,7 +23062,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="793" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A793" t="s">
         <v>481</v>
       </c>
@@ -23088,7 +23088,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="794" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A794" t="s">
         <v>485</v>
       </c>
@@ -23114,7 +23114,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="795" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A795" t="s">
         <v>485</v>
       </c>
@@ -23140,7 +23140,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="796" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A796" t="s">
         <v>485</v>
       </c>
@@ -23166,7 +23166,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="797" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A797" t="s">
         <v>485</v>
       </c>
@@ -23192,7 +23192,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="798" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A798" t="s">
         <v>485</v>
       </c>
@@ -23218,7 +23218,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="799" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A799" t="s">
         <v>485</v>
       </c>
@@ -23244,7 +23244,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="800" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A800" t="s">
         <v>489</v>
       </c>
@@ -23270,7 +23270,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="801" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A801" t="s">
         <v>489</v>
       </c>
@@ -23296,7 +23296,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="802" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A802" t="s">
         <v>489</v>
       </c>
@@ -23322,7 +23322,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="803" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A803" t="s">
         <v>489</v>
       </c>
@@ -23348,7 +23348,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="804" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A804" t="s">
         <v>489</v>
       </c>
@@ -23374,7 +23374,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="805" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A805" t="s">
         <v>489</v>
       </c>
@@ -23400,7 +23400,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="806" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A806" t="s">
         <v>493</v>
       </c>
@@ -23426,7 +23426,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="807" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A807" t="s">
         <v>493</v>
       </c>
@@ -23452,7 +23452,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="808" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A808" t="s">
         <v>493</v>
       </c>
@@ -23478,7 +23478,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="809" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A809" t="s">
         <v>493</v>
       </c>
@@ -23504,7 +23504,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="810" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A810" t="s">
         <v>493</v>
       </c>
@@ -23530,7 +23530,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="811" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A811" t="s">
         <v>493</v>
       </c>
@@ -23556,7 +23556,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="812" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A812" t="s">
         <v>498</v>
       </c>
@@ -23582,7 +23582,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="813" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A813" t="s">
         <v>498</v>
       </c>
@@ -23608,7 +23608,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="814" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A814" t="s">
         <v>498</v>
       </c>
@@ -23634,7 +23634,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="815" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A815" t="s">
         <v>498</v>
       </c>
@@ -23660,7 +23660,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="816" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A816" t="s">
         <v>498</v>
       </c>
@@ -23686,7 +23686,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="817" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A817" t="s">
         <v>498</v>
       </c>
@@ -23712,7 +23712,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="818" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A818" t="s">
         <v>500</v>
       </c>
@@ -23738,7 +23738,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="819" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A819" t="s">
         <v>500</v>
       </c>
@@ -23764,7 +23764,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="820" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A820" t="s">
         <v>500</v>
       </c>
@@ -23790,7 +23790,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="821" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A821" t="s">
         <v>500</v>
       </c>
@@ -23816,7 +23816,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="822" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A822" t="s">
         <v>500</v>
       </c>
@@ -23842,7 +23842,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="823" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A823" t="s">
         <v>500</v>
       </c>
@@ -23868,7 +23868,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="824" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A824" t="s">
         <v>501</v>
       </c>
@@ -23894,7 +23894,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="825" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A825" t="s">
         <v>501</v>
       </c>
@@ -23920,7 +23920,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="826" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A826" t="s">
         <v>501</v>
       </c>
@@ -23946,7 +23946,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="827" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A827" t="s">
         <v>501</v>
       </c>
@@ -23972,7 +23972,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="828" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A828" t="s">
         <v>501</v>
       </c>
@@ -23998,7 +23998,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="829" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A829" t="s">
         <v>501</v>
       </c>
@@ -24024,7 +24024,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="830" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A830" t="s">
         <v>503</v>
       </c>
@@ -24050,7 +24050,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="831" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A831" t="s">
         <v>503</v>
       </c>
@@ -24076,7 +24076,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="832" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A832" t="s">
         <v>503</v>
       </c>
@@ -24102,7 +24102,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="833" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A833" t="s">
         <v>503</v>
       </c>
@@ -24128,7 +24128,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="834" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A834" t="s">
         <v>503</v>
       </c>
@@ -24154,7 +24154,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="835" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A835" t="s">
         <v>503</v>
       </c>
@@ -24180,7 +24180,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="836" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A836" t="s">
         <v>506</v>
       </c>
@@ -24206,7 +24206,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="837" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A837" t="s">
         <v>506</v>
       </c>
@@ -24232,7 +24232,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="838" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A838" t="s">
         <v>506</v>
       </c>
@@ -24258,7 +24258,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="839" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A839" t="s">
         <v>506</v>
       </c>
@@ -24284,7 +24284,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="840" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A840" t="s">
         <v>506</v>
       </c>
@@ -24310,7 +24310,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="841" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A841" t="s">
         <v>506</v>
       </c>
@@ -24336,7 +24336,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="842" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A842" t="s">
         <v>509</v>
       </c>
@@ -24362,7 +24362,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="843" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A843" t="s">
         <v>509</v>
       </c>
@@ -24388,7 +24388,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="844" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A844" t="s">
         <v>509</v>
       </c>
@@ -24414,7 +24414,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="845" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A845" t="s">
         <v>509</v>
       </c>
@@ -24440,7 +24440,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="846" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A846" t="s">
         <v>509</v>
       </c>
@@ -24466,7 +24466,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="847" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A847" t="s">
         <v>509</v>
       </c>
@@ -24492,7 +24492,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="848" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A848" t="s">
         <v>510</v>
       </c>
@@ -24518,7 +24518,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="849" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A849" t="s">
         <v>510</v>
       </c>
@@ -24544,7 +24544,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="850" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A850" t="s">
         <v>510</v>
       </c>
@@ -24570,7 +24570,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="851" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A851" t="s">
         <v>510</v>
       </c>
@@ -24596,7 +24596,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="852" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A852" t="s">
         <v>510</v>
       </c>
@@ -24622,7 +24622,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="853" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A853" t="s">
         <v>510</v>
       </c>
@@ -24648,7 +24648,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="854" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A854" t="s">
         <v>513</v>
       </c>
@@ -24674,7 +24674,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="855" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A855" t="s">
         <v>513</v>
       </c>
@@ -24700,7 +24700,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="856" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A856" t="s">
         <v>513</v>
       </c>
@@ -24726,7 +24726,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="857" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A857" t="s">
         <v>513</v>
       </c>
@@ -24752,7 +24752,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="858" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A858" t="s">
         <v>513</v>
       </c>
@@ -24778,7 +24778,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="859" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A859" t="s">
         <v>513</v>
       </c>
@@ -24804,7 +24804,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="860" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A860" t="s">
         <v>515</v>
       </c>
@@ -24830,7 +24830,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="861" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A861" t="s">
         <v>515</v>
       </c>
@@ -24856,7 +24856,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="862" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A862" t="s">
         <v>515</v>
       </c>
@@ -24882,7 +24882,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="863" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A863" t="s">
         <v>515</v>
       </c>
@@ -24908,7 +24908,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="864" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A864" t="s">
         <v>515</v>
       </c>
@@ -24934,7 +24934,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="865" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A865" t="s">
         <v>515</v>
       </c>
@@ -24960,7 +24960,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="866" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A866" t="s">
         <v>517</v>
       </c>
@@ -24986,7 +24986,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="867" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A867" t="s">
         <v>517</v>
       </c>
@@ -25012,7 +25012,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="868" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A868" t="s">
         <v>517</v>
       </c>
@@ -25038,7 +25038,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="869" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A869" t="s">
         <v>517</v>
       </c>
@@ -25064,7 +25064,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="870" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A870" t="s">
         <v>517</v>
       </c>
@@ -25090,7 +25090,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="871" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A871" t="s">
         <v>517</v>
       </c>
@@ -25116,7 +25116,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="872" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A872" t="s">
         <v>518</v>
       </c>
@@ -25142,7 +25142,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="873" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A873" t="s">
         <v>518</v>
       </c>
@@ -25168,7 +25168,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="874" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A874" t="s">
         <v>518</v>
       </c>
@@ -25194,7 +25194,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="875" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A875" t="s">
         <v>518</v>
       </c>
@@ -25220,7 +25220,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="876" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A876" t="s">
         <v>518</v>
       </c>
@@ -25246,7 +25246,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="877" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A877" t="s">
         <v>518</v>
       </c>
@@ -25272,7 +25272,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="878" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A878" t="s">
         <v>521</v>
       </c>
@@ -25298,7 +25298,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="879" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A879" t="s">
         <v>521</v>
       </c>
@@ -25324,7 +25324,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="880" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A880" t="s">
         <v>521</v>
       </c>
@@ -25350,7 +25350,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="881" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A881" t="s">
         <v>521</v>
       </c>
@@ -25376,7 +25376,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="882" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A882" t="s">
         <v>521</v>
       </c>
@@ -25402,7 +25402,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="883" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A883" t="s">
         <v>521</v>
       </c>
@@ -25428,7 +25428,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="884" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A884" t="s">
         <v>525</v>
       </c>
@@ -25454,7 +25454,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="885" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A885" t="s">
         <v>525</v>
       </c>
@@ -25480,7 +25480,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="886" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A886" t="s">
         <v>525</v>
       </c>
@@ -25506,7 +25506,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="887" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A887" t="s">
         <v>525</v>
       </c>
@@ -25532,7 +25532,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="888" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A888" t="s">
         <v>525</v>
       </c>
@@ -25558,7 +25558,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="889" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="889" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A889" t="s">
         <v>525</v>
       </c>
@@ -25584,7 +25584,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="890" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="890" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A890" t="s">
         <v>528</v>
       </c>
@@ -25610,7 +25610,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="891" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A891" t="s">
         <v>528</v>
       </c>
@@ -25636,7 +25636,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="892" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A892" t="s">
         <v>528</v>
       </c>
@@ -25662,7 +25662,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="893" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A893" t="s">
         <v>528</v>
       </c>
@@ -25688,7 +25688,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="894" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A894" t="s">
         <v>528</v>
       </c>
@@ -25714,7 +25714,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="895" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A895" t="s">
         <v>528</v>
       </c>
@@ -25740,7 +25740,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="896" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A896" t="s">
         <v>532</v>
       </c>
@@ -25766,7 +25766,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="897" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A897" t="s">
         <v>532</v>
       </c>
@@ -25792,7 +25792,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="898" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A898" t="s">
         <v>532</v>
       </c>
@@ -25818,7 +25818,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="899" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A899" t="s">
         <v>532</v>
       </c>
@@ -25844,7 +25844,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="900" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A900" t="s">
         <v>532</v>
       </c>
@@ -25870,7 +25870,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="901" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A901" t="s">
         <v>532</v>
       </c>
@@ -25896,7 +25896,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="902" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="902" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A902" t="s">
         <v>535</v>
       </c>
@@ -25922,7 +25922,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="903" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A903" t="s">
         <v>535</v>
       </c>
@@ -25948,7 +25948,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="904" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A904" t="s">
         <v>535</v>
       </c>
@@ -25974,7 +25974,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="905" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="905" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A905" t="s">
         <v>535</v>
       </c>
@@ -26000,7 +26000,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="906" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A906" t="s">
         <v>535</v>
       </c>
@@ -26026,7 +26026,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="907" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A907" t="s">
         <v>535</v>
       </c>
@@ -26052,7 +26052,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="908" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="908" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A908" t="s">
         <v>537</v>
       </c>
@@ -26078,7 +26078,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="909" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="909" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A909" t="s">
         <v>537</v>
       </c>
@@ -26104,7 +26104,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="910" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="910" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A910" t="s">
         <v>537</v>
       </c>
@@ -26130,7 +26130,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="911" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="911" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A911" t="s">
         <v>537</v>
       </c>
@@ -26156,7 +26156,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="912" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="912" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A912" t="s">
         <v>537</v>
       </c>
@@ -26182,7 +26182,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="913" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="913" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A913" t="s">
         <v>537</v>
       </c>
@@ -26208,7 +26208,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="914" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="914" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A914" t="s">
         <v>539</v>
       </c>
@@ -26234,7 +26234,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="915" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="915" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A915" t="s">
         <v>539</v>
       </c>
@@ -26260,7 +26260,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="916" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="916" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A916" t="s">
         <v>539</v>
       </c>
@@ -26286,7 +26286,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="917" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="917" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A917" t="s">
         <v>539</v>
       </c>
@@ -26338,7 +26338,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="919" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="919" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A919" t="s">
         <v>539</v>
       </c>
@@ -26364,7 +26364,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="920" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="920" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A920" t="s">
         <v>540</v>
       </c>
@@ -26390,7 +26390,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="921" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="921" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A921" t="s">
         <v>540</v>
       </c>
@@ -26416,7 +26416,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="922" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="922" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A922" t="s">
         <v>540</v>
       </c>
@@ -26442,7 +26442,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="923" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="923" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A923" t="s">
         <v>540</v>
       </c>
@@ -26468,7 +26468,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="924" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="924" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A924" t="s">
         <v>540</v>
       </c>
@@ -26494,7 +26494,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="925" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="925" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A925" t="s">
         <v>540</v>
       </c>
@@ -26520,7 +26520,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="926" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="926" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A926" t="s">
         <v>541</v>
       </c>
@@ -26546,7 +26546,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="927" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="927" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A927" t="s">
         <v>541</v>
       </c>
@@ -26572,7 +26572,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="928" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="928" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A928" t="s">
         <v>541</v>
       </c>
@@ -26598,7 +26598,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="929" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="929" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A929" t="s">
         <v>541</v>
       </c>
@@ -26624,7 +26624,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="930" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="930" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A930" t="s">
         <v>541</v>
       </c>
@@ -26650,7 +26650,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="931" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="931" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A931" t="s">
         <v>541</v>
       </c>
@@ -26676,7 +26676,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="932" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="932" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A932" t="s">
         <v>542</v>
       </c>
@@ -26702,7 +26702,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="933" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="933" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A933" t="s">
         <v>542</v>
       </c>
@@ -26728,7 +26728,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="934" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="934" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A934" t="s">
         <v>542</v>
       </c>
@@ -26754,7 +26754,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="935" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="935" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A935" t="s">
         <v>542</v>
       </c>
@@ -26780,7 +26780,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="936" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="936" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A936" t="s">
         <v>542</v>
       </c>
@@ -26806,7 +26806,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="937" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="937" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A937" t="s">
         <v>542</v>
       </c>
@@ -26832,7 +26832,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="938" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="938" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A938" t="s">
         <v>543</v>
       </c>
@@ -26858,7 +26858,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="939" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="939" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A939" t="s">
         <v>543</v>
       </c>
@@ -26884,7 +26884,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="940" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="940" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A940" t="s">
         <v>543</v>
       </c>
@@ -26910,7 +26910,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="941" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="941" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A941" t="s">
         <v>543</v>
       </c>
@@ -26936,7 +26936,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="942" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="942" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A942" t="s">
         <v>543</v>
       </c>
@@ -26962,7 +26962,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="943" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="943" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A943" t="s">
         <v>543</v>
       </c>
@@ -26988,7 +26988,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="944" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="944" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A944" t="s">
         <v>545</v>
       </c>
@@ -27014,7 +27014,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="945" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="945" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A945" t="s">
         <v>545</v>
       </c>
@@ -27040,7 +27040,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="946" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="946" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A946" t="s">
         <v>545</v>
       </c>
@@ -27066,7 +27066,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="947" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="947" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A947" t="s">
         <v>545</v>
       </c>
@@ -27092,7 +27092,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="948" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="948" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A948" t="s">
         <v>545</v>
       </c>
@@ -27118,7 +27118,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="949" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="949" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A949" t="s">
         <v>545</v>
       </c>
@@ -27144,7 +27144,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="950" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="950" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A950" t="s">
         <v>547</v>
       </c>
@@ -27170,7 +27170,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="951" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="951" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A951" t="s">
         <v>547</v>
       </c>
@@ -27196,7 +27196,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="952" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="952" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A952" t="s">
         <v>547</v>
       </c>
@@ -27222,7 +27222,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="953" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="953" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A953" t="s">
         <v>547</v>
       </c>
@@ -27248,7 +27248,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="954" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="954" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A954" t="s">
         <v>547</v>
       </c>
@@ -27274,7 +27274,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="955" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="955" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A955" t="s">
         <v>547</v>
       </c>
@@ -27300,7 +27300,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="956" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="956" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A956" t="s">
         <v>548</v>
       </c>
@@ -27326,7 +27326,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="957" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="957" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A957" t="s">
         <v>548</v>
       </c>
@@ -27352,7 +27352,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="958" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="958" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A958" t="s">
         <v>548</v>
       </c>
@@ -27378,7 +27378,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="959" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="959" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A959" t="s">
         <v>548</v>
       </c>
@@ -27404,7 +27404,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="960" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="960" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A960" t="s">
         <v>548</v>
       </c>
@@ -27430,7 +27430,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="961" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="961" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A961" t="s">
         <v>548</v>
       </c>
@@ -27456,7 +27456,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="962" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="962" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A962" t="s">
         <v>550</v>
       </c>
@@ -27482,7 +27482,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="963" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="963" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A963" t="s">
         <v>550</v>
       </c>
@@ -27508,7 +27508,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="964" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="964" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A964" t="s">
         <v>550</v>
       </c>
@@ -27534,7 +27534,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="965" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="965" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A965" t="s">
         <v>550</v>
       </c>
@@ -27560,7 +27560,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="966" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="966" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A966" t="s">
         <v>550</v>
       </c>
@@ -27586,7 +27586,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="967" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="967" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A967" t="s">
         <v>550</v>
       </c>
@@ -27612,7 +27612,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="968" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="968" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A968" t="s">
         <v>552</v>
       </c>
@@ -27638,7 +27638,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="969" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="969" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A969" t="s">
         <v>552</v>
       </c>
@@ -27664,7 +27664,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="970" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="970" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A970" t="s">
         <v>552</v>
       </c>
@@ -27690,7 +27690,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="971" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="971" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A971" t="s">
         <v>552</v>
       </c>
@@ -27716,7 +27716,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="972" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="972" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A972" t="s">
         <v>552</v>
       </c>
@@ -27742,7 +27742,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="973" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="973" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A973" t="s">
         <v>552</v>
       </c>
@@ -27768,7 +27768,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="974" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="974" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A974" t="s">
         <v>554</v>
       </c>
@@ -27794,7 +27794,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="975" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="975" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A975" t="s">
         <v>554</v>
       </c>
@@ -27820,7 +27820,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="976" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="976" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A976" t="s">
         <v>554</v>
       </c>
@@ -27846,7 +27846,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="977" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="977" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A977" t="s">
         <v>554</v>
       </c>
@@ -27872,7 +27872,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="978" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="978" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A978" t="s">
         <v>554</v>
       </c>
@@ -27898,7 +27898,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="979" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="979" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A979" t="s">
         <v>554</v>
       </c>
@@ -27924,7 +27924,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="980" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="980" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A980" t="s">
         <v>555</v>
       </c>
@@ -27950,7 +27950,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="981" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="981" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A981" t="s">
         <v>555</v>
       </c>
@@ -27976,7 +27976,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="982" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="982" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A982" t="s">
         <v>555</v>
       </c>
@@ -28002,7 +28002,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="983" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="983" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A983" t="s">
         <v>555</v>
       </c>
@@ -28028,7 +28028,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="984" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="984" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A984" t="s">
         <v>555</v>
       </c>
@@ -28054,7 +28054,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="985" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="985" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A985" t="s">
         <v>555</v>
       </c>
@@ -28080,7 +28080,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="986" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="986" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A986" t="s">
         <v>558</v>
       </c>
@@ -28106,7 +28106,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="987" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="987" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A987" t="s">
         <v>558</v>
       </c>
@@ -28132,7 +28132,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="988" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="988" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A988" t="s">
         <v>558</v>
       </c>
@@ -28158,7 +28158,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="989" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="989" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A989" t="s">
         <v>558</v>
       </c>
@@ -28184,7 +28184,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="990" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="990" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A990" t="s">
         <v>558</v>
       </c>
@@ -28210,7 +28210,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="991" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="991" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A991" t="s">
         <v>558</v>
       </c>
@@ -28236,7 +28236,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="992" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="992" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A992" t="s">
         <v>560</v>
       </c>
@@ -28262,7 +28262,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="993" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="993" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A993" t="s">
         <v>560</v>
       </c>
@@ -28288,7 +28288,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="994" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="994" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A994" t="s">
         <v>560</v>
       </c>
@@ -28314,7 +28314,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="995" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="995" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A995" t="s">
         <v>560</v>
       </c>
@@ -28340,7 +28340,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="996" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="996" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A996" t="s">
         <v>560</v>
       </c>
@@ -28366,7 +28366,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="997" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="997" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A997" t="s">
         <v>560</v>
       </c>
@@ -28392,7 +28392,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="998" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="998" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A998" t="s">
         <v>562</v>
       </c>
@@ -28418,7 +28418,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="999" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="999" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A999" t="s">
         <v>562</v>
       </c>
@@ -28444,7 +28444,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1000" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1000" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1000" t="s">
         <v>562</v>
       </c>
@@ -28470,7 +28470,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1001" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1001" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1001" t="s">
         <v>562</v>
       </c>
@@ -28496,7 +28496,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1002" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1002" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1002" t="s">
         <v>562</v>
       </c>
@@ -28522,7 +28522,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="1003" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1003" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1003" t="s">
         <v>562</v>
       </c>
@@ -28548,7 +28548,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1004" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1004" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1004" t="s">
         <v>563</v>
       </c>
@@ -28574,7 +28574,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1005" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1005" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1005" t="s">
         <v>563</v>
       </c>
@@ -28600,7 +28600,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1006" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1006" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1006" t="s">
         <v>563</v>
       </c>
@@ -28626,7 +28626,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1007" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1007" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1007" t="s">
         <v>563</v>
       </c>
@@ -28652,7 +28652,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1008" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1008" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1008" t="s">
         <v>563</v>
       </c>
@@ -28678,7 +28678,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1009" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1009" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1009" t="s">
         <v>563</v>
       </c>
@@ -28704,7 +28704,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1010" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1010" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1010" t="s">
         <v>565</v>
       </c>
@@ -28730,7 +28730,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1011" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1011" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1011" t="s">
         <v>565</v>
       </c>
@@ -28756,7 +28756,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1012" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1012" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1012" t="s">
         <v>565</v>
       </c>
@@ -28782,7 +28782,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1013" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1013" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1013" t="s">
         <v>565</v>
       </c>
@@ -28808,7 +28808,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1014" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1014" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1014" t="s">
         <v>565</v>
       </c>
@@ -28834,7 +28834,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1015" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1015" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1015" t="s">
         <v>565</v>
       </c>
@@ -28860,7 +28860,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1016" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1016" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1016" t="s">
         <v>567</v>
       </c>
@@ -28886,7 +28886,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1017" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1017" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1017" t="s">
         <v>567</v>
       </c>
@@ -28912,7 +28912,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1018" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1018" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1018" t="s">
         <v>567</v>
       </c>
@@ -28938,7 +28938,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1019" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1019" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1019" t="s">
         <v>567</v>
       </c>
@@ -28964,7 +28964,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1020" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1020" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1020" t="s">
         <v>567</v>
       </c>
@@ -28990,7 +28990,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1021" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1021" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1021" t="s">
         <v>567</v>
       </c>
@@ -29016,7 +29016,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1022" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1022" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1022" t="s">
         <v>568</v>
       </c>
@@ -29042,7 +29042,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1023" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1023" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1023" t="s">
         <v>568</v>
       </c>
@@ -29068,7 +29068,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1024" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1024" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1024" t="s">
         <v>568</v>
       </c>
@@ -29094,7 +29094,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1025" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1025" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1025" t="s">
         <v>568</v>
       </c>
@@ -29120,7 +29120,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1026" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1026" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1026" t="s">
         <v>568</v>
       </c>
@@ -29146,7 +29146,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1027" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1027" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1027" t="s">
         <v>568</v>
       </c>
@@ -29172,7 +29172,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1028" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1028" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1028" t="s">
         <v>569</v>
       </c>
@@ -29198,7 +29198,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1029" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1029" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1029" t="s">
         <v>569</v>
       </c>
@@ -29224,7 +29224,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1030" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1030" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1030" t="s">
         <v>569</v>
       </c>
@@ -29250,7 +29250,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1031" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1031" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1031" t="s">
         <v>569</v>
       </c>
@@ -29276,7 +29276,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1032" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1032" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1032" t="s">
         <v>569</v>
       </c>
@@ -29302,7 +29302,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1033" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1033" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1033" t="s">
         <v>569</v>
       </c>
@@ -29328,7 +29328,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1034" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1034" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1034" t="s">
         <v>570</v>
       </c>
@@ -29354,7 +29354,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1035" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1035" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1035" t="s">
         <v>570</v>
       </c>
@@ -29380,7 +29380,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1036" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1036" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1036" t="s">
         <v>570</v>
       </c>
@@ -29406,7 +29406,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1037" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1037" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1037" t="s">
         <v>570</v>
       </c>
@@ -29432,7 +29432,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1038" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1038" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1038" t="s">
         <v>570</v>
       </c>
@@ -29458,7 +29458,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1039" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1039" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1039" t="s">
         <v>570</v>
       </c>
@@ -29484,7 +29484,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1040" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1040" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1040" t="s">
         <v>572</v>
       </c>
@@ -29536,7 +29536,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1042" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1042" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1042" t="s">
         <v>572</v>
       </c>
@@ -29562,7 +29562,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1043" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1043" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1043" t="s">
         <v>572</v>
       </c>
@@ -29588,7 +29588,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1044" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1044" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1044" t="s">
         <v>572</v>
       </c>
@@ -29614,7 +29614,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1045" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1045" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1045" t="s">
         <v>572</v>
       </c>
@@ -29640,7 +29640,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1046" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1046" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1046" t="s">
         <v>576</v>
       </c>
@@ -29666,7 +29666,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="1047" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1047" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1047" t="s">
         <v>576</v>
       </c>
@@ -29692,7 +29692,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="1048" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1048" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1048" t="s">
         <v>576</v>
       </c>
@@ -29718,7 +29718,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1049" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1049" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1049" t="s">
         <v>576</v>
       </c>
@@ -29744,7 +29744,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1050" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1050" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1050" t="s">
         <v>576</v>
       </c>
@@ -29770,7 +29770,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1051" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1051" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1051" t="s">
         <v>576</v>
       </c>
@@ -29797,13 +29797,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1051" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="Sirfetch’d"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:H1051" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -33877,6 +33871,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{716DE396-DFF8-497C-823B-D1510266F474}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -33897,7 +33892,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="65.25" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>615</v>
       </c>
@@ -33914,7 +33909,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>616</v>
       </c>
@@ -33931,7 +33926,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>617</v>
       </c>
@@ -33948,7 +33943,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>618</v>
       </c>
@@ -33965,7 +33960,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>619</v>
       </c>
@@ -33982,7 +33977,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>620</v>
       </c>
@@ -33999,7 +33994,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>621</v>
       </c>
@@ -34016,7 +34011,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>622</v>
       </c>
@@ -34033,7 +34028,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>623</v>
       </c>
@@ -34050,7 +34045,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>624</v>
       </c>
@@ -34067,7 +34062,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>625</v>
       </c>
@@ -34084,7 +34079,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>626</v>
       </c>
@@ -34101,7 +34096,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>627</v>
       </c>
@@ -34118,7 +34113,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>628</v>
       </c>
@@ -34135,7 +34130,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>629</v>
       </c>
@@ -34152,7 +34147,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>630</v>
       </c>
@@ -34169,7 +34164,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>631</v>
       </c>
@@ -34186,7 +34181,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>632</v>
       </c>
@@ -34203,7 +34198,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>633</v>
       </c>
@@ -34220,7 +34215,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>634</v>
       </c>
@@ -34237,7 +34232,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>635</v>
       </c>
@@ -34254,7 +34249,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>637</v>
       </c>
@@ -34271,7 +34266,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>638</v>
       </c>
@@ -34288,7 +34283,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>639</v>
       </c>
@@ -34305,7 +34300,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>640</v>
       </c>
@@ -34322,7 +34317,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
         <v>641</v>
       </c>
@@ -34339,7 +34334,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>642</v>
       </c>
@@ -34356,7 +34351,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>643</v>
       </c>
@@ -34373,7 +34368,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>644</v>
       </c>
@@ -34407,7 +34402,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
         <v>646</v>
       </c>
@@ -34424,7 +34419,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
         <v>647</v>
       </c>
@@ -34441,7 +34436,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
         <v>648</v>
       </c>
@@ -34458,7 +34453,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>649</v>
       </c>
@@ -34475,7 +34470,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>650</v>
       </c>
@@ -34492,7 +34487,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>651</v>
       </c>
@@ -34509,7 +34504,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>652</v>
       </c>
@@ -34526,7 +34521,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>653</v>
       </c>
@@ -34543,7 +34538,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
         <v>654</v>
       </c>
@@ -34560,7 +34555,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
         <v>655</v>
       </c>
@@ -34578,6 +34573,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E41" xr:uid="{716DE396-DFF8-497C-823B-D1510266F474}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Jorginho Tv"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/tiers_gen9nationaldexdoubles.xlsx
+++ b/tiers_gen9nationaldexdoubles.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\power bi\webhook\Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53B53FEC-E4B1-41BE-9888-A70C6008E694}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A15198C-1FDF-4168-B125-310FEA2DBE67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/tiers_gen9nationaldexdoubles.xlsx
+++ b/tiers_gen9nationaldexdoubles.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\power bi\webhook\Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A15198C-1FDF-4168-B125-310FEA2DBE67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{843F128A-D5D4-4133-BEC0-9BA38848EB61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pokemon" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="Teams" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Equipos!$A$1:$G$176</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Pokemon!$A$1:$H$1051</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Teams!$A$1:$E$41</definedName>
   </definedNames>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3895" uniqueCount="657">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3895" uniqueCount="656">
   <si>
     <t>Equipo</t>
   </si>
@@ -1925,9 +1926,6 @@
   </si>
   <si>
     <t>mounstronio</t>
-  </si>
-  <si>
-    <t>Alto mando Aza</t>
   </si>
   <si>
     <t>JaLax</t>
@@ -3433,7 +3431,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>51</v>
       </c>
@@ -3459,7 +3457,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>51</v>
       </c>
@@ -3485,7 +3483,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>51</v>
       </c>
@@ -3511,7 +3509,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>51</v>
       </c>
@@ -3537,7 +3535,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>51</v>
       </c>
@@ -3563,7 +3561,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>51</v>
       </c>
@@ -6059,12 +6057,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>140</v>
       </c>
       <c r="B139" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C139">
         <v>0.23100000000000001</v>
@@ -6215,12 +6213,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>145</v>
       </c>
       <c r="B145" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C145">
         <v>0.30499999999999999</v>
@@ -7572,7 +7570,7 @@
         <v>180</v>
       </c>
       <c r="B197" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C197">
         <v>0</v>
@@ -8352,7 +8350,7 @@
         <v>188</v>
       </c>
       <c r="B227" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C227">
         <v>0</v>
@@ -8451,7 +8449,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>189</v>
       </c>
@@ -16173,12 +16171,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="528" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
         <v>358</v>
       </c>
       <c r="B528" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C528">
         <v>0.30499999999999999</v>
@@ -17270,7 +17268,7 @@
         <v>376</v>
       </c>
       <c r="B570" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C570">
         <v>0.2</v>
@@ -19163,12 +19161,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="643" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
         <v>413</v>
       </c>
       <c r="B643" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C643">
         <v>0.30499999999999999</v>
@@ -21378,7 +21376,7 @@
         <v>452</v>
       </c>
       <c r="B728" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C728">
         <v>0.2</v>
@@ -23167,12 +23165,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="797" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A797" t="s">
         <v>482</v>
       </c>
       <c r="B797" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C797">
         <v>0.30499999999999999</v>
@@ -25871,12 +25869,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="901" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A901" t="s">
         <v>529</v>
       </c>
       <c r="B901" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C901">
         <v>0.30499999999999999</v>
@@ -26318,7 +26316,7 @@
         <v>536</v>
       </c>
       <c r="B918" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C918">
         <v>0</v>
@@ -29516,7 +29514,7 @@
         <v>569</v>
       </c>
       <c r="B1041" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C1041">
         <v>0</v>
@@ -29799,11 +29797,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:H1051" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="1">
+    <filterColumn colId="0">
       <filters>
-        <filter val="Tauros"/>
-        <filter val="Tauros-Paldea-Aqua"/>
-        <filter val="Tauros-Paldea-Blaze"/>
+        <filter val="Alto Mando Aza"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -29813,6 +29809,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:G176"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -29848,7 +29845,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>233</v>
       </c>
@@ -29871,7 +29868,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>559</v>
       </c>
@@ -29894,7 +29891,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>349</v>
       </c>
@@ -29917,7 +29914,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>454</v>
       </c>
@@ -29940,7 +29937,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>443</v>
       </c>
@@ -29963,7 +29960,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>394</v>
       </c>
@@ -29986,7 +29983,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -30009,7 +30006,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>132</v>
       </c>
@@ -30032,7 +30029,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>364</v>
       </c>
@@ -30055,7 +30052,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>411</v>
       </c>
@@ -30078,7 +30075,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>322</v>
       </c>
@@ -30101,7 +30098,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>186</v>
       </c>
@@ -30124,7 +30121,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>497</v>
       </c>
@@ -30147,7 +30144,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>515</v>
       </c>
@@ -30170,7 +30167,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>431</v>
       </c>
@@ -30193,7 +30190,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>408</v>
       </c>
@@ -30216,7 +30213,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>158</v>
       </c>
@@ -30239,7 +30236,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>104</v>
       </c>
@@ -30262,7 +30259,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>486</v>
       </c>
@@ -30285,7 +30282,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>183</v>
       </c>
@@ -30308,7 +30305,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>333</v>
       </c>
@@ -30331,7 +30328,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>466</v>
       </c>
@@ -30354,7 +30351,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>537</v>
       </c>
@@ -30377,7 +30374,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>69</v>
       </c>
@@ -30400,7 +30397,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>445</v>
       </c>
@@ -30423,7 +30420,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>542</v>
       </c>
@@ -30446,7 +30443,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>293</v>
       </c>
@@ -30469,7 +30466,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>506</v>
       </c>
@@ -30492,7 +30489,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>474</v>
       </c>
@@ -30515,7 +30512,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>440</v>
       </c>
@@ -30538,7 +30535,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>567</v>
       </c>
@@ -30561,7 +30558,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>163</v>
       </c>
@@ -30584,7 +30581,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>196</v>
       </c>
@@ -30607,7 +30604,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>383</v>
       </c>
@@ -30630,7 +30627,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>173</v>
       </c>
@@ -30653,7 +30650,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>367</v>
       </c>
@@ -30676,7 +30673,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>168</v>
       </c>
@@ -30699,7 +30696,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>185</v>
       </c>
@@ -30722,7 +30719,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>370</v>
       </c>
@@ -30745,7 +30742,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>432</v>
       </c>
@@ -30768,7 +30765,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>514</v>
       </c>
@@ -30791,7 +30788,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>148</v>
       </c>
@@ -30814,7 +30811,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>562</v>
       </c>
@@ -30837,7 +30834,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>33</v>
       </c>
@@ -30860,7 +30857,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>8</v>
       </c>
@@ -30906,7 +30903,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>510</v>
       </c>
@@ -30929,7 +30926,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>225</v>
       </c>
@@ -30952,7 +30949,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>512</v>
       </c>
@@ -30975,7 +30972,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>74</v>
       </c>
@@ -30998,7 +30995,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>495</v>
       </c>
@@ -31021,7 +31018,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>340</v>
       </c>
@@ -31044,7 +31041,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>218</v>
       </c>
@@ -31067,7 +31064,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>525</v>
       </c>
@@ -31090,7 +31087,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>400</v>
       </c>
@@ -31113,7 +31110,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>418</v>
       </c>
@@ -31136,7 +31133,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>437</v>
       </c>
@@ -31159,7 +31156,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>201</v>
       </c>
@@ -31182,7 +31179,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>573</v>
       </c>
@@ -31205,7 +31202,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>557</v>
       </c>
@@ -31228,7 +31225,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>137</v>
       </c>
@@ -31251,7 +31248,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>265</v>
       </c>
@@ -31274,7 +31271,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>320</v>
       </c>
@@ -31297,7 +31294,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>255</v>
       </c>
@@ -31320,7 +31317,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>63</v>
       </c>
@@ -31343,7 +31340,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>344</v>
       </c>
@@ -31366,7 +31363,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>438</v>
       </c>
@@ -31389,7 +31386,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>547</v>
       </c>
@@ -31412,7 +31409,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>184</v>
       </c>
@@ -31435,7 +31432,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>482</v>
       </c>
@@ -31458,7 +31455,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>434</v>
       </c>
@@ -31481,7 +31478,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>92</v>
       </c>
@@ -31504,7 +31501,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>472</v>
       </c>
@@ -31527,7 +31524,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>306</v>
       </c>
@@ -31550,7 +31547,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>301</v>
       </c>
@@ -31573,7 +31570,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>464</v>
       </c>
@@ -31596,7 +31593,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>469</v>
       </c>
@@ -31619,7 +31616,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>498</v>
       </c>
@@ -31642,7 +31639,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>539</v>
       </c>
@@ -31665,7 +31662,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>413</v>
       </c>
@@ -31688,7 +31685,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>478</v>
       </c>
@@ -31711,7 +31708,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>156</v>
       </c>
@@ -31734,7 +31731,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>540</v>
       </c>
@@ -31757,7 +31754,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>507</v>
       </c>
@@ -31780,7 +31777,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>566</v>
       </c>
@@ -31803,7 +31800,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>409</v>
       </c>
@@ -31826,7 +31823,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>534</v>
       </c>
@@ -31849,7 +31846,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>317</v>
       </c>
@@ -31872,7 +31869,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>209</v>
       </c>
@@ -31895,7 +31892,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>145</v>
       </c>
@@ -31918,7 +31915,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>564</v>
       </c>
@@ -31941,7 +31938,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>46</v>
       </c>
@@ -31964,7 +31961,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>268</v>
       </c>
@@ -31987,7 +31984,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>374</v>
       </c>
@@ -32010,7 +32007,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>114</v>
       </c>
@@ -32033,7 +32030,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>387</v>
       </c>
@@ -32056,7 +32053,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>461</v>
       </c>
@@ -32079,7 +32076,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>544</v>
       </c>
@@ -32102,7 +32099,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>195</v>
       </c>
@@ -32125,7 +32122,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>336</v>
       </c>
@@ -32148,7 +32145,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>375</v>
       </c>
@@ -32171,7 +32168,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>405</v>
       </c>
@@ -32194,7 +32191,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>348</v>
       </c>
@@ -32217,7 +32214,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>552</v>
       </c>
@@ -32240,7 +32237,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>81</v>
       </c>
@@ -32263,7 +32260,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>468</v>
       </c>
@@ -32286,7 +32283,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>206</v>
       </c>
@@ -32309,7 +32306,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>435</v>
       </c>
@@ -32332,7 +32329,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>324</v>
       </c>
@@ -32355,7 +32352,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>549</v>
       </c>
@@ -32378,7 +32375,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>362</v>
       </c>
@@ -32401,7 +32398,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>150</v>
       </c>
@@ -32424,7 +32421,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>180</v>
       </c>
@@ -32447,7 +32444,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>314</v>
       </c>
@@ -32470,7 +32467,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>555</v>
       </c>
@@ -32493,7 +32490,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>193</v>
       </c>
@@ -32516,7 +32513,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>154</v>
       </c>
@@ -32539,7 +32536,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>310</v>
       </c>
@@ -32562,7 +32559,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>26</v>
       </c>
@@ -32585,7 +32582,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>565</v>
       </c>
@@ -32608,7 +32605,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>259</v>
       </c>
@@ -32631,7 +32628,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>252</v>
       </c>
@@ -32654,7 +32651,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>263</v>
       </c>
@@ -32677,7 +32674,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>500</v>
       </c>
@@ -32700,7 +32697,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>99</v>
       </c>
@@ -32723,7 +32720,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>551</v>
       </c>
@@ -32746,7 +32743,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>197</v>
       </c>
@@ -32769,7 +32766,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>243</v>
       </c>
@@ -32792,7 +32789,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>247</v>
       </c>
@@ -32815,7 +32812,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>560</v>
       </c>
@@ -32838,7 +32835,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>420</v>
       </c>
@@ -32861,7 +32858,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>283</v>
       </c>
@@ -32884,7 +32881,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>213</v>
       </c>
@@ -32907,7 +32904,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>532</v>
       </c>
@@ -32930,7 +32927,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>277</v>
       </c>
@@ -32953,7 +32950,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>522</v>
       </c>
@@ -32976,7 +32973,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>538</v>
       </c>
@@ -32999,7 +32996,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>503</v>
       </c>
@@ -33022,7 +33019,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>229</v>
       </c>
@@ -33045,7 +33042,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>325</v>
       </c>
@@ -33068,7 +33065,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>358</v>
       </c>
@@ -33091,7 +33088,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>120</v>
       </c>
@@ -33114,7 +33111,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>376</v>
       </c>
@@ -33137,7 +33134,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>529</v>
       </c>
@@ -33160,7 +33157,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>330</v>
       </c>
@@ -33183,7 +33180,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>352</v>
       </c>
@@ -33206,7 +33203,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>140</v>
       </c>
@@ -33229,7 +33226,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>452</v>
       </c>
@@ -33252,7 +33249,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>490</v>
       </c>
@@ -33275,7 +33272,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>56</v>
       </c>
@@ -33298,7 +33295,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>428</v>
       </c>
@@ -33321,7 +33318,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>354</v>
       </c>
@@ -33344,7 +33341,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>518</v>
       </c>
@@ -33367,7 +33364,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>356</v>
       </c>
@@ -33390,7 +33387,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>456</v>
       </c>
@@ -33413,7 +33410,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>189</v>
       </c>
@@ -33436,7 +33433,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>289</v>
       </c>
@@ -33459,7 +33456,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>536</v>
       </c>
@@ -33482,7 +33479,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>221</v>
       </c>
@@ -33505,7 +33502,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>569</v>
       </c>
@@ -33528,7 +33525,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>126</v>
       </c>
@@ -33551,7 +33548,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>295</v>
       </c>
@@ -33574,7 +33571,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>107</v>
       </c>
@@ -33597,7 +33594,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>238</v>
       </c>
@@ -33620,7 +33617,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>389</v>
       </c>
@@ -33643,7 +33640,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>545</v>
       </c>
@@ -33666,7 +33663,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>280</v>
       </c>
@@ -33689,7 +33686,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>273</v>
       </c>
@@ -33712,7 +33709,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>396</v>
       </c>
@@ -33735,7 +33732,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>87</v>
       </c>
@@ -33758,7 +33755,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>188</v>
       </c>
@@ -33781,7 +33778,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>379</v>
       </c>
@@ -33804,7 +33801,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>422</v>
       </c>
@@ -33827,7 +33824,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>39</v>
       </c>
@@ -33850,7 +33847,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>449</v>
       </c>
@@ -33874,6 +33871,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G176" xr:uid="{00000000-0001-0000-0100-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Alto Mando Aza"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -34245,13 +34249,13 @@
         <v>632</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>633</v>
+        <v>51</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>265</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>633</v>
+        <v>51</v>
       </c>
       <c r="E22" s="5" t="s">
         <v>265</v>
@@ -34259,7 +34263,7 @@
     </row>
     <row r="23" spans="1:5" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>490</v>
@@ -34276,7 +34280,7 @@
     </row>
     <row r="24" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>537</v>
@@ -34293,7 +34297,7 @@
     </row>
     <row r="25" spans="1:5" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>495</v>
@@ -34310,7 +34314,7 @@
     </row>
     <row r="26" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>573</v>
@@ -34327,7 +34331,7 @@
     </row>
     <row r="27" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>340</v>
@@ -34344,7 +34348,7 @@
     </row>
     <row r="28" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>356</v>
@@ -34361,7 +34365,7 @@
     </row>
     <row r="29" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>512</v>
@@ -34378,7 +34382,7 @@
     </row>
     <row r="30" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>26</v>
@@ -34395,7 +34399,7 @@
     </row>
     <row r="31" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>225</v>
@@ -34412,7 +34416,7 @@
     </row>
     <row r="32" spans="1:5" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>472</v>
@@ -34429,7 +34433,7 @@
     </row>
     <row r="33" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>383</v>
@@ -34446,7 +34450,7 @@
     </row>
     <row r="34" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>420</v>
@@ -34463,7 +34467,7 @@
     </row>
     <row r="35" spans="1:5" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>478</v>
@@ -34480,7 +34484,7 @@
     </row>
     <row r="36" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>370</v>
@@ -34497,7 +34501,7 @@
     </row>
     <row r="37" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>349</v>
@@ -34514,7 +34518,7 @@
     </row>
     <row r="38" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>137</v>
@@ -34531,7 +34535,7 @@
     </row>
     <row r="39" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>418</v>
@@ -34548,7 +34552,7 @@
     </row>
     <row r="40" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>538</v>
@@ -34565,7 +34569,7 @@
     </row>
     <row r="41" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>148</v>

--- a/tiers_gen9nationaldexdoubles.xlsx
+++ b/tiers_gen9nationaldexdoubles.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\power bi\webhook\Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{843F128A-D5D4-4133-BEC0-9BA38848EB61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C525502-8404-4B80-9B98-302CF8C4C7F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,18 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Pokemon!$A$1:$H$1051</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Teams!$A$1:$E$41</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1940,9 +1951,6 @@
     <t>Nigga Chan</t>
   </si>
   <si>
-    <t>lefael</t>
-  </si>
-  <si>
     <t>ZapeohDev</t>
   </si>
   <si>
@@ -1995,6 +2003,9 @@
   </si>
   <si>
     <t>Tauros_Paldea_Blaze</t>
+  </si>
+  <si>
+    <t>Lefael</t>
   </si>
 </sst>
 </file>
@@ -6062,7 +6073,7 @@
         <v>140</v>
       </c>
       <c r="B139" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C139">
         <v>0.23100000000000001</v>
@@ -6218,7 +6229,7 @@
         <v>145</v>
       </c>
       <c r="B145" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C145">
         <v>0.30499999999999999</v>
@@ -7570,7 +7581,7 @@
         <v>180</v>
       </c>
       <c r="B197" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C197">
         <v>0</v>
@@ -8350,7 +8361,7 @@
         <v>188</v>
       </c>
       <c r="B227" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C227">
         <v>0</v>
@@ -16176,7 +16187,7 @@
         <v>358</v>
       </c>
       <c r="B528" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C528">
         <v>0.30499999999999999</v>
@@ -17268,7 +17279,7 @@
         <v>376</v>
       </c>
       <c r="B570" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C570">
         <v>0.2</v>
@@ -19166,7 +19177,7 @@
         <v>413</v>
       </c>
       <c r="B643" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C643">
         <v>0.30499999999999999</v>
@@ -21376,7 +21387,7 @@
         <v>452</v>
       </c>
       <c r="B728" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C728">
         <v>0.2</v>
@@ -23170,7 +23181,7 @@
         <v>482</v>
       </c>
       <c r="B797" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C797">
         <v>0.30499999999999999</v>
@@ -25874,7 +25885,7 @@
         <v>529</v>
       </c>
       <c r="B901" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C901">
         <v>0.30499999999999999</v>
@@ -26316,7 +26327,7 @@
         <v>536</v>
       </c>
       <c r="B918" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C918">
         <v>0</v>
@@ -29514,7 +29525,7 @@
         <v>569</v>
       </c>
       <c r="B1041" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C1041">
         <v>0</v>
@@ -33884,6 +33895,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{716DE396-DFF8-497C-823B-D1510266F474}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -33904,7 +33916,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="65.25" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>612</v>
       </c>
@@ -33921,7 +33933,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>613</v>
       </c>
@@ -33938,7 +33950,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>614</v>
       </c>
@@ -33955,7 +33967,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>615</v>
       </c>
@@ -33972,7 +33984,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>616</v>
       </c>
@@ -33989,7 +34001,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>617</v>
       </c>
@@ -34006,7 +34018,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>618</v>
       </c>
@@ -34023,7 +34035,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>619</v>
       </c>
@@ -34040,7 +34052,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>620</v>
       </c>
@@ -34057,7 +34069,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>621</v>
       </c>
@@ -34074,7 +34086,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>622</v>
       </c>
@@ -34091,7 +34103,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>623</v>
       </c>
@@ -34108,7 +34120,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>624</v>
       </c>
@@ -34125,7 +34137,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>625</v>
       </c>
@@ -34142,7 +34154,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>626</v>
       </c>
@@ -34159,7 +34171,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>627</v>
       </c>
@@ -34176,7 +34188,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>628</v>
       </c>
@@ -34193,7 +34205,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>629</v>
       </c>
@@ -34210,7 +34222,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>630</v>
       </c>
@@ -34227,7 +34239,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>631</v>
       </c>
@@ -34244,7 +34256,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>632</v>
       </c>
@@ -34261,7 +34273,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>633</v>
       </c>
@@ -34278,7 +34290,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>634</v>
       </c>
@@ -34295,7 +34307,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>635</v>
       </c>
@@ -34312,7 +34324,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>636</v>
       </c>
@@ -34331,7 +34343,7 @@
     </row>
     <row r="27" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>637</v>
+        <v>655</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>340</v>
@@ -34346,9 +34358,9 @@
         <v>440</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>356</v>
@@ -34363,9 +34375,9 @@
         <v>209</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>512</v>
@@ -34380,9 +34392,9 @@
         <v>163</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>26</v>
@@ -34397,9 +34409,9 @@
         <v>497</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>225</v>
@@ -34414,9 +34426,9 @@
         <v>19</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>472</v>
@@ -34431,9 +34443,9 @@
         <v>173</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>383</v>
@@ -34448,9 +34460,9 @@
         <v>428</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>420</v>
@@ -34465,9 +34477,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>478</v>
@@ -34482,9 +34494,9 @@
         <v>63</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>370</v>
@@ -34499,9 +34511,9 @@
         <v>186</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>349</v>
@@ -34516,9 +34528,9 @@
         <v>534</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>137</v>
@@ -34533,9 +34545,9 @@
         <v>376</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>418</v>
@@ -34550,9 +34562,9 @@
         <v>506</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>538</v>
@@ -34567,9 +34579,9 @@
         <v>539</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>148</v>
@@ -34585,7 +34597,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E41" xr:uid="{716DE396-DFF8-497C-823B-D1510266F474}"/>
+  <autoFilter ref="A1:E41" xr:uid="{716DE396-DFF8-497C-823B-D1510266F474}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="lefael"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/tiers_gen9nationaldexdoubles.xlsx
+++ b/tiers_gen9nationaldexdoubles.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\power bi\webhook\Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C525502-8404-4B80-9B98-302CF8C4C7F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{825E6F91-CCAA-4D9A-875C-486EF57E0153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1966,9 +1966,6 @@
     <t>Porygon Z</t>
   </si>
   <si>
-    <t>MafiaPolar</t>
-  </si>
-  <si>
     <t>Dino agente</t>
   </si>
   <si>
@@ -2006,6 +2003,9 @@
   </si>
   <si>
     <t>Lefael</t>
+  </si>
+  <si>
+    <t>MafiaPolar6242</t>
   </si>
 </sst>
 </file>
@@ -6073,7 +6073,7 @@
         <v>140</v>
       </c>
       <c r="B139" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C139">
         <v>0.23100000000000001</v>
@@ -6229,7 +6229,7 @@
         <v>145</v>
       </c>
       <c r="B145" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C145">
         <v>0.30499999999999999</v>
@@ -7581,7 +7581,7 @@
         <v>180</v>
       </c>
       <c r="B197" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C197">
         <v>0</v>
@@ -8361,7 +8361,7 @@
         <v>188</v>
       </c>
       <c r="B227" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C227">
         <v>0</v>
@@ -16187,7 +16187,7 @@
         <v>358</v>
       </c>
       <c r="B528" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C528">
         <v>0.30499999999999999</v>
@@ -17279,7 +17279,7 @@
         <v>376</v>
       </c>
       <c r="B570" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C570">
         <v>0.2</v>
@@ -19177,7 +19177,7 @@
         <v>413</v>
       </c>
       <c r="B643" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C643">
         <v>0.30499999999999999</v>
@@ -21387,7 +21387,7 @@
         <v>452</v>
       </c>
       <c r="B728" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C728">
         <v>0.2</v>
@@ -23181,7 +23181,7 @@
         <v>482</v>
       </c>
       <c r="B797" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C797">
         <v>0.30499999999999999</v>
@@ -25885,7 +25885,7 @@
         <v>529</v>
       </c>
       <c r="B901" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C901">
         <v>0.30499999999999999</v>
@@ -26327,7 +26327,7 @@
         <v>536</v>
       </c>
       <c r="B918" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C918">
         <v>0</v>
@@ -29525,7 +29525,7 @@
         <v>569</v>
       </c>
       <c r="B1041" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C1041">
         <v>0</v>
@@ -34341,9 +34341,9 @@
         <v>566</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>340</v>
@@ -34443,9 +34443,9 @@
         <v>173</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
-        <v>642</v>
+        <v>655</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>383</v>
@@ -34462,7 +34462,7 @@
     </row>
     <row r="34" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>420</v>
@@ -34479,7 +34479,7 @@
     </row>
     <row r="35" spans="1:5" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>478</v>
@@ -34496,7 +34496,7 @@
     </row>
     <row r="36" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>370</v>
@@ -34513,7 +34513,7 @@
     </row>
     <row r="37" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>349</v>
@@ -34530,7 +34530,7 @@
     </row>
     <row r="38" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>137</v>
@@ -34547,7 +34547,7 @@
     </row>
     <row r="39" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>418</v>
@@ -34564,7 +34564,7 @@
     </row>
     <row r="40" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>538</v>
@@ -34581,7 +34581,7 @@
     </row>
     <row r="41" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>148</v>
@@ -34600,7 +34600,7 @@
   <autoFilter ref="A1:E41" xr:uid="{716DE396-DFF8-497C-823B-D1510266F474}">
     <filterColumn colId="0">
       <filters>
-        <filter val="lefael"/>
+        <filter val="MafiaPolar"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/tiers_gen9nationaldexdoubles.xlsx
+++ b/tiers_gen9nationaldexdoubles.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\power bi\webhook\Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{825E6F91-CCAA-4D9A-875C-486EF57E0153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5BF7734-EABB-4C86-A829-2DFAAE4B4D28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1960,9 +1960,6 @@
     <t>Minipapus</t>
   </si>
   <si>
-    <t>Jorginho Tv</t>
-  </si>
-  <si>
     <t>Porygon Z</t>
   </si>
   <si>
@@ -2006,6 +2003,9 @@
   </si>
   <si>
     <t>MafiaPolar6242</t>
+  </si>
+  <si>
+    <t>Jorginho tv</t>
   </si>
 </sst>
 </file>
@@ -6073,7 +6073,7 @@
         <v>140</v>
       </c>
       <c r="B139" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C139">
         <v>0.23100000000000001</v>
@@ -6229,7 +6229,7 @@
         <v>145</v>
       </c>
       <c r="B145" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C145">
         <v>0.30499999999999999</v>
@@ -7581,7 +7581,7 @@
         <v>180</v>
       </c>
       <c r="B197" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C197">
         <v>0</v>
@@ -8361,7 +8361,7 @@
         <v>188</v>
       </c>
       <c r="B227" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C227">
         <v>0</v>
@@ -16187,7 +16187,7 @@
         <v>358</v>
       </c>
       <c r="B528" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C528">
         <v>0.30499999999999999</v>
@@ -17279,7 +17279,7 @@
         <v>376</v>
       </c>
       <c r="B570" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C570">
         <v>0.2</v>
@@ -19177,7 +19177,7 @@
         <v>413</v>
       </c>
       <c r="B643" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C643">
         <v>0.30499999999999999</v>
@@ -21387,7 +21387,7 @@
         <v>452</v>
       </c>
       <c r="B728" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C728">
         <v>0.2</v>
@@ -23181,7 +23181,7 @@
         <v>482</v>
       </c>
       <c r="B797" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C797">
         <v>0.30499999999999999</v>
@@ -25885,7 +25885,7 @@
         <v>529</v>
       </c>
       <c r="B901" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C901">
         <v>0.30499999999999999</v>
@@ -26327,7 +26327,7 @@
         <v>536</v>
       </c>
       <c r="B918" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C918">
         <v>0</v>
@@ -29525,7 +29525,7 @@
         <v>569</v>
       </c>
       <c r="B1041" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C1041">
         <v>0</v>
@@ -34343,7 +34343,7 @@
     </row>
     <row r="27" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>340</v>
@@ -34409,9 +34409,9 @@
         <v>497</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>640</v>
+        <v>655</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>225</v>
@@ -34428,7 +34428,7 @@
     </row>
     <row r="32" spans="1:5" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>472</v>
@@ -34443,9 +34443,9 @@
         <v>173</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>383</v>
@@ -34462,7 +34462,7 @@
     </row>
     <row r="34" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>420</v>
@@ -34479,7 +34479,7 @@
     </row>
     <row r="35" spans="1:5" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>478</v>
@@ -34496,7 +34496,7 @@
     </row>
     <row r="36" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>370</v>
@@ -34513,7 +34513,7 @@
     </row>
     <row r="37" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>349</v>
@@ -34530,7 +34530,7 @@
     </row>
     <row r="38" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>137</v>
@@ -34547,7 +34547,7 @@
     </row>
     <row r="39" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>418</v>
@@ -34564,7 +34564,7 @@
     </row>
     <row r="40" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>538</v>
@@ -34581,7 +34581,7 @@
     </row>
     <row r="41" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>148</v>
@@ -34600,7 +34600,7 @@
   <autoFilter ref="A1:E41" xr:uid="{716DE396-DFF8-497C-823B-D1510266F474}">
     <filterColumn colId="0">
       <filters>
-        <filter val="MafiaPolar"/>
+        <filter val="Jorginho Tv"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/tiers_gen9nationaldexdoubles.xlsx
+++ b/tiers_gen9nationaldexdoubles.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\power bi\webhook\Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5BF7734-EABB-4C86-A829-2DFAAE4B4D28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{192DDB72-3951-4376-A36E-F87CEDD5E5A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pokemon" sheetId="1" r:id="rId1"/>
@@ -2005,7 +2005,7 @@
     <t>MafiaPolar6242</t>
   </si>
   <si>
-    <t>Jorginho tv</t>
+    <t>Jorginho Tv</t>
   </si>
 </sst>
 </file>
@@ -34205,7 +34205,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>629</v>
       </c>
@@ -34409,7 +34409,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>655</v>
       </c>
@@ -34600,7 +34600,7 @@
   <autoFilter ref="A1:E41" xr:uid="{716DE396-DFF8-497C-823B-D1510266F474}">
     <filterColumn colId="0">
       <filters>
-        <filter val="Jorginho Tv"/>
+        <filter val="Jupiter"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/tiers_gen9nationaldexdoubles.xlsx
+++ b/tiers_gen9nationaldexdoubles.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\power bi\webhook\Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{192DDB72-3951-4376-A36E-F87CEDD5E5A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA4F2B08-A243-4074-B398-80C2CE33E9A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1972,9 +1972,6 @@
     <t>Saga</t>
   </si>
   <si>
-    <t>aikauwu</t>
-  </si>
-  <si>
     <t>Joscake</t>
   </si>
   <si>
@@ -2006,6 +2003,9 @@
   </si>
   <si>
     <t>Jorginho Tv</t>
+  </si>
+  <si>
+    <t>Aikauwu</t>
   </si>
 </sst>
 </file>
@@ -6073,7 +6073,7 @@
         <v>140</v>
       </c>
       <c r="B139" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C139">
         <v>0.23100000000000001</v>
@@ -6229,7 +6229,7 @@
         <v>145</v>
       </c>
       <c r="B145" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C145">
         <v>0.30499999999999999</v>
@@ -7581,7 +7581,7 @@
         <v>180</v>
       </c>
       <c r="B197" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C197">
         <v>0</v>
@@ -8361,7 +8361,7 @@
         <v>188</v>
       </c>
       <c r="B227" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C227">
         <v>0</v>
@@ -16187,7 +16187,7 @@
         <v>358</v>
       </c>
       <c r="B528" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C528">
         <v>0.30499999999999999</v>
@@ -17279,7 +17279,7 @@
         <v>376</v>
       </c>
       <c r="B570" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C570">
         <v>0.2</v>
@@ -19177,7 +19177,7 @@
         <v>413</v>
       </c>
       <c r="B643" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C643">
         <v>0.30499999999999999</v>
@@ -21387,7 +21387,7 @@
         <v>452</v>
       </c>
       <c r="B728" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C728">
         <v>0.2</v>
@@ -23181,7 +23181,7 @@
         <v>482</v>
       </c>
       <c r="B797" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C797">
         <v>0.30499999999999999</v>
@@ -25885,7 +25885,7 @@
         <v>529</v>
       </c>
       <c r="B901" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C901">
         <v>0.30499999999999999</v>
@@ -26327,7 +26327,7 @@
         <v>536</v>
       </c>
       <c r="B918" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C918">
         <v>0</v>
@@ -29525,7 +29525,7 @@
         <v>569</v>
       </c>
       <c r="B1041" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C1041">
         <v>0</v>
@@ -34205,7 +34205,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>629</v>
       </c>
@@ -34343,7 +34343,7 @@
     </row>
     <row r="27" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>340</v>
@@ -34411,7 +34411,7 @@
     </row>
     <row r="31" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>225</v>
@@ -34445,7 +34445,7 @@
     </row>
     <row r="33" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>383</v>
@@ -34511,9 +34511,9 @@
         <v>186</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
-        <v>644</v>
+        <v>655</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>349</v>
@@ -34530,7 +34530,7 @@
     </row>
     <row r="38" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>137</v>
@@ -34547,7 +34547,7 @@
     </row>
     <row r="39" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>418</v>
@@ -34564,7 +34564,7 @@
     </row>
     <row r="40" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>538</v>
@@ -34581,7 +34581,7 @@
     </row>
     <row r="41" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>148</v>
@@ -34600,7 +34600,7 @@
   <autoFilter ref="A1:E41" xr:uid="{716DE396-DFF8-497C-823B-D1510266F474}">
     <filterColumn colId="0">
       <filters>
-        <filter val="Jupiter"/>
+        <filter val="aikauwu"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/tiers_gen9nationaldexdoubles.xlsx
+++ b/tiers_gen9nationaldexdoubles.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\power bi\webhook\Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA4F2B08-A243-4074-B398-80C2CE33E9A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB378D39-69FE-4891-A2BC-28671C60B87C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1912,9 +1912,6 @@
     <t>LABIAMG</t>
   </si>
   <si>
-    <t>chonarthas</t>
-  </si>
-  <si>
     <t>Ger</t>
   </si>
   <si>
@@ -2006,6 +2003,9 @@
   </si>
   <si>
     <t>Aikauwu</t>
+  </si>
+  <si>
+    <t>Chonarthas</t>
   </si>
 </sst>
 </file>
@@ -6073,7 +6073,7 @@
         <v>140</v>
       </c>
       <c r="B139" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C139">
         <v>0.23100000000000001</v>
@@ -6229,7 +6229,7 @@
         <v>145</v>
       </c>
       <c r="B145" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C145">
         <v>0.30499999999999999</v>
@@ -7581,7 +7581,7 @@
         <v>180</v>
       </c>
       <c r="B197" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C197">
         <v>0</v>
@@ -8361,7 +8361,7 @@
         <v>188</v>
       </c>
       <c r="B227" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C227">
         <v>0</v>
@@ -16187,7 +16187,7 @@
         <v>358</v>
       </c>
       <c r="B528" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C528">
         <v>0.30499999999999999</v>
@@ -17279,7 +17279,7 @@
         <v>376</v>
       </c>
       <c r="B570" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C570">
         <v>0.2</v>
@@ -19177,7 +19177,7 @@
         <v>413</v>
       </c>
       <c r="B643" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C643">
         <v>0.30499999999999999</v>
@@ -21387,7 +21387,7 @@
         <v>452</v>
       </c>
       <c r="B728" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C728">
         <v>0.2</v>
@@ -23181,7 +23181,7 @@
         <v>482</v>
       </c>
       <c r="B797" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C797">
         <v>0.30499999999999999</v>
@@ -25885,7 +25885,7 @@
         <v>529</v>
       </c>
       <c r="B901" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C901">
         <v>0.30499999999999999</v>
@@ -26327,7 +26327,7 @@
         <v>536</v>
       </c>
       <c r="B918" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C918">
         <v>0</v>
@@ -29525,7 +29525,7 @@
         <v>569</v>
       </c>
       <c r="B1041" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C1041">
         <v>0</v>
@@ -34120,9 +34120,9 @@
         <v>364</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>624</v>
+        <v>655</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>486</v>
@@ -34139,7 +34139,7 @@
     </row>
     <row r="15" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>374</v>
@@ -34156,7 +34156,7 @@
     </row>
     <row r="16" spans="1:5" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>515</v>
@@ -34173,7 +34173,7 @@
     </row>
     <row r="17" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>255</v>
@@ -34190,7 +34190,7 @@
     </row>
     <row r="18" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>525</v>
@@ -34207,7 +34207,7 @@
     </row>
     <row r="19" spans="1:5" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>544</v>
@@ -34224,7 +34224,7 @@
     </row>
     <row r="20" spans="1:5" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>469</v>
@@ -34241,7 +34241,7 @@
     </row>
     <row r="21" spans="1:5" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>464</v>
@@ -34258,7 +34258,7 @@
     </row>
     <row r="22" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>51</v>
@@ -34275,7 +34275,7 @@
     </row>
     <row r="23" spans="1:5" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>490</v>
@@ -34292,7 +34292,7 @@
     </row>
     <row r="24" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>537</v>
@@ -34309,7 +34309,7 @@
     </row>
     <row r="25" spans="1:5" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>495</v>
@@ -34326,7 +34326,7 @@
     </row>
     <row r="26" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>573</v>
@@ -34343,7 +34343,7 @@
     </row>
     <row r="27" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>340</v>
@@ -34360,7 +34360,7 @@
     </row>
     <row r="28" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>356</v>
@@ -34377,7 +34377,7 @@
     </row>
     <row r="29" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>512</v>
@@ -34394,7 +34394,7 @@
     </row>
     <row r="30" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>26</v>
@@ -34411,7 +34411,7 @@
     </row>
     <row r="31" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>225</v>
@@ -34428,7 +34428,7 @@
     </row>
     <row r="32" spans="1:5" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>472</v>
@@ -34445,7 +34445,7 @@
     </row>
     <row r="33" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>383</v>
@@ -34462,7 +34462,7 @@
     </row>
     <row r="34" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>420</v>
@@ -34479,7 +34479,7 @@
     </row>
     <row r="35" spans="1:5" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>478</v>
@@ -34496,7 +34496,7 @@
     </row>
     <row r="36" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>370</v>
@@ -34511,9 +34511,9 @@
         <v>186</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>349</v>
@@ -34530,7 +34530,7 @@
     </row>
     <row r="38" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>137</v>
@@ -34547,7 +34547,7 @@
     </row>
     <row r="39" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>418</v>
@@ -34564,7 +34564,7 @@
     </row>
     <row r="40" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>538</v>
@@ -34581,7 +34581,7 @@
     </row>
     <row r="41" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>148</v>
@@ -34600,7 +34600,7 @@
   <autoFilter ref="A1:E41" xr:uid="{716DE396-DFF8-497C-823B-D1510266F474}">
     <filterColumn colId="0">
       <filters>
-        <filter val="aikauwu"/>
+        <filter val="chonarthas"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/tiers_gen9nationaldexdoubles.xlsx
+++ b/tiers_gen9nationaldexdoubles.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\power bi\webhook\Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB378D39-69FE-4891-A2BC-28671C60B87C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4C78090-2B02-4FEE-B5FC-1D6EBE28DE59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pokemon" sheetId="1" r:id="rId1"/>
@@ -1999,13 +1999,13 @@
     <t>MafiaPolar6242</t>
   </si>
   <si>
-    <t>Jorginho Tv</t>
-  </si>
-  <si>
     <t>Aikauwu</t>
   </si>
   <si>
     <t>Chonarthas</t>
+  </si>
+  <si>
+    <t>Jorginho</t>
   </si>
 </sst>
 </file>
@@ -34120,9 +34120,9 @@
         <v>364</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>486</v>
@@ -34409,9 +34409,9 @@
         <v>497</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>225</v>
@@ -34513,7 +34513,7 @@
     </row>
     <row r="37" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>349</v>
@@ -34600,7 +34600,7 @@
   <autoFilter ref="A1:E41" xr:uid="{716DE396-DFF8-497C-823B-D1510266F474}">
     <filterColumn colId="0">
       <filters>
-        <filter val="chonarthas"/>
+        <filter val="Jorginho Tv"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/tiers_gen9nationaldexdoubles.xlsx
+++ b/tiers_gen9nationaldexdoubles.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\power bi\webhook\Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4C78090-2B02-4FEE-B5FC-1D6EBE28DE59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A1339BF-33D9-49CF-9DCB-89F146F21C22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pokemon" sheetId="1" r:id="rId1"/>
@@ -1987,12 +1987,6 @@
     <t>Zygarde10</t>
   </si>
   <si>
-    <t>Tauros_Paldea_Aqua</t>
-  </si>
-  <si>
-    <t>Tauros_Paldea_Blaze</t>
-  </si>
-  <si>
     <t>Lefael</t>
   </si>
   <si>
@@ -2006,6 +2000,12 @@
   </si>
   <si>
     <t>Jorginho</t>
+  </si>
+  <si>
+    <t>Tauros-Paldea-Blaze</t>
+  </si>
+  <si>
+    <t>Tauros-Paldea-Aqua</t>
   </si>
 </sst>
 </file>
@@ -3442,7 +3442,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>51</v>
       </c>
@@ -3468,7 +3468,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>51</v>
       </c>
@@ -3494,7 +3494,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>51</v>
       </c>
@@ -3520,7 +3520,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>51</v>
       </c>
@@ -3546,7 +3546,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>51</v>
       </c>
@@ -3572,7 +3572,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>51</v>
       </c>
@@ -6068,12 +6068,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="139" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>140</v>
       </c>
       <c r="B139" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="C139">
         <v>0.23100000000000001</v>
@@ -6224,12 +6224,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="145" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>145</v>
       </c>
       <c r="B145" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="C145">
         <v>0.30499999999999999</v>
@@ -16182,12 +16182,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="528" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
         <v>358</v>
       </c>
       <c r="B528" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="C528">
         <v>0.30499999999999999</v>
@@ -19172,12 +19172,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="643" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
         <v>413</v>
       </c>
       <c r="B643" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="C643">
         <v>0.30499999999999999</v>
@@ -23176,12 +23176,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="797" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A797" t="s">
         <v>482</v>
       </c>
       <c r="B797" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="C797">
         <v>0.30499999999999999</v>
@@ -25880,12 +25880,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="901" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A901" t="s">
         <v>529</v>
       </c>
       <c r="B901" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="C901">
         <v>0.30499999999999999</v>
@@ -29808,9 +29808,10 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:H1051" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="0">
+    <filterColumn colId="1">
       <filters>
-        <filter val="Alto Mando Aza"/>
+        <filter val="Tauros_Paldea_Aqua"/>
+        <filter val="Tauros_Paldea_Blaze"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -29820,7 +29821,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:G176"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -29856,7 +29856,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>233</v>
       </c>
@@ -29879,7 +29879,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>559</v>
       </c>
@@ -29902,7 +29902,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>349</v>
       </c>
@@ -29925,7 +29925,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>454</v>
       </c>
@@ -29948,7 +29948,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>443</v>
       </c>
@@ -29971,7 +29971,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>394</v>
       </c>
@@ -29994,7 +29994,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -30017,7 +30017,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>132</v>
       </c>
@@ -30040,7 +30040,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>364</v>
       </c>
@@ -30063,7 +30063,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>411</v>
       </c>
@@ -30086,7 +30086,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>322</v>
       </c>
@@ -30109,7 +30109,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>186</v>
       </c>
@@ -30132,7 +30132,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>497</v>
       </c>
@@ -30155,7 +30155,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>515</v>
       </c>
@@ -30178,7 +30178,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>431</v>
       </c>
@@ -30201,7 +30201,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>408</v>
       </c>
@@ -30224,7 +30224,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>158</v>
       </c>
@@ -30247,7 +30247,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>104</v>
       </c>
@@ -30270,7 +30270,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>486</v>
       </c>
@@ -30293,7 +30293,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>183</v>
       </c>
@@ -30316,7 +30316,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>333</v>
       </c>
@@ -30339,7 +30339,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>466</v>
       </c>
@@ -30362,7 +30362,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>537</v>
       </c>
@@ -30385,7 +30385,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>69</v>
       </c>
@@ -30408,7 +30408,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>445</v>
       </c>
@@ -30431,7 +30431,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>542</v>
       </c>
@@ -30454,7 +30454,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>293</v>
       </c>
@@ -30477,7 +30477,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>506</v>
       </c>
@@ -30500,7 +30500,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>474</v>
       </c>
@@ -30523,7 +30523,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="31" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>440</v>
       </c>
@@ -30546,7 +30546,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>567</v>
       </c>
@@ -30569,7 +30569,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>163</v>
       </c>
@@ -30592,7 +30592,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="34" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>196</v>
       </c>
@@ -30615,7 +30615,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="35" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>383</v>
       </c>
@@ -30638,7 +30638,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="36" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>173</v>
       </c>
@@ -30661,7 +30661,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="37" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>367</v>
       </c>
@@ -30684,7 +30684,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>168</v>
       </c>
@@ -30707,7 +30707,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>185</v>
       </c>
@@ -30730,7 +30730,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="40" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>370</v>
       </c>
@@ -30753,7 +30753,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="41" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>432</v>
       </c>
@@ -30776,7 +30776,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="42" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>514</v>
       </c>
@@ -30799,7 +30799,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="43" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>148</v>
       </c>
@@ -30822,7 +30822,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="44" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>562</v>
       </c>
@@ -30845,7 +30845,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="45" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>33</v>
       </c>
@@ -30868,7 +30868,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="46" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>8</v>
       </c>
@@ -30914,7 +30914,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="48" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>510</v>
       </c>
@@ -30937,7 +30937,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="49" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>225</v>
       </c>
@@ -30960,7 +30960,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="50" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>512</v>
       </c>
@@ -30983,7 +30983,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="51" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>74</v>
       </c>
@@ -31006,7 +31006,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="52" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>495</v>
       </c>
@@ -31029,7 +31029,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="53" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>340</v>
       </c>
@@ -31052,7 +31052,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="54" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>218</v>
       </c>
@@ -31075,7 +31075,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="55" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>525</v>
       </c>
@@ -31098,7 +31098,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="56" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>400</v>
       </c>
@@ -31121,7 +31121,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="57" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>418</v>
       </c>
@@ -31144,7 +31144,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="58" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>437</v>
       </c>
@@ -31167,7 +31167,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="59" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>201</v>
       </c>
@@ -31190,7 +31190,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="60" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>573</v>
       </c>
@@ -31213,7 +31213,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="61" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>557</v>
       </c>
@@ -31236,7 +31236,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="62" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>137</v>
       </c>
@@ -31259,7 +31259,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="63" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>265</v>
       </c>
@@ -31282,7 +31282,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="64" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>320</v>
       </c>
@@ -31305,7 +31305,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="65" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>255</v>
       </c>
@@ -31328,7 +31328,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="66" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>63</v>
       </c>
@@ -31351,7 +31351,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="67" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>344</v>
       </c>
@@ -31374,7 +31374,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="68" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>438</v>
       </c>
@@ -31397,7 +31397,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="69" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>547</v>
       </c>
@@ -31420,7 +31420,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="70" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>184</v>
       </c>
@@ -31443,7 +31443,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="71" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>482</v>
       </c>
@@ -31466,7 +31466,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="72" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>434</v>
       </c>
@@ -31489,7 +31489,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="73" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>92</v>
       </c>
@@ -31512,7 +31512,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="74" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>472</v>
       </c>
@@ -31535,7 +31535,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="75" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>306</v>
       </c>
@@ -31558,7 +31558,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="76" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>301</v>
       </c>
@@ -31581,7 +31581,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="77" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>464</v>
       </c>
@@ -31604,7 +31604,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="78" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>469</v>
       </c>
@@ -31627,7 +31627,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="79" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>498</v>
       </c>
@@ -31650,7 +31650,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="80" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>539</v>
       </c>
@@ -31673,7 +31673,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="81" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>413</v>
       </c>
@@ -31696,7 +31696,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="82" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>478</v>
       </c>
@@ -31719,7 +31719,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="83" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>156</v>
       </c>
@@ -31742,7 +31742,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="84" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>540</v>
       </c>
@@ -31765,7 +31765,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="85" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>507</v>
       </c>
@@ -31788,7 +31788,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="86" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>566</v>
       </c>
@@ -31811,7 +31811,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="87" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>409</v>
       </c>
@@ -31834,7 +31834,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="88" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>534</v>
       </c>
@@ -31857,7 +31857,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="89" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>317</v>
       </c>
@@ -31880,7 +31880,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="90" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>209</v>
       </c>
@@ -31903,7 +31903,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="91" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>145</v>
       </c>
@@ -31926,7 +31926,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="92" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>564</v>
       </c>
@@ -31949,7 +31949,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="93" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>46</v>
       </c>
@@ -31972,7 +31972,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="94" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>268</v>
       </c>
@@ -31995,7 +31995,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="95" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>374</v>
       </c>
@@ -32018,7 +32018,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="96" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>114</v>
       </c>
@@ -32041,7 +32041,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="97" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>387</v>
       </c>
@@ -32064,7 +32064,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="98" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>461</v>
       </c>
@@ -32087,7 +32087,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="99" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>544</v>
       </c>
@@ -32110,7 +32110,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="100" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>195</v>
       </c>
@@ -32133,7 +32133,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="101" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>336</v>
       </c>
@@ -32156,7 +32156,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="102" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>375</v>
       </c>
@@ -32179,7 +32179,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="103" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>405</v>
       </c>
@@ -32202,7 +32202,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="104" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>348</v>
       </c>
@@ -32225,7 +32225,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="105" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>552</v>
       </c>
@@ -32248,7 +32248,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="106" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>81</v>
       </c>
@@ -32271,7 +32271,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="107" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>468</v>
       </c>
@@ -32294,7 +32294,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="108" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>206</v>
       </c>
@@ -32317,7 +32317,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="109" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>435</v>
       </c>
@@ -32340,7 +32340,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="110" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>324</v>
       </c>
@@ -32363,7 +32363,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="111" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>549</v>
       </c>
@@ -32386,7 +32386,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="112" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>362</v>
       </c>
@@ -32409,7 +32409,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="113" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>150</v>
       </c>
@@ -32432,7 +32432,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="114" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>180</v>
       </c>
@@ -32455,7 +32455,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="115" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>314</v>
       </c>
@@ -32478,7 +32478,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="116" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>555</v>
       </c>
@@ -32501,7 +32501,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="117" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>193</v>
       </c>
@@ -32524,7 +32524,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="118" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>154</v>
       </c>
@@ -32547,7 +32547,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="119" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>310</v>
       </c>
@@ -32570,7 +32570,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="120" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>26</v>
       </c>
@@ -32593,7 +32593,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="121" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>565</v>
       </c>
@@ -32616,7 +32616,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="122" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>259</v>
       </c>
@@ -32639,7 +32639,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="123" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>252</v>
       </c>
@@ -32662,7 +32662,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="124" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>263</v>
       </c>
@@ -32685,7 +32685,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="125" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>500</v>
       </c>
@@ -32708,7 +32708,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="126" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>99</v>
       </c>
@@ -32731,7 +32731,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="127" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>551</v>
       </c>
@@ -32754,7 +32754,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="128" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>197</v>
       </c>
@@ -32777,7 +32777,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="129" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>243</v>
       </c>
@@ -32800,7 +32800,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="130" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>247</v>
       </c>
@@ -32823,7 +32823,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="131" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>560</v>
       </c>
@@ -32846,7 +32846,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="132" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>420</v>
       </c>
@@ -32869,7 +32869,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="133" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>283</v>
       </c>
@@ -32892,7 +32892,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="134" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>213</v>
       </c>
@@ -32915,7 +32915,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="135" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>532</v>
       </c>
@@ -32938,7 +32938,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="136" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>277</v>
       </c>
@@ -32961,7 +32961,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="137" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>522</v>
       </c>
@@ -32984,7 +32984,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="138" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>538</v>
       </c>
@@ -33007,7 +33007,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="139" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>503</v>
       </c>
@@ -33030,7 +33030,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="140" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>229</v>
       </c>
@@ -33053,7 +33053,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="141" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>325</v>
       </c>
@@ -33076,7 +33076,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="142" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>358</v>
       </c>
@@ -33099,7 +33099,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="143" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>120</v>
       </c>
@@ -33122,7 +33122,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="144" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>376</v>
       </c>
@@ -33145,7 +33145,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="145" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>529</v>
       </c>
@@ -33168,7 +33168,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="146" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>330</v>
       </c>
@@ -33191,7 +33191,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="147" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>352</v>
       </c>
@@ -33214,7 +33214,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="148" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>140</v>
       </c>
@@ -33237,7 +33237,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="149" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>452</v>
       </c>
@@ -33260,7 +33260,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="150" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>490</v>
       </c>
@@ -33283,7 +33283,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="151" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>56</v>
       </c>
@@ -33306,7 +33306,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="152" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>428</v>
       </c>
@@ -33329,7 +33329,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="153" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>354</v>
       </c>
@@ -33352,7 +33352,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="154" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>518</v>
       </c>
@@ -33375,7 +33375,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="155" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>356</v>
       </c>
@@ -33398,7 +33398,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="156" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>456</v>
       </c>
@@ -33421,7 +33421,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="157" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>189</v>
       </c>
@@ -33444,7 +33444,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="158" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>289</v>
       </c>
@@ -33467,7 +33467,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="159" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>536</v>
       </c>
@@ -33490,7 +33490,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="160" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>221</v>
       </c>
@@ -33513,7 +33513,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="161" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>569</v>
       </c>
@@ -33536,7 +33536,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="162" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>126</v>
       </c>
@@ -33559,7 +33559,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="163" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>295</v>
       </c>
@@ -33582,7 +33582,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="164" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>107</v>
       </c>
@@ -33605,7 +33605,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="165" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>238</v>
       </c>
@@ -33628,7 +33628,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="166" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>389</v>
       </c>
@@ -33651,7 +33651,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="167" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>545</v>
       </c>
@@ -33674,7 +33674,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="168" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>280</v>
       </c>
@@ -33697,7 +33697,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="169" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>273</v>
       </c>
@@ -33720,7 +33720,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="170" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>396</v>
       </c>
@@ -33743,7 +33743,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="171" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>87</v>
       </c>
@@ -33766,7 +33766,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="172" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>188</v>
       </c>
@@ -33789,7 +33789,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="173" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>379</v>
       </c>
@@ -33812,7 +33812,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="174" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>422</v>
       </c>
@@ -33835,7 +33835,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="175" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>39</v>
       </c>
@@ -33858,7 +33858,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="176" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>449</v>
       </c>
@@ -33882,20 +33882,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G176" xr:uid="{00000000-0001-0000-0100-000000000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Alto Mando Aza"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:G176" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{716DE396-DFF8-497C-823B-D1510266F474}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -33916,7 +33909,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="65.25" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>612</v>
       </c>
@@ -33933,7 +33926,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>613</v>
       </c>
@@ -33950,7 +33943,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>614</v>
       </c>
@@ -33967,7 +33960,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>615</v>
       </c>
@@ -33984,7 +33977,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>616</v>
       </c>
@@ -34001,7 +33994,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>617</v>
       </c>
@@ -34018,7 +34011,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>618</v>
       </c>
@@ -34035,7 +34028,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>619</v>
       </c>
@@ -34052,7 +34045,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>620</v>
       </c>
@@ -34069,7 +34062,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>621</v>
       </c>
@@ -34086,7 +34079,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>622</v>
       </c>
@@ -34103,7 +34096,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>623</v>
       </c>
@@ -34120,9 +34113,9 @@
         <v>364</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>486</v>
@@ -34137,7 +34130,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>624</v>
       </c>
@@ -34154,7 +34147,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>625</v>
       </c>
@@ -34171,7 +34164,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>626</v>
       </c>
@@ -34188,7 +34181,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>627</v>
       </c>
@@ -34205,7 +34198,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:5" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>628</v>
       </c>
@@ -34222,7 +34215,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>629</v>
       </c>
@@ -34239,7 +34232,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>630</v>
       </c>
@@ -34256,7 +34249,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>631</v>
       </c>
@@ -34273,7 +34266,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>632</v>
       </c>
@@ -34290,7 +34283,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
         <v>633</v>
       </c>
@@ -34307,7 +34300,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:5" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
         <v>634</v>
       </c>
@@ -34324,7 +34317,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
         <v>635</v>
       </c>
@@ -34341,9 +34334,9 @@
         <v>566</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>340</v>
@@ -34358,7 +34351,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>636</v>
       </c>
@@ -34375,7 +34368,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
         <v>637</v>
       </c>
@@ -34392,7 +34385,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
         <v>638</v>
       </c>
@@ -34411,7 +34404,7 @@
     </row>
     <row r="31" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>225</v>
@@ -34426,7 +34419,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="39.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
         <v>639</v>
       </c>
@@ -34443,9 +34436,9 @@
         <v>173</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>383</v>
@@ -34460,7 +34453,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="34" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
         <v>640</v>
       </c>
@@ -34477,7 +34470,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="52.5" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
         <v>641</v>
       </c>
@@ -34494,7 +34487,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>642</v>
       </c>
@@ -34511,9 +34504,9 @@
         <v>186</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>349</v>
@@ -34528,7 +34521,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="38" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
         <v>643</v>
       </c>
@@ -34545,7 +34538,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
         <v>644</v>
       </c>
@@ -34562,7 +34555,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="27" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
         <v>645</v>
       </c>
@@ -34579,7 +34572,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
         <v>646</v>
       </c>
@@ -34597,13 +34590,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E41" xr:uid="{716DE396-DFF8-497C-823B-D1510266F474}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Jorginho Tv"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:E41" xr:uid="{716DE396-DFF8-497C-823B-D1510266F474}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/tiers_gen9nationaldexdoubles.xlsx
+++ b/tiers_gen9nationaldexdoubles.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\power bi\webhook\Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A1339BF-33D9-49CF-9DCB-89F146F21C22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7275690F-0466-43EB-8DD1-08E563FE84C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/tiers_gen9nationaldexdoubles.xlsx
+++ b/tiers_gen9nationaldexdoubles.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\power bi\webhook\Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7275690F-0466-43EB-8DD1-08E563FE84C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{710D1251-4C3E-4726-8F88-800FF1165A13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/tiers_gen9nationaldexdoubles.xlsx
+++ b/tiers_gen9nationaldexdoubles.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\power bi\webhook\Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{710D1251-4C3E-4726-8F88-800FF1165A13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D32762A-3D51-4A74-9E41-A4F6A1869518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2002,10 +2002,10 @@
     <t>Jorginho</t>
   </si>
   <si>
-    <t>Tauros-Paldea-Blaze</t>
-  </si>
-  <si>
-    <t>Tauros-Paldea-Aqua</t>
+    <t>Tauros-paldeaaqua</t>
+  </si>
+  <si>
+    <t>Tauros-paldeablaze</t>
   </si>
 </sst>
 </file>
@@ -6073,7 +6073,7 @@
         <v>140</v>
       </c>
       <c r="B139" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C139">
         <v>0.23100000000000001</v>
@@ -6229,7 +6229,7 @@
         <v>145</v>
       </c>
       <c r="B145" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C145">
         <v>0.30499999999999999</v>
@@ -16187,7 +16187,7 @@
         <v>358</v>
       </c>
       <c r="B528" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C528">
         <v>0.30499999999999999</v>
@@ -19177,7 +19177,7 @@
         <v>413</v>
       </c>
       <c r="B643" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C643">
         <v>0.30499999999999999</v>
@@ -23181,7 +23181,7 @@
         <v>482</v>
       </c>
       <c r="B797" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C797">
         <v>0.30499999999999999</v>
@@ -25885,7 +25885,7 @@
         <v>529</v>
       </c>
       <c r="B901" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C901">
         <v>0.30499999999999999</v>

--- a/tiers_gen9nationaldexdoubles.xlsx
+++ b/tiers_gen9nationaldexdoubles.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\power bi\webhook\Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D32762A-3D51-4A74-9E41-A4F6A1869518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E3DA97D-26AE-4CFB-B583-B2A0DAFD3975}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/tiers_gen9nationaldexdoubles.xlsx
+++ b/tiers_gen9nationaldexdoubles.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\power bi\webhook\Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E3DA97D-26AE-4CFB-B583-B2A0DAFD3975}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA0BEB0B-6147-4678-B7FA-23FC8EC1D9E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2005,7 +2005,7 @@
     <t>Tauros-paldeaaqua</t>
   </si>
   <si>
-    <t>Tauros-paldeablaze</t>
+    <t>Tauros-blaze</t>
   </si>
 </sst>
 </file>

--- a/tiers_gen9nationaldexdoubles.xlsx
+++ b/tiers_gen9nationaldexdoubles.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\power bi\webhook\Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA0BEB0B-6147-4678-B7FA-23FC8EC1D9E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F8FCF30-F764-4F02-9AC8-5ACF86B1B828}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pokemon" sheetId="1" r:id="rId1"/>
@@ -2466,7 +2466,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:H1051"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2506,7 +2505,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -2532,7 +2531,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -2558,7 +2557,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -2584,7 +2583,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -2610,7 +2609,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -2636,7 +2635,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -2662,7 +2661,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -2688,7 +2687,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -2714,7 +2713,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -2740,7 +2739,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -2766,7 +2765,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -2792,7 +2791,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -2818,7 +2817,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -2844,7 +2843,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>26</v>
       </c>
@@ -2870,7 +2869,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>26</v>
       </c>
@@ -2896,7 +2895,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -2922,7 +2921,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>26</v>
       </c>
@@ -2948,7 +2947,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>26</v>
       </c>
@@ -2974,7 +2973,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -3000,7 +2999,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>33</v>
       </c>
@@ -3026,7 +3025,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>33</v>
       </c>
@@ -3052,7 +3051,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>33</v>
       </c>
@@ -3078,7 +3077,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>33</v>
       </c>
@@ -3104,7 +3103,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="25" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>33</v>
       </c>
@@ -3130,7 +3129,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>39</v>
       </c>
@@ -3156,7 +3155,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="27" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>39</v>
       </c>
@@ -3182,7 +3181,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="28" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>39</v>
       </c>
@@ -3208,7 +3207,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="29" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>39</v>
       </c>
@@ -3234,7 +3233,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="30" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>39</v>
       </c>
@@ -3260,7 +3259,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="31" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>39</v>
       </c>
@@ -3286,7 +3285,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="32" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>46</v>
       </c>
@@ -3312,7 +3311,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="33" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>46</v>
       </c>
@@ -3338,7 +3337,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>46</v>
       </c>
@@ -3364,7 +3363,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="35" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>46</v>
       </c>
@@ -3390,7 +3389,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>46</v>
       </c>
@@ -3416,7 +3415,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="37" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>46</v>
       </c>
@@ -3442,7 +3441,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>51</v>
       </c>
@@ -3468,7 +3467,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="39" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>51</v>
       </c>
@@ -3494,7 +3493,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>51</v>
       </c>
@@ -3520,7 +3519,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="41" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>51</v>
       </c>
@@ -3546,7 +3545,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="42" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>51</v>
       </c>
@@ -3572,7 +3571,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="43" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>51</v>
       </c>
@@ -3598,7 +3597,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>56</v>
       </c>
@@ -3624,7 +3623,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="45" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>56</v>
       </c>
@@ -3650,7 +3649,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="46" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>56</v>
       </c>
@@ -3676,7 +3675,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="47" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>56</v>
       </c>
@@ -3702,7 +3701,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="48" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>56</v>
       </c>
@@ -3728,7 +3727,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="49" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>56</v>
       </c>
@@ -3754,7 +3753,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="50" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>63</v>
       </c>
@@ -3780,7 +3779,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="51" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>63</v>
       </c>
@@ -3806,7 +3805,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="52" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>63</v>
       </c>
@@ -3832,7 +3831,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="53" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>63</v>
       </c>
@@ -3858,7 +3857,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="54" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>63</v>
       </c>
@@ -3884,7 +3883,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="55" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>63</v>
       </c>
@@ -3910,7 +3909,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="56" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>69</v>
       </c>
@@ -3936,7 +3935,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="57" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>69</v>
       </c>
@@ -3962,7 +3961,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="58" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>69</v>
       </c>
@@ -3988,7 +3987,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="59" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>69</v>
       </c>
@@ -4014,7 +4013,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="60" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>69</v>
       </c>
@@ -4040,7 +4039,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="61" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>69</v>
       </c>
@@ -4066,7 +4065,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="62" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>74</v>
       </c>
@@ -4092,7 +4091,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="63" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>74</v>
       </c>
@@ -4118,7 +4117,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="64" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>74</v>
       </c>
@@ -4144,7 +4143,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="65" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>74</v>
       </c>
@@ -4170,7 +4169,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="66" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>74</v>
       </c>
@@ -4196,7 +4195,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="67" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>74</v>
       </c>
@@ -4222,7 +4221,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="68" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>81</v>
       </c>
@@ -4248,7 +4247,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="69" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>81</v>
       </c>
@@ -4274,7 +4273,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="70" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>81</v>
       </c>
@@ -4300,7 +4299,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="71" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>81</v>
       </c>
@@ -4326,7 +4325,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="72" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>81</v>
       </c>
@@ -4352,7 +4351,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="73" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>81</v>
       </c>
@@ -4378,7 +4377,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="74" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>87</v>
       </c>
@@ -4404,7 +4403,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="75" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>87</v>
       </c>
@@ -4430,7 +4429,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="76" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>87</v>
       </c>
@@ -4456,7 +4455,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="77" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>87</v>
       </c>
@@ -4482,7 +4481,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="78" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>87</v>
       </c>
@@ -4508,7 +4507,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="79" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>87</v>
       </c>
@@ -4534,7 +4533,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="80" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>92</v>
       </c>
@@ -4560,7 +4559,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="81" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>92</v>
       </c>
@@ -4586,7 +4585,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="82" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>92</v>
       </c>
@@ -4612,7 +4611,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="83" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>92</v>
       </c>
@@ -4638,7 +4637,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="84" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>92</v>
       </c>
@@ -4664,7 +4663,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="85" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>92</v>
       </c>
@@ -4690,7 +4689,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="86" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>99</v>
       </c>
@@ -4716,7 +4715,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="87" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>99</v>
       </c>
@@ -4742,7 +4741,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="88" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>99</v>
       </c>
@@ -4768,7 +4767,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="89" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>99</v>
       </c>
@@ -4794,7 +4793,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="90" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>99</v>
       </c>
@@ -4820,7 +4819,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="91" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>99</v>
       </c>
@@ -4846,7 +4845,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="92" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>104</v>
       </c>
@@ -4872,7 +4871,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="93" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>104</v>
       </c>
@@ -4898,7 +4897,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="94" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>104</v>
       </c>
@@ -4924,7 +4923,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="95" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>104</v>
       </c>
@@ -4950,7 +4949,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="96" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>104</v>
       </c>
@@ -4976,7 +4975,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="97" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>104</v>
       </c>
@@ -5002,7 +5001,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="98" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>107</v>
       </c>
@@ -5028,7 +5027,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="99" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>107</v>
       </c>
@@ -5054,7 +5053,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="100" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>107</v>
       </c>
@@ -5080,7 +5079,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="101" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>107</v>
       </c>
@@ -5106,7 +5105,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="102" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>107</v>
       </c>
@@ -5132,7 +5131,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="103" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>107</v>
       </c>
@@ -5158,7 +5157,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="104" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>114</v>
       </c>
@@ -5184,7 +5183,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="105" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>114</v>
       </c>
@@ -5210,7 +5209,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="106" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>114</v>
       </c>
@@ -5236,7 +5235,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="107" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>114</v>
       </c>
@@ -5262,7 +5261,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="108" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>114</v>
       </c>
@@ -5288,7 +5287,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="109" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>114</v>
       </c>
@@ -5314,7 +5313,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="110" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>120</v>
       </c>
@@ -5340,7 +5339,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="111" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>120</v>
       </c>
@@ -5366,7 +5365,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="112" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>120</v>
       </c>
@@ -5392,7 +5391,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="113" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>120</v>
       </c>
@@ -5418,7 +5417,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="114" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>120</v>
       </c>
@@ -5444,7 +5443,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="115" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>120</v>
       </c>
@@ -5470,7 +5469,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="116" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>126</v>
       </c>
@@ -5496,7 +5495,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="117" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>126</v>
       </c>
@@ -5522,7 +5521,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="118" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>126</v>
       </c>
@@ -5548,7 +5547,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="119" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>126</v>
       </c>
@@ -5574,7 +5573,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="120" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>126</v>
       </c>
@@ -5600,7 +5599,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="121" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>126</v>
       </c>
@@ -5626,7 +5625,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="122" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>132</v>
       </c>
@@ -5652,7 +5651,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="123" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>132</v>
       </c>
@@ -5678,7 +5677,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="124" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>132</v>
       </c>
@@ -5704,7 +5703,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="125" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>132</v>
       </c>
@@ -5730,7 +5729,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="126" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>132</v>
       </c>
@@ -5756,7 +5755,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="127" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>132</v>
       </c>
@@ -5782,7 +5781,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="128" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>137</v>
       </c>
@@ -5808,7 +5807,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="129" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>137</v>
       </c>
@@ -5834,7 +5833,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="130" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>137</v>
       </c>
@@ -5860,7 +5859,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="131" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>137</v>
       </c>
@@ -5886,7 +5885,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="132" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>137</v>
       </c>
@@ -5912,7 +5911,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="133" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>137</v>
       </c>
@@ -5938,7 +5937,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="134" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>140</v>
       </c>
@@ -5964,7 +5963,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="135" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>140</v>
       </c>
@@ -5990,7 +5989,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="136" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>140</v>
       </c>
@@ -6016,7 +6015,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="137" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>140</v>
       </c>
@@ -6042,7 +6041,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="138" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>140</v>
       </c>
@@ -6094,7 +6093,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="140" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>145</v>
       </c>
@@ -6120,7 +6119,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="141" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>145</v>
       </c>
@@ -6146,7 +6145,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="142" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>145</v>
       </c>
@@ -6172,7 +6171,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="143" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>145</v>
       </c>
@@ -6198,7 +6197,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="144" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>145</v>
       </c>
@@ -6250,7 +6249,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="146" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>148</v>
       </c>
@@ -6276,7 +6275,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="147" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>148</v>
       </c>
@@ -6302,7 +6301,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="148" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>148</v>
       </c>
@@ -6328,7 +6327,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="149" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>148</v>
       </c>
@@ -6354,7 +6353,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="150" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>148</v>
       </c>
@@ -6380,7 +6379,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="151" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>148</v>
       </c>
@@ -6406,7 +6405,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="152" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>150</v>
       </c>
@@ -6432,7 +6431,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="153" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>150</v>
       </c>
@@ -6458,7 +6457,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="154" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>150</v>
       </c>
@@ -6484,7 +6483,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="155" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>150</v>
       </c>
@@ -6510,7 +6509,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="156" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>150</v>
       </c>
@@ -6536,7 +6535,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="157" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>150</v>
       </c>
@@ -6562,7 +6561,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="158" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>154</v>
       </c>
@@ -6588,7 +6587,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="159" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>154</v>
       </c>
@@ -6614,7 +6613,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="160" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>154</v>
       </c>
@@ -6640,7 +6639,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="161" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>154</v>
       </c>
@@ -6666,7 +6665,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="162" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>154</v>
       </c>
@@ -6692,7 +6691,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="163" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>154</v>
       </c>
@@ -6718,7 +6717,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="164" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>156</v>
       </c>
@@ -6744,7 +6743,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="165" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>156</v>
       </c>
@@ -6770,7 +6769,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="166" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>156</v>
       </c>
@@ -6796,7 +6795,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="167" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>156</v>
       </c>
@@ -6822,7 +6821,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="168" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>156</v>
       </c>
@@ -6848,7 +6847,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="169" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>156</v>
       </c>
@@ -6874,7 +6873,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="170" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>158</v>
       </c>
@@ -6900,7 +6899,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="171" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>158</v>
       </c>
@@ -6926,7 +6925,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="172" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>158</v>
       </c>
@@ -6952,7 +6951,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="173" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>158</v>
       </c>
@@ -6978,7 +6977,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="174" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>158</v>
       </c>
@@ -7004,7 +7003,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="175" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>158</v>
       </c>
@@ -7030,7 +7029,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="176" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>163</v>
       </c>
@@ -7056,7 +7055,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="177" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>163</v>
       </c>
@@ -7082,7 +7081,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="178" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>163</v>
       </c>
@@ -7108,7 +7107,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="179" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>163</v>
       </c>
@@ -7134,7 +7133,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="180" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>163</v>
       </c>
@@ -7160,7 +7159,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="181" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>163</v>
       </c>
@@ -7186,7 +7185,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="182" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>168</v>
       </c>
@@ -7212,7 +7211,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="183" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>168</v>
       </c>
@@ -7238,7 +7237,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="184" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>168</v>
       </c>
@@ -7264,7 +7263,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="185" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>168</v>
       </c>
@@ -7290,7 +7289,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="186" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>168</v>
       </c>
@@ -7316,7 +7315,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="187" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>168</v>
       </c>
@@ -7342,7 +7341,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="188" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>173</v>
       </c>
@@ -7368,7 +7367,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="189" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>173</v>
       </c>
@@ -7394,7 +7393,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="190" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>173</v>
       </c>
@@ -7420,7 +7419,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="191" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>173</v>
       </c>
@@ -7446,7 +7445,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="192" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>173</v>
       </c>
@@ -7472,7 +7471,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="193" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>173</v>
       </c>
@@ -7498,7 +7497,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="194" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>180</v>
       </c>
@@ -7524,7 +7523,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="195" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>180</v>
       </c>
@@ -7550,7 +7549,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="196" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>180</v>
       </c>
@@ -7576,7 +7575,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="197" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>180</v>
       </c>
@@ -7602,7 +7601,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="198" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>180</v>
       </c>
@@ -7628,7 +7627,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="199" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>180</v>
       </c>
@@ -7654,7 +7653,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="200" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>183</v>
       </c>
@@ -7680,7 +7679,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="201" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>183</v>
       </c>
@@ -7706,7 +7705,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="202" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>183</v>
       </c>
@@ -7732,7 +7731,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="203" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>183</v>
       </c>
@@ -7758,7 +7757,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="204" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>183</v>
       </c>
@@ -7784,7 +7783,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="205" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>183</v>
       </c>
@@ -7810,7 +7809,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="206" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>184</v>
       </c>
@@ -7836,7 +7835,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="207" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>184</v>
       </c>
@@ -7862,7 +7861,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="208" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>184</v>
       </c>
@@ -7888,7 +7887,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="209" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>184</v>
       </c>
@@ -7914,7 +7913,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="210" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>184</v>
       </c>
@@ -7940,7 +7939,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="211" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>184</v>
       </c>
@@ -7966,7 +7965,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="212" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>185</v>
       </c>
@@ -7992,7 +7991,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="213" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>185</v>
       </c>
@@ -8018,7 +8017,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="214" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>185</v>
       </c>
@@ -8044,7 +8043,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="215" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>185</v>
       </c>
@@ -8070,7 +8069,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="216" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>185</v>
       </c>
@@ -8096,7 +8095,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="217" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>185</v>
       </c>
@@ -8122,7 +8121,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="218" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>186</v>
       </c>
@@ -8148,7 +8147,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="219" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>186</v>
       </c>
@@ -8174,7 +8173,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="220" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>186</v>
       </c>
@@ -8200,7 +8199,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="221" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>186</v>
       </c>
@@ -8226,7 +8225,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="222" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>186</v>
       </c>
@@ -8252,7 +8251,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="223" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>186</v>
       </c>
@@ -8278,7 +8277,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="224" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>188</v>
       </c>
@@ -8304,7 +8303,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="225" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>188</v>
       </c>
@@ -8330,7 +8329,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="226" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>188</v>
       </c>
@@ -8356,7 +8355,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="227" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>188</v>
       </c>
@@ -8382,7 +8381,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="228" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>188</v>
       </c>
@@ -8408,7 +8407,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="229" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>188</v>
       </c>
@@ -8434,7 +8433,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="230" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>189</v>
       </c>
@@ -8460,7 +8459,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="231" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>189</v>
       </c>
@@ -8486,7 +8485,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="232" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>189</v>
       </c>
@@ -8512,7 +8511,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="233" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>189</v>
       </c>
@@ -8538,7 +8537,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="234" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>189</v>
       </c>
@@ -8564,7 +8563,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="235" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>189</v>
       </c>
@@ -8590,7 +8589,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="236" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>193</v>
       </c>
@@ -8616,7 +8615,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="237" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>193</v>
       </c>
@@ -8642,7 +8641,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="238" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>193</v>
       </c>
@@ -8668,7 +8667,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="239" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>193</v>
       </c>
@@ -8694,7 +8693,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="240" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>193</v>
       </c>
@@ -8720,7 +8719,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="241" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>193</v>
       </c>
@@ -8746,7 +8745,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="242" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>195</v>
       </c>
@@ -8772,7 +8771,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="243" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>195</v>
       </c>
@@ -8798,7 +8797,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="244" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>195</v>
       </c>
@@ -8824,7 +8823,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="245" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>195</v>
       </c>
@@ -8850,7 +8849,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="246" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>195</v>
       </c>
@@ -8876,7 +8875,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="247" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>195</v>
       </c>
@@ -8902,7 +8901,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="248" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>196</v>
       </c>
@@ -8928,7 +8927,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="249" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>196</v>
       </c>
@@ -8954,7 +8953,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="250" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>196</v>
       </c>
@@ -8980,7 +8979,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="251" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>196</v>
       </c>
@@ -9006,7 +9005,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="252" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>196</v>
       </c>
@@ -9032,7 +9031,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="253" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>196</v>
       </c>
@@ -9058,7 +9057,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="254" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>197</v>
       </c>
@@ -9084,7 +9083,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="255" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>197</v>
       </c>
@@ -9110,7 +9109,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="256" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>197</v>
       </c>
@@ -9136,7 +9135,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="257" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>197</v>
       </c>
@@ -9162,7 +9161,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="258" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>197</v>
       </c>
@@ -9188,7 +9187,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="259" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>197</v>
       </c>
@@ -9214,7 +9213,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="260" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>201</v>
       </c>
@@ -9240,7 +9239,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="261" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>201</v>
       </c>
@@ -9266,7 +9265,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="262" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>201</v>
       </c>
@@ -9292,7 +9291,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="263" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>201</v>
       </c>
@@ -9318,7 +9317,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="264" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>201</v>
       </c>
@@ -9344,7 +9343,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="265" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>201</v>
       </c>
@@ -9370,7 +9369,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="266" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>206</v>
       </c>
@@ -9396,7 +9395,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="267" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>206</v>
       </c>
@@ -9422,7 +9421,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="268" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>206</v>
       </c>
@@ -9448,7 +9447,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="269" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>206</v>
       </c>
@@ -9474,7 +9473,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="270" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>206</v>
       </c>
@@ -9500,7 +9499,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="271" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>206</v>
       </c>
@@ -9526,7 +9525,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="272" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>209</v>
       </c>
@@ -9552,7 +9551,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="273" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>209</v>
       </c>
@@ -9578,7 +9577,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="274" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>209</v>
       </c>
@@ -9604,7 +9603,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="275" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>209</v>
       </c>
@@ -9630,7 +9629,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="276" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>209</v>
       </c>
@@ -9656,7 +9655,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="277" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>209</v>
       </c>
@@ -9682,7 +9681,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="278" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>213</v>
       </c>
@@ -9708,7 +9707,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="279" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>213</v>
       </c>
@@ -9734,7 +9733,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="280" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>213</v>
       </c>
@@ -9760,7 +9759,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="281" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>213</v>
       </c>
@@ -9786,7 +9785,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="282" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>213</v>
       </c>
@@ -9812,7 +9811,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="283" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>213</v>
       </c>
@@ -9838,7 +9837,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="284" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>218</v>
       </c>
@@ -9864,7 +9863,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="285" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>218</v>
       </c>
@@ -9890,7 +9889,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="286" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>218</v>
       </c>
@@ -9916,7 +9915,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="287" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>218</v>
       </c>
@@ -9942,7 +9941,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="288" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>218</v>
       </c>
@@ -9968,7 +9967,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="289" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>218</v>
       </c>
@@ -9994,7 +9993,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="290" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>221</v>
       </c>
@@ -10020,7 +10019,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="291" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>221</v>
       </c>
@@ -10046,7 +10045,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="292" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>221</v>
       </c>
@@ -10072,7 +10071,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="293" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>221</v>
       </c>
@@ -10098,7 +10097,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="294" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>221</v>
       </c>
@@ -10124,7 +10123,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="295" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>221</v>
       </c>
@@ -10150,7 +10149,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="296" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>225</v>
       </c>
@@ -10176,7 +10175,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="297" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>225</v>
       </c>
@@ -10202,7 +10201,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="298" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>225</v>
       </c>
@@ -10228,7 +10227,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="299" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>225</v>
       </c>
@@ -10254,7 +10253,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="300" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>225</v>
       </c>
@@ -10280,7 +10279,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="301" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>225</v>
       </c>
@@ -10306,7 +10305,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="302" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>229</v>
       </c>
@@ -10332,7 +10331,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="303" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>229</v>
       </c>
@@ -10358,7 +10357,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="304" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>229</v>
       </c>
@@ -10384,7 +10383,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="305" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>229</v>
       </c>
@@ -10410,7 +10409,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="306" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>229</v>
       </c>
@@ -10436,7 +10435,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="307" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>229</v>
       </c>
@@ -10462,7 +10461,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="308" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>233</v>
       </c>
@@ -10488,7 +10487,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="309" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>233</v>
       </c>
@@ -10514,7 +10513,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="310" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>233</v>
       </c>
@@ -10540,7 +10539,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="311" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>233</v>
       </c>
@@ -10566,7 +10565,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="312" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>233</v>
       </c>
@@ -10592,7 +10591,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="313" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>233</v>
       </c>
@@ -10618,7 +10617,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="314" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>238</v>
       </c>
@@ -10644,7 +10643,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="315" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>238</v>
       </c>
@@ -10670,7 +10669,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="316" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>238</v>
       </c>
@@ -10696,7 +10695,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="317" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>238</v>
       </c>
@@ -10722,7 +10721,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="318" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>238</v>
       </c>
@@ -10748,7 +10747,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="319" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>238</v>
       </c>
@@ -10774,7 +10773,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="320" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>243</v>
       </c>
@@ -10800,7 +10799,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="321" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>243</v>
       </c>
@@ -10826,7 +10825,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="322" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>243</v>
       </c>
@@ -10852,7 +10851,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="323" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>243</v>
       </c>
@@ -10878,7 +10877,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="324" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>243</v>
       </c>
@@ -10904,7 +10903,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="325" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>243</v>
       </c>
@@ -10930,7 +10929,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="326" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>247</v>
       </c>
@@ -10956,7 +10955,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="327" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>247</v>
       </c>
@@ -10982,7 +10981,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="328" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>247</v>
       </c>
@@ -11008,7 +11007,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="329" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>247</v>
       </c>
@@ -11034,7 +11033,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="330" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>247</v>
       </c>
@@ -11060,7 +11059,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="331" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>247</v>
       </c>
@@ -11086,7 +11085,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="332" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>252</v>
       </c>
@@ -11112,7 +11111,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="333" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>252</v>
       </c>
@@ -11138,7 +11137,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="334" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>252</v>
       </c>
@@ -11164,7 +11163,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="335" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>252</v>
       </c>
@@ -11190,7 +11189,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="336" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>252</v>
       </c>
@@ -11216,7 +11215,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="337" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>252</v>
       </c>
@@ -11242,7 +11241,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="338" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>255</v>
       </c>
@@ -11268,7 +11267,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="339" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>255</v>
       </c>
@@ -11294,7 +11293,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="340" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>255</v>
       </c>
@@ -11320,7 +11319,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="341" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>255</v>
       </c>
@@ -11346,7 +11345,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="342" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>255</v>
       </c>
@@ -11372,7 +11371,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="343" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>255</v>
       </c>
@@ -11398,7 +11397,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="344" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>259</v>
       </c>
@@ -11424,7 +11423,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="345" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>259</v>
       </c>
@@ -11450,7 +11449,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="346" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>259</v>
       </c>
@@ -11476,7 +11475,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="347" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>259</v>
       </c>
@@ -11502,7 +11501,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="348" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>259</v>
       </c>
@@ -11528,7 +11527,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="349" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>259</v>
       </c>
@@ -11554,7 +11553,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="350" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>263</v>
       </c>
@@ -11580,7 +11579,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="351" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>263</v>
       </c>
@@ -11606,7 +11605,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="352" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>263</v>
       </c>
@@ -11632,7 +11631,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="353" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>263</v>
       </c>
@@ -11658,7 +11657,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="354" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>263</v>
       </c>
@@ -11684,7 +11683,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="355" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>263</v>
       </c>
@@ -11710,7 +11709,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="356" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>265</v>
       </c>
@@ -11736,7 +11735,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="357" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>265</v>
       </c>
@@ -11762,7 +11761,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="358" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>265</v>
       </c>
@@ -11788,7 +11787,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="359" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>265</v>
       </c>
@@ -11814,7 +11813,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="360" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>265</v>
       </c>
@@ -11840,7 +11839,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="361" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>265</v>
       </c>
@@ -11866,7 +11865,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="362" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>268</v>
       </c>
@@ -11892,7 +11891,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="363" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>268</v>
       </c>
@@ -11918,7 +11917,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="364" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>268</v>
       </c>
@@ -11944,7 +11943,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="365" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>268</v>
       </c>
@@ -11970,7 +11969,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="366" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>268</v>
       </c>
@@ -11996,7 +11995,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="367" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>268</v>
       </c>
@@ -12022,7 +12021,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="368" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>273</v>
       </c>
@@ -12048,7 +12047,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="369" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>273</v>
       </c>
@@ -12074,7 +12073,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="370" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>273</v>
       </c>
@@ -12100,7 +12099,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="371" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>273</v>
       </c>
@@ -12126,7 +12125,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="372" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>273</v>
       </c>
@@ -12152,7 +12151,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="373" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>273</v>
       </c>
@@ -12178,7 +12177,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="374" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>277</v>
       </c>
@@ -12204,7 +12203,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="375" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>277</v>
       </c>
@@ -12230,7 +12229,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="376" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>277</v>
       </c>
@@ -12256,7 +12255,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="377" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>277</v>
       </c>
@@ -12282,7 +12281,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="378" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>277</v>
       </c>
@@ -12308,7 +12307,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="379" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>277</v>
       </c>
@@ -12334,7 +12333,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="380" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>280</v>
       </c>
@@ -12360,7 +12359,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="381" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>280</v>
       </c>
@@ -12386,7 +12385,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="382" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>280</v>
       </c>
@@ -12412,7 +12411,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="383" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>280</v>
       </c>
@@ -12438,7 +12437,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="384" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>280</v>
       </c>
@@ -12464,7 +12463,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="385" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>280</v>
       </c>
@@ -12490,7 +12489,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="386" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>283</v>
       </c>
@@ -12516,7 +12515,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="387" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>283</v>
       </c>
@@ -12542,7 +12541,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="388" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>283</v>
       </c>
@@ -12568,7 +12567,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="389" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>283</v>
       </c>
@@ -12594,7 +12593,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="390" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>283</v>
       </c>
@@ -12620,7 +12619,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="391" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>283</v>
       </c>
@@ -12646,7 +12645,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="392" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>289</v>
       </c>
@@ -12672,7 +12671,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="393" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>289</v>
       </c>
@@ -12698,7 +12697,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="394" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>289</v>
       </c>
@@ -12724,7 +12723,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="395" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>289</v>
       </c>
@@ -12750,7 +12749,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="396" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>289</v>
       </c>
@@ -12776,7 +12775,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="397" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>289</v>
       </c>
@@ -12802,7 +12801,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="398" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>293</v>
       </c>
@@ -12828,7 +12827,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="399" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>293</v>
       </c>
@@ -12854,7 +12853,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="400" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>293</v>
       </c>
@@ -12880,7 +12879,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="401" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>293</v>
       </c>
@@ -12906,7 +12905,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="402" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>293</v>
       </c>
@@ -12932,7 +12931,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="403" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>293</v>
       </c>
@@ -12958,7 +12957,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="404" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>295</v>
       </c>
@@ -12984,7 +12983,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="405" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>295</v>
       </c>
@@ -13010,7 +13009,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="406" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>295</v>
       </c>
@@ -13036,7 +13035,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="407" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>295</v>
       </c>
@@ -13062,7 +13061,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="408" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>295</v>
       </c>
@@ -13088,7 +13087,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="409" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>295</v>
       </c>
@@ -13114,7 +13113,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="410" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>301</v>
       </c>
@@ -13140,7 +13139,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="411" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>301</v>
       </c>
@@ -13166,7 +13165,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="412" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>301</v>
       </c>
@@ -13192,7 +13191,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="413" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>301</v>
       </c>
@@ -13218,7 +13217,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="414" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>301</v>
       </c>
@@ -13244,7 +13243,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="415" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>301</v>
       </c>
@@ -13270,7 +13269,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="416" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>306</v>
       </c>
@@ -13296,7 +13295,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="417" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>306</v>
       </c>
@@ -13322,7 +13321,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="418" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>306</v>
       </c>
@@ -13348,7 +13347,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="419" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>306</v>
       </c>
@@ -13374,7 +13373,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="420" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>306</v>
       </c>
@@ -13400,7 +13399,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="421" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>306</v>
       </c>
@@ -13426,7 +13425,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="422" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>310</v>
       </c>
@@ -13452,7 +13451,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="423" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>310</v>
       </c>
@@ -13478,7 +13477,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="424" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>310</v>
       </c>
@@ -13504,7 +13503,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="425" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>310</v>
       </c>
@@ -13530,7 +13529,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="426" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>310</v>
       </c>
@@ -13556,7 +13555,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="427" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>310</v>
       </c>
@@ -13582,7 +13581,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="428" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>314</v>
       </c>
@@ -13608,7 +13607,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="429" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>314</v>
       </c>
@@ -13634,7 +13633,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="430" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>314</v>
       </c>
@@ -13660,7 +13659,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="431" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>314</v>
       </c>
@@ -13686,7 +13685,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="432" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>314</v>
       </c>
@@ -13712,7 +13711,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="433" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>314</v>
       </c>
@@ -13738,7 +13737,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="434" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>317</v>
       </c>
@@ -13764,7 +13763,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="435" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>317</v>
       </c>
@@ -13790,7 +13789,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="436" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>317</v>
       </c>
@@ -13816,7 +13815,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="437" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>317</v>
       </c>
@@ -13842,7 +13841,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="438" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>317</v>
       </c>
@@ -13868,7 +13867,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="439" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>317</v>
       </c>
@@ -13894,7 +13893,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="440" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>320</v>
       </c>
@@ -13920,7 +13919,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="441" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>320</v>
       </c>
@@ -13946,7 +13945,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="442" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>320</v>
       </c>
@@ -13972,7 +13971,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="443" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>320</v>
       </c>
@@ -13998,7 +13997,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="444" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>320</v>
       </c>
@@ -14024,7 +14023,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="445" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>320</v>
       </c>
@@ -14050,7 +14049,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="446" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>322</v>
       </c>
@@ -14076,7 +14075,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="447" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>322</v>
       </c>
@@ -14102,7 +14101,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="448" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>322</v>
       </c>
@@ -14128,7 +14127,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="449" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>322</v>
       </c>
@@ -14154,7 +14153,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="450" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>322</v>
       </c>
@@ -14180,7 +14179,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="451" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>322</v>
       </c>
@@ -14206,7 +14205,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="452" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>324</v>
       </c>
@@ -14232,7 +14231,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="453" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>324</v>
       </c>
@@ -14258,7 +14257,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="454" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>324</v>
       </c>
@@ -14284,7 +14283,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="455" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>324</v>
       </c>
@@ -14310,7 +14309,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="456" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>324</v>
       </c>
@@ -14336,7 +14335,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="457" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>324</v>
       </c>
@@ -14362,7 +14361,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="458" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>325</v>
       </c>
@@ -14388,7 +14387,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="459" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>325</v>
       </c>
@@ -14414,7 +14413,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="460" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>325</v>
       </c>
@@ -14440,7 +14439,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="461" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>325</v>
       </c>
@@ -14466,7 +14465,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="462" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>325</v>
       </c>
@@ -14492,7 +14491,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="463" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>325</v>
       </c>
@@ -14518,7 +14517,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="464" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>330</v>
       </c>
@@ -14544,7 +14543,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="465" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>330</v>
       </c>
@@ -14570,7 +14569,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="466" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>330</v>
       </c>
@@ -14596,7 +14595,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="467" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>330</v>
       </c>
@@ -14622,7 +14621,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="468" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>330</v>
       </c>
@@ -14648,7 +14647,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="469" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>330</v>
       </c>
@@ -14674,7 +14673,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="470" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>333</v>
       </c>
@@ -14700,7 +14699,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="471" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>333</v>
       </c>
@@ -14726,7 +14725,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="472" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>333</v>
       </c>
@@ -14752,7 +14751,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="473" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>333</v>
       </c>
@@ -14778,7 +14777,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="474" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>333</v>
       </c>
@@ -14804,7 +14803,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="475" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>333</v>
       </c>
@@ -14830,7 +14829,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="476" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>336</v>
       </c>
@@ -14856,7 +14855,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="477" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>336</v>
       </c>
@@ -14882,7 +14881,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="478" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>336</v>
       </c>
@@ -14908,7 +14907,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="479" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>336</v>
       </c>
@@ -14934,7 +14933,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="480" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>336</v>
       </c>
@@ -14960,7 +14959,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="481" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>336</v>
       </c>
@@ -14986,7 +14985,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="482" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>340</v>
       </c>
@@ -15012,7 +15011,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="483" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
         <v>340</v>
       </c>
@@ -15038,7 +15037,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="484" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
         <v>340</v>
       </c>
@@ -15064,7 +15063,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="485" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
         <v>340</v>
       </c>
@@ -15090,7 +15089,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="486" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
         <v>340</v>
       </c>
@@ -15116,7 +15115,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="487" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
         <v>340</v>
       </c>
@@ -15142,7 +15141,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="488" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
         <v>344</v>
       </c>
@@ -15168,7 +15167,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="489" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
         <v>344</v>
       </c>
@@ -15194,7 +15193,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="490" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
         <v>344</v>
       </c>
@@ -15220,7 +15219,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="491" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
         <v>344</v>
       </c>
@@ -15246,7 +15245,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="492" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
         <v>344</v>
       </c>
@@ -15272,7 +15271,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="493" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
         <v>344</v>
       </c>
@@ -15298,7 +15297,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="494" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
         <v>348</v>
       </c>
@@ -15324,7 +15323,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="495" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
         <v>348</v>
       </c>
@@ -15350,7 +15349,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="496" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
         <v>348</v>
       </c>
@@ -15376,7 +15375,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="497" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
         <v>348</v>
       </c>
@@ -15402,7 +15401,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="498" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
         <v>348</v>
       </c>
@@ -15428,7 +15427,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="499" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
         <v>348</v>
       </c>
@@ -15454,7 +15453,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="500" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>349</v>
       </c>
@@ -15480,7 +15479,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="501" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
         <v>349</v>
       </c>
@@ -15506,7 +15505,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="502" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
         <v>349</v>
       </c>
@@ -15532,7 +15531,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="503" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
         <v>349</v>
       </c>
@@ -15558,7 +15557,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="504" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
         <v>349</v>
       </c>
@@ -15584,7 +15583,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="505" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
         <v>349</v>
       </c>
@@ -15610,7 +15609,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="506" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
         <v>352</v>
       </c>
@@ -15636,7 +15635,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="507" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
         <v>352</v>
       </c>
@@ -15662,7 +15661,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="508" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
         <v>352</v>
       </c>
@@ -15688,7 +15687,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="509" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
         <v>352</v>
       </c>
@@ -15714,7 +15713,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="510" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
         <v>352</v>
       </c>
@@ -15740,7 +15739,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="511" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
         <v>352</v>
       </c>
@@ -15766,7 +15765,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="512" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
         <v>354</v>
       </c>
@@ -15792,7 +15791,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="513" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
         <v>354</v>
       </c>
@@ -15818,7 +15817,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="514" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
         <v>354</v>
       </c>
@@ -15844,7 +15843,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="515" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
         <v>354</v>
       </c>
@@ -15870,7 +15869,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="516" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
         <v>354</v>
       </c>
@@ -15896,7 +15895,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="517" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
         <v>354</v>
       </c>
@@ -15922,7 +15921,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="518" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
         <v>356</v>
       </c>
@@ -15948,7 +15947,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="519" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
         <v>356</v>
       </c>
@@ -15974,7 +15973,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="520" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
         <v>356</v>
       </c>
@@ -16000,7 +15999,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="521" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
         <v>356</v>
       </c>
@@ -16026,7 +16025,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="522" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
         <v>356</v>
       </c>
@@ -16052,7 +16051,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="523" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
         <v>356</v>
       </c>
@@ -16078,7 +16077,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="524" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
         <v>358</v>
       </c>
@@ -16104,7 +16103,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="525" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
         <v>358</v>
       </c>
@@ -16130,7 +16129,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="526" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
         <v>358</v>
       </c>
@@ -16156,7 +16155,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="527" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
         <v>358</v>
       </c>
@@ -16208,7 +16207,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="529" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
         <v>358</v>
       </c>
@@ -16234,7 +16233,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="530" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
         <v>362</v>
       </c>
@@ -16260,7 +16259,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="531" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
         <v>362</v>
       </c>
@@ -16286,7 +16285,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="532" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
         <v>362</v>
       </c>
@@ -16312,7 +16311,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="533" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
         <v>362</v>
       </c>
@@ -16338,7 +16337,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="534" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
         <v>362</v>
       </c>
@@ -16364,7 +16363,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="535" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
         <v>362</v>
       </c>
@@ -16390,7 +16389,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="536" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
         <v>364</v>
       </c>
@@ -16416,7 +16415,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="537" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
         <v>364</v>
       </c>
@@ -16442,7 +16441,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="538" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
         <v>364</v>
       </c>
@@ -16468,7 +16467,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="539" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
         <v>364</v>
       </c>
@@ -16494,7 +16493,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="540" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
         <v>364</v>
       </c>
@@ -16520,7 +16519,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="541" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
         <v>364</v>
       </c>
@@ -16546,7 +16545,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="542" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
         <v>367</v>
       </c>
@@ -16572,7 +16571,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="543" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
         <v>367</v>
       </c>
@@ -16598,7 +16597,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="544" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
         <v>367</v>
       </c>
@@ -16624,7 +16623,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="545" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
         <v>367</v>
       </c>
@@ -16650,7 +16649,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="546" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
         <v>367</v>
       </c>
@@ -16676,7 +16675,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="547" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
         <v>367</v>
       </c>
@@ -16702,7 +16701,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="548" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
         <v>370</v>
       </c>
@@ -16728,7 +16727,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="549" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
         <v>370</v>
       </c>
@@ -16754,7 +16753,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="550" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
         <v>370</v>
       </c>
@@ -16780,7 +16779,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="551" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
         <v>370</v>
       </c>
@@ -16806,7 +16805,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="552" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
         <v>370</v>
       </c>
@@ -16832,7 +16831,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="553" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
         <v>370</v>
       </c>
@@ -16858,7 +16857,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="554" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
         <v>374</v>
       </c>
@@ -16884,7 +16883,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="555" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
         <v>374</v>
       </c>
@@ -16910,7 +16909,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="556" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
         <v>374</v>
       </c>
@@ -16936,7 +16935,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="557" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
         <v>374</v>
       </c>
@@ -16962,7 +16961,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="558" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
         <v>374</v>
       </c>
@@ -16988,7 +16987,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="559" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
         <v>374</v>
       </c>
@@ -17014,7 +17013,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="560" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
         <v>375</v>
       </c>
@@ -17040,7 +17039,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="561" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
         <v>375</v>
       </c>
@@ -17066,7 +17065,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="562" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
         <v>375</v>
       </c>
@@ -17092,7 +17091,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="563" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
         <v>375</v>
       </c>
@@ -17118,7 +17117,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="564" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
         <v>375</v>
       </c>
@@ -17144,7 +17143,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="565" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
         <v>375</v>
       </c>
@@ -17170,7 +17169,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="566" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
         <v>376</v>
       </c>
@@ -17196,7 +17195,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="567" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
         <v>376</v>
       </c>
@@ -17222,7 +17221,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="568" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
         <v>376</v>
       </c>
@@ -17248,7 +17247,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="569" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
         <v>376</v>
       </c>
@@ -17274,7 +17273,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="570" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
         <v>376</v>
       </c>
@@ -17300,7 +17299,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="571" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
         <v>376</v>
       </c>
@@ -17326,7 +17325,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="572" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
         <v>379</v>
       </c>
@@ -17352,7 +17351,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="573" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
         <v>379</v>
       </c>
@@ -17378,7 +17377,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="574" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
         <v>379</v>
       </c>
@@ -17404,7 +17403,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="575" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
         <v>379</v>
       </c>
@@ -17430,7 +17429,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="576" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
         <v>379</v>
       </c>
@@ -17456,7 +17455,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="577" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
         <v>379</v>
       </c>
@@ -17482,7 +17481,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="578" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
         <v>383</v>
       </c>
@@ -17508,7 +17507,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="579" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
         <v>383</v>
       </c>
@@ -17534,7 +17533,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="580" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
         <v>383</v>
       </c>
@@ -17560,7 +17559,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="581" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
         <v>383</v>
       </c>
@@ -17586,7 +17585,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="582" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
         <v>383</v>
       </c>
@@ -17612,7 +17611,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="583" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
         <v>383</v>
       </c>
@@ -17638,7 +17637,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="584" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
         <v>387</v>
       </c>
@@ -17664,7 +17663,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="585" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
         <v>387</v>
       </c>
@@ -17690,7 +17689,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="586" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
         <v>387</v>
       </c>
@@ -17716,7 +17715,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="587" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
         <v>387</v>
       </c>
@@ -17742,7 +17741,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="588" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
         <v>387</v>
       </c>
@@ -17768,7 +17767,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="589" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
         <v>387</v>
       </c>
@@ -17794,7 +17793,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="590" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
         <v>389</v>
       </c>
@@ -17820,7 +17819,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="591" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
         <v>389</v>
       </c>
@@ -17846,7 +17845,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="592" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
         <v>389</v>
       </c>
@@ -17872,7 +17871,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="593" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
         <v>389</v>
       </c>
@@ -17898,7 +17897,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="594" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
         <v>389</v>
       </c>
@@ -17924,7 +17923,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="595" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
         <v>389</v>
       </c>
@@ -17950,7 +17949,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="596" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
         <v>394</v>
       </c>
@@ -17976,7 +17975,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="597" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
         <v>394</v>
       </c>
@@ -18002,7 +18001,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="598" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
         <v>394</v>
       </c>
@@ -18028,7 +18027,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="599" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
         <v>394</v>
       </c>
@@ -18054,7 +18053,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="600" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
         <v>394</v>
       </c>
@@ -18080,7 +18079,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="601" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
         <v>394</v>
       </c>
@@ -18106,7 +18105,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="602" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
         <v>396</v>
       </c>
@@ -18132,7 +18131,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="603" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
         <v>396</v>
       </c>
@@ -18158,7 +18157,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="604" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
         <v>396</v>
       </c>
@@ -18184,7 +18183,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="605" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
         <v>396</v>
       </c>
@@ -18210,7 +18209,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="606" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
         <v>396</v>
       </c>
@@ -18236,7 +18235,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="607" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
         <v>396</v>
       </c>
@@ -18262,7 +18261,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="608" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
         <v>400</v>
       </c>
@@ -18288,7 +18287,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="609" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
         <v>400</v>
       </c>
@@ -18314,7 +18313,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="610" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
         <v>400</v>
       </c>
@@ -18340,7 +18339,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="611" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
         <v>400</v>
       </c>
@@ -18366,7 +18365,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="612" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
         <v>400</v>
       </c>
@@ -18392,7 +18391,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="613" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
         <v>400</v>
       </c>
@@ -18418,7 +18417,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="614" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
         <v>405</v>
       </c>
@@ -18444,7 +18443,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="615" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
         <v>405</v>
       </c>
@@ -18470,7 +18469,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="616" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
         <v>405</v>
       </c>
@@ -18496,7 +18495,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="617" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
         <v>405</v>
       </c>
@@ -18522,7 +18521,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="618" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
         <v>405</v>
       </c>
@@ -18548,7 +18547,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="619" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
         <v>405</v>
       </c>
@@ -18574,7 +18573,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="620" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
         <v>408</v>
       </c>
@@ -18600,7 +18599,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="621" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
         <v>408</v>
       </c>
@@ -18626,7 +18625,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="622" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
         <v>408</v>
       </c>
@@ -18652,7 +18651,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="623" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
         <v>408</v>
       </c>
@@ -18678,7 +18677,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="624" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
         <v>408</v>
       </c>
@@ -18704,7 +18703,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="625" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
         <v>408</v>
       </c>
@@ -18730,7 +18729,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="626" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
         <v>409</v>
       </c>
@@ -18756,7 +18755,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="627" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
         <v>409</v>
       </c>
@@ -18782,7 +18781,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="628" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
         <v>409</v>
       </c>
@@ -18808,7 +18807,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="629" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
         <v>409</v>
       </c>
@@ -18834,7 +18833,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="630" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
         <v>409</v>
       </c>
@@ -18860,7 +18859,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="631" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
         <v>409</v>
       </c>
@@ -18886,7 +18885,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="632" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
         <v>411</v>
       </c>
@@ -18912,7 +18911,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="633" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
         <v>411</v>
       </c>
@@ -18938,7 +18937,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="634" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
         <v>411</v>
       </c>
@@ -18964,7 +18963,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="635" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
         <v>411</v>
       </c>
@@ -18990,7 +18989,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="636" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
         <v>411</v>
       </c>
@@ -19016,7 +19015,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="637" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
         <v>411</v>
       </c>
@@ -19042,7 +19041,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="638" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
         <v>413</v>
       </c>
@@ -19068,7 +19067,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="639" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
         <v>413</v>
       </c>
@@ -19094,7 +19093,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="640" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
         <v>413</v>
       </c>
@@ -19120,7 +19119,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="641" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
         <v>413</v>
       </c>
@@ -19146,7 +19145,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="642" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
         <v>413</v>
       </c>
@@ -19198,7 +19197,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="644" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
         <v>418</v>
       </c>
@@ -19224,7 +19223,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="645" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
         <v>418</v>
       </c>
@@ -19250,7 +19249,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="646" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
         <v>418</v>
       </c>
@@ -19276,7 +19275,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="647" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
         <v>418</v>
       </c>
@@ -19302,7 +19301,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="648" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
         <v>418</v>
       </c>
@@ -19328,7 +19327,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="649" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
         <v>418</v>
       </c>
@@ -19354,7 +19353,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="650" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
         <v>420</v>
       </c>
@@ -19380,7 +19379,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="651" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
         <v>420</v>
       </c>
@@ -19406,7 +19405,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="652" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
         <v>420</v>
       </c>
@@ -19432,7 +19431,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="653" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
         <v>420</v>
       </c>
@@ -19458,7 +19457,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="654" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
         <v>420</v>
       </c>
@@ -19484,7 +19483,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="655" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
         <v>420</v>
       </c>
@@ -19510,7 +19509,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="656" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
         <v>422</v>
       </c>
@@ -19536,7 +19535,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="657" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
         <v>422</v>
       </c>
@@ -19562,7 +19561,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="658" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
         <v>422</v>
       </c>
@@ -19588,7 +19587,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="659" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
         <v>422</v>
       </c>
@@ -19614,7 +19613,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="660" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
         <v>422</v>
       </c>
@@ -19640,7 +19639,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="661" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
         <v>422</v>
       </c>
@@ -19666,7 +19665,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="662" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
         <v>428</v>
       </c>
@@ -19692,7 +19691,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="663" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
         <v>428</v>
       </c>
@@ -19718,7 +19717,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="664" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
         <v>428</v>
       </c>
@@ -19744,7 +19743,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="665" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
         <v>428</v>
       </c>
@@ -19770,7 +19769,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="666" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
         <v>428</v>
       </c>
@@ -19796,7 +19795,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="667" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
         <v>428</v>
       </c>
@@ -19822,7 +19821,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="668" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
         <v>431</v>
       </c>
@@ -19848,7 +19847,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="669" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
         <v>431</v>
       </c>
@@ -19874,7 +19873,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="670" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
         <v>431</v>
       </c>
@@ -19900,7 +19899,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="671" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
         <v>431</v>
       </c>
@@ -19926,7 +19925,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="672" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
         <v>431</v>
       </c>
@@ -19952,7 +19951,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="673" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
         <v>431</v>
       </c>
@@ -19978,7 +19977,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="674" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
         <v>432</v>
       </c>
@@ -20004,7 +20003,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="675" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
         <v>432</v>
       </c>
@@ -20030,7 +20029,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="676" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
         <v>432</v>
       </c>
@@ -20056,7 +20055,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="677" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
         <v>432</v>
       </c>
@@ -20082,7 +20081,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="678" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
         <v>432</v>
       </c>
@@ -20108,7 +20107,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="679" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
         <v>432</v>
       </c>
@@ -20134,7 +20133,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="680" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
         <v>434</v>
       </c>
@@ -20160,7 +20159,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="681" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
         <v>434</v>
       </c>
@@ -20186,7 +20185,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="682" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
         <v>434</v>
       </c>
@@ -20212,7 +20211,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="683" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
         <v>434</v>
       </c>
@@ -20238,7 +20237,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="684" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
         <v>434</v>
       </c>
@@ -20264,7 +20263,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="685" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
         <v>434</v>
       </c>
@@ -20290,7 +20289,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="686" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
         <v>435</v>
       </c>
@@ -20316,7 +20315,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="687" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
         <v>435</v>
       </c>
@@ -20342,7 +20341,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="688" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
         <v>435</v>
       </c>
@@ -20368,7 +20367,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="689" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
         <v>435</v>
       </c>
@@ -20394,7 +20393,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="690" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
         <v>435</v>
       </c>
@@ -20420,7 +20419,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="691" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
         <v>435</v>
       </c>
@@ -20446,7 +20445,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="692" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
         <v>437</v>
       </c>
@@ -20472,7 +20471,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="693" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
         <v>437</v>
       </c>
@@ -20498,7 +20497,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="694" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
         <v>437</v>
       </c>
@@ -20524,7 +20523,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="695" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
         <v>437</v>
       </c>
@@ -20550,7 +20549,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="696" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
         <v>437</v>
       </c>
@@ -20576,7 +20575,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="697" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
         <v>437</v>
       </c>
@@ -20602,7 +20601,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="698" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
         <v>438</v>
       </c>
@@ -20628,7 +20627,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="699" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
         <v>438</v>
       </c>
@@ -20654,7 +20653,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="700" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
         <v>438</v>
       </c>
@@ -20680,7 +20679,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="701" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
         <v>438</v>
       </c>
@@ -20706,7 +20705,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="702" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A702" t="s">
         <v>438</v>
       </c>
@@ -20732,7 +20731,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="703" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
         <v>438</v>
       </c>
@@ -20758,7 +20757,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="704" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A704" t="s">
         <v>440</v>
       </c>
@@ -20784,7 +20783,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="705" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
         <v>440</v>
       </c>
@@ -20810,7 +20809,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="706" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
         <v>440</v>
       </c>
@@ -20836,7 +20835,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="707" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
         <v>440</v>
       </c>
@@ -20862,7 +20861,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="708" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A708" t="s">
         <v>440</v>
       </c>
@@ -20888,7 +20887,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="709" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A709" t="s">
         <v>440</v>
       </c>
@@ -20914,7 +20913,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="710" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
         <v>443</v>
       </c>
@@ -20940,7 +20939,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="711" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A711" t="s">
         <v>443</v>
       </c>
@@ -20966,7 +20965,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="712" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A712" t="s">
         <v>443</v>
       </c>
@@ -20992,7 +20991,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="713" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A713" t="s">
         <v>443</v>
       </c>
@@ -21018,7 +21017,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="714" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A714" t="s">
         <v>443</v>
       </c>
@@ -21044,7 +21043,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="715" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A715" t="s">
         <v>443</v>
       </c>
@@ -21070,7 +21069,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="716" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A716" t="s">
         <v>445</v>
       </c>
@@ -21096,7 +21095,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="717" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A717" t="s">
         <v>445</v>
       </c>
@@ -21122,7 +21121,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="718" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A718" t="s">
         <v>445</v>
       </c>
@@ -21148,7 +21147,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="719" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A719" t="s">
         <v>445</v>
       </c>
@@ -21174,7 +21173,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="720" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A720" t="s">
         <v>445</v>
       </c>
@@ -21200,7 +21199,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="721" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A721" t="s">
         <v>445</v>
       </c>
@@ -21226,7 +21225,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="722" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A722" t="s">
         <v>449</v>
       </c>
@@ -21252,7 +21251,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="723" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A723" t="s">
         <v>449</v>
       </c>
@@ -21278,7 +21277,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="724" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A724" t="s">
         <v>449</v>
       </c>
@@ -21304,7 +21303,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="725" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A725" t="s">
         <v>449</v>
       </c>
@@ -21330,7 +21329,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="726" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A726" t="s">
         <v>449</v>
       </c>
@@ -21356,7 +21355,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="727" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A727" t="s">
         <v>449</v>
       </c>
@@ -21382,7 +21381,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="728" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A728" t="s">
         <v>452</v>
       </c>
@@ -21408,7 +21407,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="729" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A729" t="s">
         <v>452</v>
       </c>
@@ -21434,7 +21433,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="730" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A730" t="s">
         <v>452</v>
       </c>
@@ -21460,7 +21459,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="731" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A731" t="s">
         <v>452</v>
       </c>
@@ -21486,7 +21485,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="732" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A732" t="s">
         <v>452</v>
       </c>
@@ -21512,7 +21511,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="733" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A733" t="s">
         <v>452</v>
       </c>
@@ -21538,7 +21537,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="734" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A734" t="s">
         <v>454</v>
       </c>
@@ -21564,7 +21563,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="735" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A735" t="s">
         <v>454</v>
       </c>
@@ -21590,7 +21589,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="736" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A736" t="s">
         <v>454</v>
       </c>
@@ -21616,7 +21615,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="737" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A737" t="s">
         <v>454</v>
       </c>
@@ -21642,7 +21641,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="738" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A738" t="s">
         <v>454</v>
       </c>
@@ -21668,7 +21667,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="739" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A739" t="s">
         <v>454</v>
       </c>
@@ -21694,7 +21693,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="740" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A740" t="s">
         <v>456</v>
       </c>
@@ -21720,7 +21719,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="741" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A741" t="s">
         <v>456</v>
       </c>
@@ -21746,7 +21745,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="742" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A742" t="s">
         <v>456</v>
       </c>
@@ -21772,7 +21771,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="743" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A743" t="s">
         <v>456</v>
       </c>
@@ -21798,7 +21797,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="744" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A744" t="s">
         <v>456</v>
       </c>
@@ -21824,7 +21823,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="745" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A745" t="s">
         <v>456</v>
       </c>
@@ -21850,7 +21849,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="746" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A746" t="s">
         <v>461</v>
       </c>
@@ -21876,7 +21875,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="747" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A747" t="s">
         <v>461</v>
       </c>
@@ -21902,7 +21901,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="748" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A748" t="s">
         <v>461</v>
       </c>
@@ -21928,7 +21927,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="749" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A749" t="s">
         <v>461</v>
       </c>
@@ -21954,7 +21953,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="750" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A750" t="s">
         <v>461</v>
       </c>
@@ -21980,7 +21979,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="751" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A751" t="s">
         <v>461</v>
       </c>
@@ -22006,7 +22005,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="752" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A752" t="s">
         <v>464</v>
       </c>
@@ -22032,7 +22031,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="753" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A753" t="s">
         <v>464</v>
       </c>
@@ -22058,7 +22057,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="754" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A754" t="s">
         <v>464</v>
       </c>
@@ -22084,7 +22083,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="755" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A755" t="s">
         <v>464</v>
       </c>
@@ -22110,7 +22109,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="756" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A756" t="s">
         <v>464</v>
       </c>
@@ -22136,7 +22135,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="757" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A757" t="s">
         <v>464</v>
       </c>
@@ -22162,7 +22161,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="758" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A758" t="s">
         <v>466</v>
       </c>
@@ -22188,7 +22187,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="759" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A759" t="s">
         <v>466</v>
       </c>
@@ -22214,7 +22213,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="760" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A760" t="s">
         <v>466</v>
       </c>
@@ -22240,7 +22239,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="761" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A761" t="s">
         <v>466</v>
       </c>
@@ -22266,7 +22265,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="762" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A762" t="s">
         <v>466</v>
       </c>
@@ -22292,7 +22291,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="763" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A763" t="s">
         <v>466</v>
       </c>
@@ -22318,7 +22317,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="764" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A764" t="s">
         <v>468</v>
       </c>
@@ -22344,7 +22343,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="765" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A765" t="s">
         <v>468</v>
       </c>
@@ -22370,7 +22369,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="766" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A766" t="s">
         <v>468</v>
       </c>
@@ -22396,7 +22395,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="767" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A767" t="s">
         <v>468</v>
       </c>
@@ -22422,7 +22421,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="768" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A768" t="s">
         <v>468</v>
       </c>
@@ -22448,7 +22447,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="769" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A769" t="s">
         <v>468</v>
       </c>
@@ -22474,7 +22473,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="770" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A770" t="s">
         <v>469</v>
       </c>
@@ -22500,7 +22499,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="771" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A771" t="s">
         <v>469</v>
       </c>
@@ -22526,7 +22525,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="772" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A772" t="s">
         <v>469</v>
       </c>
@@ -22552,7 +22551,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="773" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A773" t="s">
         <v>469</v>
       </c>
@@ -22578,7 +22577,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="774" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A774" t="s">
         <v>469</v>
       </c>
@@ -22604,7 +22603,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="775" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A775" t="s">
         <v>469</v>
       </c>
@@ -22630,7 +22629,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="776" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A776" t="s">
         <v>472</v>
       </c>
@@ -22656,7 +22655,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="777" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A777" t="s">
         <v>472</v>
       </c>
@@ -22682,7 +22681,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="778" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A778" t="s">
         <v>472</v>
       </c>
@@ -22708,7 +22707,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="779" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A779" t="s">
         <v>472</v>
       </c>
@@ -22734,7 +22733,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="780" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A780" t="s">
         <v>472</v>
       </c>
@@ -22760,7 +22759,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="781" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A781" t="s">
         <v>472</v>
       </c>
@@ -22786,7 +22785,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="782" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A782" t="s">
         <v>474</v>
       </c>
@@ -22812,7 +22811,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="783" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A783" t="s">
         <v>474</v>
       </c>
@@ -22838,7 +22837,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="784" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A784" t="s">
         <v>474</v>
       </c>
@@ -22864,7 +22863,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="785" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A785" t="s">
         <v>474</v>
       </c>
@@ -22890,7 +22889,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="786" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A786" t="s">
         <v>474</v>
       </c>
@@ -22916,7 +22915,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="787" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A787" t="s">
         <v>474</v>
       </c>
@@ -22942,7 +22941,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="788" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A788" t="s">
         <v>478</v>
       </c>
@@ -22968,7 +22967,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="789" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A789" t="s">
         <v>478</v>
       </c>
@@ -22994,7 +22993,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="790" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A790" t="s">
         <v>478</v>
       </c>
@@ -23020,7 +23019,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="791" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A791" t="s">
         <v>478</v>
       </c>
@@ -23046,7 +23045,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="792" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A792" t="s">
         <v>478</v>
       </c>
@@ -23072,7 +23071,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="793" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A793" t="s">
         <v>478</v>
       </c>
@@ -23098,7 +23097,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="794" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A794" t="s">
         <v>482</v>
       </c>
@@ -23124,7 +23123,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="795" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A795" t="s">
         <v>482</v>
       </c>
@@ -23150,7 +23149,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="796" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A796" t="s">
         <v>482</v>
       </c>
@@ -23202,7 +23201,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="798" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A798" t="s">
         <v>482</v>
       </c>
@@ -23228,7 +23227,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="799" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A799" t="s">
         <v>482</v>
       </c>
@@ -23254,7 +23253,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="800" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A800" t="s">
         <v>486</v>
       </c>
@@ -23280,7 +23279,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="801" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A801" t="s">
         <v>486</v>
       </c>
@@ -23306,7 +23305,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="802" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A802" t="s">
         <v>486</v>
       </c>
@@ -23332,7 +23331,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="803" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A803" t="s">
         <v>486</v>
       </c>
@@ -23358,7 +23357,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="804" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A804" t="s">
         <v>486</v>
       </c>
@@ -23384,7 +23383,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="805" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A805" t="s">
         <v>486</v>
       </c>
@@ -23410,7 +23409,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="806" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A806" t="s">
         <v>490</v>
       </c>
@@ -23436,7 +23435,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="807" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A807" t="s">
         <v>490</v>
       </c>
@@ -23462,7 +23461,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="808" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A808" t="s">
         <v>490</v>
       </c>
@@ -23488,7 +23487,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="809" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A809" t="s">
         <v>490</v>
       </c>
@@ -23514,7 +23513,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="810" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A810" t="s">
         <v>490</v>
       </c>
@@ -23540,7 +23539,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="811" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A811" t="s">
         <v>490</v>
       </c>
@@ -23566,7 +23565,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="812" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A812" t="s">
         <v>495</v>
       </c>
@@ -23592,7 +23591,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="813" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A813" t="s">
         <v>495</v>
       </c>
@@ -23618,7 +23617,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="814" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A814" t="s">
         <v>495</v>
       </c>
@@ -23644,7 +23643,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="815" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A815" t="s">
         <v>495</v>
       </c>
@@ -23670,7 +23669,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="816" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A816" t="s">
         <v>495</v>
       </c>
@@ -23696,7 +23695,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="817" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A817" t="s">
         <v>495</v>
       </c>
@@ -23722,7 +23721,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="818" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A818" t="s">
         <v>497</v>
       </c>
@@ -23748,7 +23747,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="819" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A819" t="s">
         <v>497</v>
       </c>
@@ -23774,7 +23773,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="820" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A820" t="s">
         <v>497</v>
       </c>
@@ -23800,7 +23799,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="821" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A821" t="s">
         <v>497</v>
       </c>
@@ -23826,7 +23825,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="822" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A822" t="s">
         <v>497</v>
       </c>
@@ -23852,7 +23851,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="823" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A823" t="s">
         <v>497</v>
       </c>
@@ -23878,7 +23877,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="824" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A824" t="s">
         <v>498</v>
       </c>
@@ -23904,7 +23903,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="825" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A825" t="s">
         <v>498</v>
       </c>
@@ -23930,7 +23929,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="826" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A826" t="s">
         <v>498</v>
       </c>
@@ -23956,7 +23955,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="827" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A827" t="s">
         <v>498</v>
       </c>
@@ -23982,7 +23981,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="828" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A828" t="s">
         <v>498</v>
       </c>
@@ -24008,7 +24007,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="829" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A829" t="s">
         <v>498</v>
       </c>
@@ -24034,7 +24033,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="830" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A830" t="s">
         <v>500</v>
       </c>
@@ -24060,7 +24059,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="831" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A831" t="s">
         <v>500</v>
       </c>
@@ -24086,7 +24085,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="832" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A832" t="s">
         <v>500</v>
       </c>
@@ -24112,7 +24111,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="833" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A833" t="s">
         <v>500</v>
       </c>
@@ -24138,7 +24137,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="834" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A834" t="s">
         <v>500</v>
       </c>
@@ -24164,7 +24163,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="835" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A835" t="s">
         <v>500</v>
       </c>
@@ -24190,7 +24189,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="836" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A836" t="s">
         <v>503</v>
       </c>
@@ -24216,7 +24215,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="837" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A837" t="s">
         <v>503</v>
       </c>
@@ -24242,7 +24241,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="838" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A838" t="s">
         <v>503</v>
       </c>
@@ -24268,7 +24267,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="839" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A839" t="s">
         <v>503</v>
       </c>
@@ -24294,7 +24293,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="840" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A840" t="s">
         <v>503</v>
       </c>
@@ -24320,7 +24319,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="841" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A841" t="s">
         <v>503</v>
       </c>
@@ -24346,7 +24345,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="842" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A842" t="s">
         <v>506</v>
       </c>
@@ -24372,7 +24371,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="843" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A843" t="s">
         <v>506</v>
       </c>
@@ -24398,7 +24397,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="844" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A844" t="s">
         <v>506</v>
       </c>
@@ -24424,7 +24423,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="845" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A845" t="s">
         <v>506</v>
       </c>
@@ -24450,7 +24449,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="846" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A846" t="s">
         <v>506</v>
       </c>
@@ -24476,7 +24475,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="847" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A847" t="s">
         <v>506</v>
       </c>
@@ -24502,7 +24501,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="848" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A848" t="s">
         <v>507</v>
       </c>
@@ -24528,7 +24527,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="849" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A849" t="s">
         <v>507</v>
       </c>
@@ -24554,7 +24553,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="850" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A850" t="s">
         <v>507</v>
       </c>
@@ -24580,7 +24579,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="851" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A851" t="s">
         <v>507</v>
       </c>
@@ -24606,7 +24605,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="852" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A852" t="s">
         <v>507</v>
       </c>
@@ -24632,7 +24631,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="853" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A853" t="s">
         <v>507</v>
       </c>
@@ -24658,7 +24657,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="854" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A854" t="s">
         <v>510</v>
       </c>
@@ -24684,7 +24683,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="855" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A855" t="s">
         <v>510</v>
       </c>
@@ -24710,7 +24709,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="856" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A856" t="s">
         <v>510</v>
       </c>
@@ -24736,7 +24735,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="857" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A857" t="s">
         <v>510</v>
       </c>
@@ -24762,7 +24761,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="858" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A858" t="s">
         <v>510</v>
       </c>
@@ -24788,7 +24787,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="859" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A859" t="s">
         <v>510</v>
       </c>
@@ -24814,7 +24813,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="860" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A860" t="s">
         <v>512</v>
       </c>
@@ -24840,7 +24839,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="861" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A861" t="s">
         <v>512</v>
       </c>
@@ -24866,7 +24865,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="862" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A862" t="s">
         <v>512</v>
       </c>
@@ -24892,7 +24891,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="863" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A863" t="s">
         <v>512</v>
       </c>
@@ -24918,7 +24917,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="864" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A864" t="s">
         <v>512</v>
       </c>
@@ -24944,7 +24943,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="865" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A865" t="s">
         <v>512</v>
       </c>
@@ -24970,7 +24969,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="866" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A866" t="s">
         <v>514</v>
       </c>
@@ -24996,7 +24995,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="867" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A867" t="s">
         <v>514</v>
       </c>
@@ -25022,7 +25021,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="868" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A868" t="s">
         <v>514</v>
       </c>
@@ -25048,7 +25047,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="869" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A869" t="s">
         <v>514</v>
       </c>
@@ -25074,7 +25073,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="870" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A870" t="s">
         <v>514</v>
       </c>
@@ -25100,7 +25099,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="871" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A871" t="s">
         <v>514</v>
       </c>
@@ -25126,7 +25125,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="872" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A872" t="s">
         <v>515</v>
       </c>
@@ -25152,7 +25151,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="873" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A873" t="s">
         <v>515</v>
       </c>
@@ -25178,7 +25177,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="874" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A874" t="s">
         <v>515</v>
       </c>
@@ -25204,7 +25203,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="875" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A875" t="s">
         <v>515</v>
       </c>
@@ -25230,7 +25229,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="876" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A876" t="s">
         <v>515</v>
       </c>
@@ -25256,7 +25255,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="877" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A877" t="s">
         <v>515</v>
       </c>
@@ -25282,7 +25281,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="878" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A878" t="s">
         <v>518</v>
       </c>
@@ -25308,7 +25307,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="879" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A879" t="s">
         <v>518</v>
       </c>
@@ -25334,7 +25333,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="880" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A880" t="s">
         <v>518</v>
       </c>
@@ -25360,7 +25359,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="881" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A881" t="s">
         <v>518</v>
       </c>
@@ -25386,7 +25385,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="882" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A882" t="s">
         <v>518</v>
       </c>
@@ -25412,7 +25411,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="883" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A883" t="s">
         <v>518</v>
       </c>
@@ -25438,7 +25437,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="884" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A884" t="s">
         <v>522</v>
       </c>
@@ -25464,7 +25463,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="885" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A885" t="s">
         <v>522</v>
       </c>
@@ -25490,7 +25489,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="886" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A886" t="s">
         <v>522</v>
       </c>
@@ -25516,7 +25515,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="887" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A887" t="s">
         <v>522</v>
       </c>
@@ -25542,7 +25541,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="888" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A888" t="s">
         <v>522</v>
       </c>
@@ -25568,7 +25567,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="889" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="889" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A889" t="s">
         <v>522</v>
       </c>
@@ -25594,7 +25593,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="890" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="890" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A890" t="s">
         <v>525</v>
       </c>
@@ -25620,7 +25619,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="891" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A891" t="s">
         <v>525</v>
       </c>
@@ -25646,7 +25645,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="892" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A892" t="s">
         <v>525</v>
       </c>
@@ -25672,7 +25671,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="893" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A893" t="s">
         <v>525</v>
       </c>
@@ -25698,7 +25697,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="894" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A894" t="s">
         <v>525</v>
       </c>
@@ -25724,7 +25723,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="895" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A895" t="s">
         <v>525</v>
       </c>
@@ -25750,7 +25749,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="896" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A896" t="s">
         <v>529</v>
       </c>
@@ -25776,7 +25775,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="897" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A897" t="s">
         <v>529</v>
       </c>
@@ -25802,7 +25801,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="898" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A898" t="s">
         <v>529</v>
       </c>
@@ -25828,7 +25827,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="899" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A899" t="s">
         <v>529</v>
       </c>
@@ -25854,7 +25853,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="900" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A900" t="s">
         <v>529</v>
       </c>
@@ -25906,7 +25905,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="902" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="902" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A902" t="s">
         <v>532</v>
       </c>
@@ -25932,7 +25931,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="903" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A903" t="s">
         <v>532</v>
       </c>
@@ -25958,7 +25957,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="904" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A904" t="s">
         <v>532</v>
       </c>
@@ -25984,7 +25983,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="905" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="905" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A905" t="s">
         <v>532</v>
       </c>
@@ -26010,7 +26009,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="906" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A906" t="s">
         <v>532</v>
       </c>
@@ -26036,7 +26035,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="907" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A907" t="s">
         <v>532</v>
       </c>
@@ -26062,7 +26061,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="908" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="908" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A908" t="s">
         <v>534</v>
       </c>
@@ -26088,7 +26087,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="909" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="909" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A909" t="s">
         <v>534</v>
       </c>
@@ -26114,7 +26113,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="910" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="910" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A910" t="s">
         <v>534</v>
       </c>
@@ -26140,7 +26139,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="911" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="911" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A911" t="s">
         <v>534</v>
       </c>
@@ -26166,7 +26165,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="912" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="912" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A912" t="s">
         <v>534</v>
       </c>
@@ -26192,7 +26191,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="913" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="913" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A913" t="s">
         <v>534</v>
       </c>
@@ -26218,7 +26217,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="914" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="914" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A914" t="s">
         <v>536</v>
       </c>
@@ -26244,7 +26243,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="915" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="915" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A915" t="s">
         <v>536</v>
       </c>
@@ -26270,7 +26269,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="916" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="916" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A916" t="s">
         <v>536</v>
       </c>
@@ -26296,7 +26295,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="917" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="917" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A917" t="s">
         <v>536</v>
       </c>
@@ -26322,7 +26321,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="918" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="918" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A918" t="s">
         <v>536</v>
       </c>
@@ -26348,7 +26347,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="919" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="919" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A919" t="s">
         <v>536</v>
       </c>
@@ -26374,7 +26373,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="920" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="920" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A920" t="s">
         <v>537</v>
       </c>
@@ -26400,7 +26399,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="921" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="921" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A921" t="s">
         <v>537</v>
       </c>
@@ -26426,7 +26425,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="922" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="922" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A922" t="s">
         <v>537</v>
       </c>
@@ -26452,7 +26451,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="923" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="923" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A923" t="s">
         <v>537</v>
       </c>
@@ -26478,7 +26477,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="924" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="924" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A924" t="s">
         <v>537</v>
       </c>
@@ -26504,7 +26503,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="925" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="925" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A925" t="s">
         <v>537</v>
       </c>
@@ -26530,7 +26529,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="926" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="926" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A926" t="s">
         <v>538</v>
       </c>
@@ -26556,7 +26555,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="927" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="927" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A927" t="s">
         <v>538</v>
       </c>
@@ -26582,7 +26581,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="928" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="928" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A928" t="s">
         <v>538</v>
       </c>
@@ -26608,7 +26607,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="929" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="929" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A929" t="s">
         <v>538</v>
       </c>
@@ -26634,7 +26633,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="930" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="930" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A930" t="s">
         <v>538</v>
       </c>
@@ -26660,7 +26659,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="931" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="931" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A931" t="s">
         <v>538</v>
       </c>
@@ -26686,7 +26685,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="932" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="932" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A932" t="s">
         <v>539</v>
       </c>
@@ -26712,7 +26711,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="933" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="933" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A933" t="s">
         <v>539</v>
       </c>
@@ -26738,7 +26737,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="934" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="934" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A934" t="s">
         <v>539</v>
       </c>
@@ -26764,7 +26763,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="935" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="935" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A935" t="s">
         <v>539</v>
       </c>
@@ -26790,7 +26789,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="936" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="936" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A936" t="s">
         <v>539</v>
       </c>
@@ -26816,7 +26815,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="937" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="937" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A937" t="s">
         <v>539</v>
       </c>
@@ -26842,7 +26841,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="938" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="938" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A938" t="s">
         <v>540</v>
       </c>
@@ -26868,7 +26867,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="939" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="939" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A939" t="s">
         <v>540</v>
       </c>
@@ -26894,7 +26893,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="940" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="940" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A940" t="s">
         <v>540</v>
       </c>
@@ -26920,7 +26919,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="941" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="941" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A941" t="s">
         <v>540</v>
       </c>
@@ -26946,7 +26945,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="942" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="942" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A942" t="s">
         <v>540</v>
       </c>
@@ -26972,7 +26971,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="943" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="943" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A943" t="s">
         <v>540</v>
       </c>
@@ -26998,7 +26997,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="944" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="944" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A944" t="s">
         <v>542</v>
       </c>
@@ -27024,7 +27023,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="945" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="945" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A945" t="s">
         <v>542</v>
       </c>
@@ -27050,7 +27049,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="946" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="946" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A946" t="s">
         <v>542</v>
       </c>
@@ -27076,7 +27075,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="947" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="947" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A947" t="s">
         <v>542</v>
       </c>
@@ -27102,7 +27101,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="948" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="948" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A948" t="s">
         <v>542</v>
       </c>
@@ -27128,7 +27127,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="949" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="949" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A949" t="s">
         <v>542</v>
       </c>
@@ -27154,7 +27153,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="950" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="950" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A950" t="s">
         <v>544</v>
       </c>
@@ -27180,7 +27179,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="951" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="951" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A951" t="s">
         <v>544</v>
       </c>
@@ -27206,7 +27205,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="952" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="952" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A952" t="s">
         <v>544</v>
       </c>
@@ -27232,7 +27231,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="953" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="953" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A953" t="s">
         <v>544</v>
       </c>
@@ -27258,7 +27257,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="954" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="954" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A954" t="s">
         <v>544</v>
       </c>
@@ -27284,7 +27283,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="955" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="955" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A955" t="s">
         <v>544</v>
       </c>
@@ -27310,7 +27309,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="956" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="956" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A956" t="s">
         <v>545</v>
       </c>
@@ -27336,7 +27335,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="957" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="957" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A957" t="s">
         <v>545</v>
       </c>
@@ -27362,7 +27361,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="958" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="958" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A958" t="s">
         <v>545</v>
       </c>
@@ -27388,7 +27387,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="959" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="959" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A959" t="s">
         <v>545</v>
       </c>
@@ -27414,7 +27413,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="960" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="960" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A960" t="s">
         <v>545</v>
       </c>
@@ -27440,7 +27439,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="961" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="961" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A961" t="s">
         <v>545</v>
       </c>
@@ -27466,7 +27465,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="962" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="962" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A962" t="s">
         <v>547</v>
       </c>
@@ -27492,7 +27491,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="963" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="963" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A963" t="s">
         <v>547</v>
       </c>
@@ -27518,7 +27517,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="964" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="964" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A964" t="s">
         <v>547</v>
       </c>
@@ -27544,7 +27543,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="965" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="965" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A965" t="s">
         <v>547</v>
       </c>
@@ -27570,7 +27569,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="966" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="966" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A966" t="s">
         <v>547</v>
       </c>
@@ -27596,7 +27595,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="967" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="967" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A967" t="s">
         <v>547</v>
       </c>
@@ -27622,7 +27621,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="968" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="968" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A968" t="s">
         <v>549</v>
       </c>
@@ -27648,7 +27647,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="969" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="969" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A969" t="s">
         <v>549</v>
       </c>
@@ -27674,7 +27673,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="970" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="970" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A970" t="s">
         <v>549</v>
       </c>
@@ -27700,7 +27699,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="971" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="971" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A971" t="s">
         <v>549</v>
       </c>
@@ -27726,7 +27725,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="972" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="972" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A972" t="s">
         <v>549</v>
       </c>
@@ -27752,7 +27751,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="973" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="973" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A973" t="s">
         <v>549</v>
       </c>
@@ -27778,7 +27777,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="974" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="974" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A974" t="s">
         <v>551</v>
       </c>
@@ -27804,7 +27803,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="975" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="975" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A975" t="s">
         <v>551</v>
       </c>
@@ -27830,7 +27829,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="976" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="976" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A976" t="s">
         <v>551</v>
       </c>
@@ -27856,7 +27855,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="977" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="977" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A977" t="s">
         <v>551</v>
       </c>
@@ -27882,7 +27881,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="978" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="978" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A978" t="s">
         <v>551</v>
       </c>
@@ -27908,7 +27907,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="979" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="979" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A979" t="s">
         <v>551</v>
       </c>
@@ -27934,7 +27933,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="980" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="980" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A980" t="s">
         <v>552</v>
       </c>
@@ -27960,7 +27959,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="981" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="981" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A981" t="s">
         <v>552</v>
       </c>
@@ -27986,7 +27985,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="982" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="982" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A982" t="s">
         <v>552</v>
       </c>
@@ -28012,7 +28011,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="983" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="983" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A983" t="s">
         <v>552</v>
       </c>
@@ -28038,7 +28037,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="984" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="984" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A984" t="s">
         <v>552</v>
       </c>
@@ -28064,7 +28063,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="985" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="985" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A985" t="s">
         <v>552</v>
       </c>
@@ -28090,7 +28089,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="986" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="986" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A986" t="s">
         <v>555</v>
       </c>
@@ -28116,7 +28115,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="987" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="987" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A987" t="s">
         <v>555</v>
       </c>
@@ -28142,7 +28141,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="988" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="988" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A988" t="s">
         <v>555</v>
       </c>
@@ -28168,7 +28167,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="989" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="989" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A989" t="s">
         <v>555</v>
       </c>
@@ -28194,7 +28193,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="990" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="990" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A990" t="s">
         <v>555</v>
       </c>
@@ -28220,7 +28219,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="991" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="991" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A991" t="s">
         <v>555</v>
       </c>
@@ -28246,7 +28245,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="992" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="992" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A992" t="s">
         <v>557</v>
       </c>
@@ -28272,7 +28271,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="993" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="993" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A993" t="s">
         <v>557</v>
       </c>
@@ -28298,7 +28297,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="994" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="994" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A994" t="s">
         <v>557</v>
       </c>
@@ -28324,7 +28323,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="995" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="995" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A995" t="s">
         <v>557</v>
       </c>
@@ -28350,7 +28349,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="996" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="996" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A996" t="s">
         <v>557</v>
       </c>
@@ -28376,7 +28375,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="997" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="997" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A997" t="s">
         <v>557</v>
       </c>
@@ -28402,7 +28401,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="998" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="998" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A998" t="s">
         <v>559</v>
       </c>
@@ -28428,7 +28427,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="999" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="999" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A999" t="s">
         <v>559</v>
       </c>
@@ -28454,7 +28453,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1000" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1000" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1000" t="s">
         <v>559</v>
       </c>
@@ -28480,7 +28479,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1001" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1001" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1001" t="s">
         <v>559</v>
       </c>
@@ -28506,7 +28505,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1002" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1002" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1002" t="s">
         <v>559</v>
       </c>
@@ -28532,7 +28531,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="1003" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1003" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1003" t="s">
         <v>559</v>
       </c>
@@ -28558,7 +28557,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1004" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1004" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1004" t="s">
         <v>560</v>
       </c>
@@ -28584,7 +28583,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1005" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1005" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1005" t="s">
         <v>560</v>
       </c>
@@ -28610,7 +28609,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1006" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1006" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1006" t="s">
         <v>560</v>
       </c>
@@ -28636,7 +28635,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1007" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1007" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1007" t="s">
         <v>560</v>
       </c>
@@ -28662,7 +28661,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1008" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1008" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1008" t="s">
         <v>560</v>
       </c>
@@ -28688,7 +28687,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1009" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1009" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1009" t="s">
         <v>560</v>
       </c>
@@ -28714,7 +28713,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1010" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1010" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1010" t="s">
         <v>562</v>
       </c>
@@ -28740,7 +28739,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1011" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1011" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1011" t="s">
         <v>562</v>
       </c>
@@ -28766,7 +28765,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1012" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1012" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1012" t="s">
         <v>562</v>
       </c>
@@ -28792,7 +28791,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1013" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1013" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1013" t="s">
         <v>562</v>
       </c>
@@ -28818,7 +28817,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1014" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1014" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1014" t="s">
         <v>562</v>
       </c>
@@ -28844,7 +28843,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1015" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1015" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1015" t="s">
         <v>562</v>
       </c>
@@ -28870,7 +28869,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1016" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1016" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1016" t="s">
         <v>564</v>
       </c>
@@ -28896,7 +28895,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1017" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1017" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1017" t="s">
         <v>564</v>
       </c>
@@ -28922,7 +28921,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1018" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1018" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1018" t="s">
         <v>564</v>
       </c>
@@ -28948,7 +28947,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1019" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1019" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1019" t="s">
         <v>564</v>
       </c>
@@ -28974,7 +28973,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1020" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1020" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1020" t="s">
         <v>564</v>
       </c>
@@ -29000,7 +28999,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1021" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1021" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1021" t="s">
         <v>564</v>
       </c>
@@ -29026,7 +29025,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1022" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1022" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1022" t="s">
         <v>565</v>
       </c>
@@ -29052,7 +29051,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1023" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1023" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1023" t="s">
         <v>565</v>
       </c>
@@ -29078,7 +29077,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1024" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1024" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1024" t="s">
         <v>565</v>
       </c>
@@ -29104,7 +29103,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1025" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1025" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1025" t="s">
         <v>565</v>
       </c>
@@ -29130,7 +29129,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1026" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1026" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1026" t="s">
         <v>565</v>
       </c>
@@ -29156,7 +29155,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1027" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1027" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1027" t="s">
         <v>565</v>
       </c>
@@ -29182,7 +29181,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1028" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1028" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1028" t="s">
         <v>566</v>
       </c>
@@ -29208,7 +29207,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1029" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1029" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1029" t="s">
         <v>566</v>
       </c>
@@ -29234,7 +29233,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1030" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1030" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1030" t="s">
         <v>566</v>
       </c>
@@ -29260,7 +29259,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1031" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1031" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1031" t="s">
         <v>566</v>
       </c>
@@ -29286,7 +29285,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1032" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1032" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1032" t="s">
         <v>566</v>
       </c>
@@ -29312,7 +29311,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1033" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1033" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1033" t="s">
         <v>566</v>
       </c>
@@ -29338,7 +29337,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1034" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1034" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1034" t="s">
         <v>567</v>
       </c>
@@ -29364,7 +29363,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1035" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1035" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1035" t="s">
         <v>567</v>
       </c>
@@ -29390,7 +29389,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1036" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1036" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1036" t="s">
         <v>567</v>
       </c>
@@ -29416,7 +29415,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1037" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1037" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1037" t="s">
         <v>567</v>
       </c>
@@ -29442,7 +29441,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1038" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1038" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1038" t="s">
         <v>567</v>
       </c>
@@ -29468,7 +29467,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1039" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1039" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1039" t="s">
         <v>567</v>
       </c>
@@ -29494,7 +29493,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1040" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1040" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1040" t="s">
         <v>569</v>
       </c>
@@ -29520,7 +29519,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1041" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1041" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1041" t="s">
         <v>569</v>
       </c>
@@ -29546,7 +29545,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1042" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1042" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1042" t="s">
         <v>569</v>
       </c>
@@ -29572,7 +29571,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1043" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1043" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1043" t="s">
         <v>569</v>
       </c>
@@ -29598,7 +29597,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1044" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1044" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1044" t="s">
         <v>569</v>
       </c>
@@ -29624,7 +29623,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1045" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1045" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1045" t="s">
         <v>569</v>
       </c>
@@ -29650,7 +29649,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1046" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1046" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1046" t="s">
         <v>573</v>
       </c>
@@ -29676,7 +29675,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="1047" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1047" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1047" t="s">
         <v>573</v>
       </c>
@@ -29702,7 +29701,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="1048" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1048" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1048" t="s">
         <v>573</v>
       </c>
@@ -29728,7 +29727,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="1049" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1049" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1049" t="s">
         <v>573</v>
       </c>
@@ -29754,7 +29753,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1050" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1050" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1050" t="s">
         <v>573</v>
       </c>
@@ -29780,7 +29779,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="1051" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1051" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1051" t="s">
         <v>573</v>
       </c>
@@ -29807,14 +29806,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1051" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="Tauros_Paldea_Aqua"/>
-        <filter val="Tauros_Paldea_Blaze"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:H1051" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/tiers_gen9nationaldexdoubles.xlsx
+++ b/tiers_gen9nationaldexdoubles.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\power bi\webhook\Produccion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F8FCF30-F764-4F02-9AC8-5ACF86B1B828}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81F95D19-53DA-4DF3-A21F-79E367670753}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1933,9 +1933,6 @@
     <t>Angelowos</t>
   </si>
   <si>
-    <t>mounstronio</t>
-  </si>
-  <si>
     <t>JaLax</t>
   </si>
   <si>
@@ -2006,6 +2003,9 @@
   </si>
   <si>
     <t>Tauros-blaze</t>
+  </si>
+  <si>
+    <t>monstruonio</t>
   </si>
 </sst>
 </file>
@@ -6072,7 +6072,7 @@
         <v>140</v>
       </c>
       <c r="B139" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C139">
         <v>0.23100000000000001</v>
@@ -6228,7 +6228,7 @@
         <v>145</v>
       </c>
       <c r="B145" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C145">
         <v>0.30499999999999999</v>
@@ -7580,7 +7580,7 @@
         <v>180</v>
       </c>
       <c r="B197" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C197">
         <v>0</v>
@@ -8360,7 +8360,7 @@
         <v>188</v>
       </c>
       <c r="B227" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C227">
         <v>0</v>
@@ -16186,7 +16186,7 @@
         <v>358</v>
       </c>
       <c r="B528" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C528">
         <v>0.30499999999999999</v>
@@ -17278,7 +17278,7 @@
         <v>376</v>
       </c>
       <c r="B570" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C570">
         <v>0.2</v>
@@ -19176,7 +19176,7 @@
         <v>413</v>
       </c>
       <c r="B643" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C643">
         <v>0.30499999999999999</v>
@@ -21386,7 +21386,7 @@
         <v>452</v>
       </c>
       <c r="B728" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C728">
         <v>0.2</v>
@@ -23180,7 +23180,7 @@
         <v>482</v>
       </c>
       <c r="B797" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C797">
         <v>0.30499999999999999</v>
@@ -25884,7 +25884,7 @@
         <v>529</v>
       </c>
       <c r="B901" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C901">
         <v>0.30499999999999999</v>
@@ -26326,7 +26326,7 @@
         <v>536</v>
       </c>
       <c r="B918" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C918">
         <v>0</v>
@@ -29524,7 +29524,7 @@
         <v>569</v>
       </c>
       <c r="B1041" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C1041">
         <v>0</v>
@@ -34107,7 +34107,7 @@
     </row>
     <row r="14" spans="1:5" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>486</v>
@@ -34243,7 +34243,7 @@
     </row>
     <row r="22" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>631</v>
+        <v>655</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>51</v>
@@ -34260,7 +34260,7 @@
     </row>
     <row r="23" spans="1:5" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>490</v>
@@ -34277,7 +34277,7 @@
     </row>
     <row r="24" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>537</v>
@@ -34294,7 +34294,7 @@
     </row>
     <row r="25" spans="1:5" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>495</v>
@@ -34311,7 +34311,7 @@
     </row>
     <row r="26" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>573</v>
@@ -34328,7 +34328,7 @@
     </row>
     <row r="27" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>340</v>
@@ -34345,7 +34345,7 @@
     </row>
     <row r="28" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>356</v>
@@ -34362,7 +34362,7 @@
     </row>
     <row r="29" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>512</v>
@@ -34379,7 +34379,7 @@
     </row>
     <row r="30" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>26</v>
@@ -34396,7 +34396,7 @@
     </row>
     <row r="31" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>225</v>
@@ -34413,7 +34413,7 @@
     </row>
     <row r="32" spans="1:5" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>472</v>
@@ -34430,7 +34430,7 @@
     </row>
     <row r="33" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>383</v>
@@ -34447,7 +34447,7 @@
     </row>
     <row r="34" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>420</v>
@@ -34464,7 +34464,7 @@
     </row>
     <row r="35" spans="1:5" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>478</v>
@@ -34481,7 +34481,7 @@
     </row>
     <row r="36" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>370</v>
@@ -34498,7 +34498,7 @@
     </row>
     <row r="37" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>349</v>
@@ -34515,7 +34515,7 @@
     </row>
     <row r="38" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>137</v>
@@ -34532,7 +34532,7 @@
     </row>
     <row r="39" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>418</v>
@@ -34549,7 +34549,7 @@
     </row>
     <row r="40" spans="1:5" ht="27" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>538</v>
@@ -34566,7 +34566,7 @@
     </row>
     <row r="41" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>148</v>
